--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8490FE09-7A4C-4A04-A09A-427C782C9E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CB9BBC-85A9-4ED5-A911-360DF8659758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,75 @@
   </si>
   <si>
     <t>Productive day and was amazing to learn new programming language.</t>
+  </si>
+  <si>
+    <t>Had football team meeting and photo session for Fresher sports league. Attended Industry Academic AI summit.</t>
+  </si>
+  <si>
+    <t>Enrolled for new skill swimming.</t>
+  </si>
+  <si>
+    <t>First day at swimming,learnt how to float. Happy to be selected in football team for fresher sports league.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Today was Sunday,had amaazing time with friends.</t>
+  </si>
+  <si>
+    <t>Made ppts for Idea Pitching in Ideabazz competition and myself accordingly for that.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Very satisfied with day curriculum,feeling sleepy in classes as well as in the library but playing football and swimming made my day.</t>
+  </si>
+  <si>
+    <t>Today I had a meeting with Agribot club lead,there I learnt 3D modeling using fusion software.Also discussed about SIH.</t>
+  </si>
+  <si>
+    <t>After classes traveled to my cousin sister's house for rakshabandhan. Discovered how the busses run in Punjab bit different from Bihar.</t>
+  </si>
+  <si>
+    <t>Today on rakshabandhan I gifted my sister a earphone. After celebrating rakshabandhan, I travelled to mini goa,ranjit sagar dam and mukteshwar mahadev mandir with my friend.</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>While returning, I came along with Punjab police who were inquiring the every doubt faces, which completely okay and was very happy to see their honesty.</t>
+  </si>
+  <si>
+    <t>Was good.</t>
+  </si>
+  <si>
+    <t>Today I played my first Fresher league match(Football) and unfrotunately lost the match but learnt good lessons.Also my first CA of english was delivered well but I am not satisfied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today we had a session with the head of Innovation studio. He spoke about  the mentorship and guidance for SIH. </t>
+  </si>
+  <si>
+    <t>Fresh start of the week with interaction with google and delloitte experts. I learnt about NLM and using AI Productively.</t>
+  </si>
+  <si>
+    <t>Today was the first day of the  month and planned the whole month.</t>
+  </si>
+  <si>
+    <t>Today i was feeling low due to internal fever.Best part my roomates helped me recover fast by providing medicine and steam.</t>
+  </si>
+  <si>
+    <t>Was good and restful day.</t>
+  </si>
+  <si>
+    <t>Today we had a another match,but got cancelled due to rian.</t>
+  </si>
+  <si>
+    <t>Last day of the weekend,looking at the watch,let all classes ends and I go to the hostel and enjoy football.</t>
   </si>
 </sst>
 </file>
@@ -1100,468 +1169,924 @@
       <c r="A8" s="18">
         <v>46253</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10" t="str">
+      <c r="B8" s="9">
+        <v>360</v>
+      </c>
+      <c r="C8" s="9">
+        <v>30</v>
+      </c>
+      <c r="D8" s="9">
+        <v>240</v>
+      </c>
+      <c r="E8" s="9">
+        <v>90</v>
+      </c>
+      <c r="F8" s="9">
+        <v>420</v>
+      </c>
+      <c r="G8" s="9">
+        <v>7</v>
+      </c>
+      <c r="H8" s="9">
+        <v>60</v>
+      </c>
+      <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="10" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J8" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
+        <v>240</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>46254</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
+      <c r="B9" s="9">
+        <v>360</v>
+      </c>
+      <c r="C9" s="9">
+        <v>30</v>
+      </c>
+      <c r="D9" s="9">
+        <v>200</v>
+      </c>
+      <c r="E9" s="9">
+        <v>90</v>
+      </c>
+      <c r="F9" s="9">
+        <v>150</v>
+      </c>
+      <c r="G9" s="9">
+        <v>3</v>
+      </c>
+      <c r="H9" s="9">
+        <v>60</v>
+      </c>
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="str">
+        <v>890</v>
+      </c>
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="18">
         <v>46255</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="str">
+      <c r="B10" s="9">
+        <v>360</v>
+      </c>
+      <c r="C10" s="9">
+        <v>60</v>
+      </c>
+      <c r="D10" s="9">
+        <v>300</v>
+      </c>
+      <c r="E10" s="9">
+        <v>60</v>
+      </c>
+      <c r="F10" s="9">
+        <v>200</v>
+      </c>
+      <c r="G10" s="9">
+        <v>4</v>
+      </c>
+      <c r="H10" s="9">
+        <v>20</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="12"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>46256</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10" t="str">
+      <c r="B11" s="9">
+        <v>420</v>
+      </c>
+      <c r="C11" s="9">
+        <v>50</v>
+      </c>
+      <c r="D11" s="9">
+        <v>300</v>
+      </c>
+      <c r="E11" s="9">
+        <v>60</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>180</v>
+      </c>
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18">
         <v>46257</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
+      <c r="B12" s="9">
+        <v>360</v>
+      </c>
+      <c r="C12" s="9">
+        <v>20</v>
+      </c>
+      <c r="D12" s="9">
+        <v>60</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>240</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>680</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>760</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>46258</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
+      <c r="B13" s="9">
+        <v>360</v>
+      </c>
+      <c r="C13" s="9">
+        <v>50</v>
+      </c>
+      <c r="D13" s="9">
+        <v>120</v>
+      </c>
+      <c r="E13" s="9">
+        <v>30</v>
+      </c>
+      <c r="F13" s="9">
+        <v>300</v>
+      </c>
+      <c r="G13" s="9">
+        <v>6</v>
+      </c>
+      <c r="H13" s="9">
+        <v>180</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="18">
         <v>46259</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+      <c r="B14" s="9">
+        <v>360</v>
+      </c>
+      <c r="C14" s="9">
+        <v>120</v>
+      </c>
+      <c r="D14" s="9">
+        <v>60</v>
+      </c>
+      <c r="E14" s="9">
+        <v>20</v>
+      </c>
+      <c r="F14" s="9">
+        <v>150</v>
+      </c>
+      <c r="G14" s="9">
+        <v>3</v>
+      </c>
+      <c r="H14" s="9">
+        <v>60</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>770</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>46260</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+      <c r="B15" s="9">
+        <v>300</v>
+      </c>
+      <c r="C15" s="9">
+        <v>50</v>
+      </c>
+      <c r="D15" s="9">
+        <v>60</v>
+      </c>
+      <c r="E15" s="9">
+        <v>20</v>
+      </c>
+      <c r="F15" s="9">
+        <v>400</v>
+      </c>
+      <c r="G15" s="9">
+        <v>8</v>
+      </c>
+      <c r="H15" s="9">
+        <v>120</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>490</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="18">
         <v>46261</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+      <c r="B16" s="9">
+        <v>300</v>
+      </c>
+      <c r="C16" s="9">
+        <v>50</v>
+      </c>
+      <c r="D16" s="9">
+        <v>60</v>
+      </c>
+      <c r="E16" s="9">
+        <v>20</v>
+      </c>
+      <c r="F16" s="9">
+        <v>250</v>
+      </c>
+      <c r="G16" s="9">
+        <v>5</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>680</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>760</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>46262</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+      <c r="B17" s="9">
+        <v>480</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>30</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>480</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>990</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="18">
         <v>46263</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+      <c r="B18" s="9">
+        <v>360</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>30</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>60</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>450</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>990</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>46264</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+      <c r="B19" s="9">
+        <v>360</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>60</v>
+      </c>
+      <c r="E19" s="9">
+        <v>20</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>60</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>500</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
+        <v>940</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="18">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="9">
+        <v>240</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>180</v>
+      </c>
+      <c r="E20" s="9">
+        <v>60</v>
+      </c>
+      <c r="F20" s="9">
+        <v>300</v>
+      </c>
+      <c r="G20" s="9">
+        <v>5</v>
+      </c>
+      <c r="H20" s="9">
+        <v>60</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>840</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+        <v>600</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="9">
+        <v>300</v>
+      </c>
+      <c r="C21" s="9">
+        <v>50</v>
+      </c>
+      <c r="D21" s="9">
+        <v>120</v>
+      </c>
+      <c r="E21" s="9">
+        <v>30</v>
+      </c>
+      <c r="F21" s="9">
+        <v>150</v>
+      </c>
+      <c r="G21" s="9">
+        <v>3</v>
+      </c>
+      <c r="H21" s="9">
+        <v>60</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>710</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+        <v>730</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="9">
+        <v>300</v>
+      </c>
+      <c r="C22" s="9">
+        <v>50</v>
+      </c>
+      <c r="D22" s="9">
+        <v>180</v>
+      </c>
+      <c r="E22" s="9">
+        <v>60</v>
+      </c>
+      <c r="F22" s="9">
+        <v>400</v>
+      </c>
+      <c r="G22" s="9">
+        <v>8</v>
+      </c>
+      <c r="H22" s="9">
+        <v>30</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
+        <v>420</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="9">
+        <v>300</v>
+      </c>
+      <c r="C23" s="9">
+        <v>50</v>
+      </c>
+      <c r="D23" s="9">
+        <v>180</v>
+      </c>
+      <c r="E23" s="9">
+        <v>30</v>
+      </c>
+      <c r="F23" s="9">
+        <v>250</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5</v>
+      </c>
+      <c r="H23" s="9">
+        <v>120</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>930</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
+        <v>510</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="9">
+        <v>360</v>
+      </c>
+      <c r="C24" s="9">
+        <v>50</v>
+      </c>
+      <c r="D24" s="9">
+        <v>180</v>
+      </c>
+      <c r="E24" s="9">
+        <v>60</v>
+      </c>
+      <c r="F24" s="9">
+        <v>300</v>
+      </c>
+      <c r="G24" s="9">
+        <v>5</v>
+      </c>
+      <c r="H24" s="9">
+        <v>120</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
+        <v>370</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="9">
+        <v>360</v>
+      </c>
+      <c r="C25" s="9">
+        <v>30</v>
+      </c>
+      <c r="D25" s="9">
+        <v>120</v>
+      </c>
+      <c r="E25" s="9">
+        <v>30</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>120</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>660</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
+        <v>780</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
+      <c r="A26" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="9">
+        <v>480</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>60</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>120</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>660</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
+        <v>780</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="9">
+        <v>480</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
+        <v>180</v>
+      </c>
+      <c r="E27" s="9">
+        <v>60</v>
+      </c>
+      <c r="F27" s="9">
+        <v>200</v>
+      </c>
+      <c r="G27" s="9">
+        <v>4</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
+        <v>920</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
+        <v>520</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
+      <c r="A28" s="8">
+        <v>46273</v>
+      </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -1583,7 +2108,9 @@
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
+      <c r="A29" s="8">
+        <v>46274</v>
+      </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -1605,7 +2132,9 @@
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
+      <c r="A30" s="8">
+        <v>46275</v>
+      </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -1627,7 +2156,9 @@
       <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
+      <c r="A31" s="8">
+        <v>46276</v>
+      </c>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -1649,7 +2180,9 @@
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
+      <c r="A32" s="8">
+        <v>46277</v>
+      </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -1671,7 +2204,9 @@
       <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
+      <c r="A33" s="8">
+        <v>46278</v>
+      </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -1693,7 +2228,9 @@
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
+      <c r="A34" s="8">
+        <v>46279</v>
+      </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -1715,7 +2252,9 @@
       <c r="N34" s="12"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
+      <c r="A35" s="8">
+        <v>46280</v>
+      </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -1737,7 +2276,9 @@
       <c r="N35" s="12"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
+      <c r="A36" s="8">
+        <v>46281</v>
+      </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -1759,7 +2300,9 @@
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
+      <c r="A37" s="8">
+        <v>46282</v>
+      </c>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -1781,7 +2324,9 @@
       <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
+      <c r="A38" s="8">
+        <v>46283</v>
+      </c>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -1803,7 +2348,9 @@
       <c r="N38" s="12"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
+      <c r="A39" s="8">
+        <v>46284</v>
+      </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -1825,7 +2372,9 @@
       <c r="N39" s="12"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
+      <c r="A40" s="8">
+        <v>46285</v>
+      </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -1847,7 +2396,9 @@
       <c r="N40" s="12"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
+      <c r="A41" s="8">
+        <v>46286</v>
+      </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -1869,7 +2420,9 @@
       <c r="N41" s="12"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
+      <c r="A42" s="8">
+        <v>46287</v>
+      </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -1891,7 +2444,9 @@
       <c r="N42" s="12"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
+      <c r="A43" s="8">
+        <v>46288</v>
+      </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -1913,7 +2468,9 @@
       <c r="N43" s="12"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
+      <c r="A44" s="8">
+        <v>46289</v>
+      </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
@@ -1935,7 +2492,9 @@
       <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
+      <c r="A45" s="8">
+        <v>46290</v>
+      </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
@@ -1957,7 +2516,9 @@
       <c r="N45" s="12"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
+      <c r="A46" s="8">
+        <v>46291</v>
+      </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
@@ -1979,7 +2540,9 @@
       <c r="N46" s="12"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
+      <c r="A47" s="8">
+        <v>46292</v>
+      </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
@@ -2001,7 +2564,9 @@
       <c r="N47" s="12"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
+      <c r="A48" s="8">
+        <v>46293</v>
+      </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
@@ -2023,7 +2588,9 @@
       <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
+      <c r="A49" s="8">
+        <v>46294</v>
+      </c>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
@@ -2045,7 +2612,9 @@
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
+      <c r="A50" s="8">
+        <v>46295</v>
+      </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CB9BBC-85A9-4ED5-A911-360DF8659758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A232FA8D-B667-45BF-8ADD-20CD3D5CB6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2087,20 +2087,24 @@
       <c r="A28" s="8">
         <v>46273</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="B28" s="9">
+        <v>360</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A232FA8D-B667-45BF-8ADD-20CD3D5CB6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B036C2-0F34-4333-B599-BDD0E1A7E5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,15 @@
   <si>
     <t>Last day of the weekend,looking at the watch,let all classes ends and I go to the hostel and enjoy football.</t>
   </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Today I had 2nd football of the fresher league. I gave my 100%. But in the evening English CA's marks were uploaded and I am unsatisfied with the evaluation.</t>
+  </si>
+  <si>
+    <t>I had DBMS viva,it was good.I discussed about the evaluation of english CA, but she has'nt genuine feedback. Also we had fresher's party, I enjoyed a lot,danced and ate every thing available and it helped me relieve.</t>
+  </si>
 </sst>
 </file>
 
@@ -292,7 +301,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -753,186 +762,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="22.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="16.8">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1">
       <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -944,7 +953,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22.109375" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
@@ -959,7 +968,7 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1">
       <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
@@ -977,7 +986,7 @@
       <c r="M1" s="20"/>
       <c r="N1" s="20"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="19.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -994,7 +1003,7 @@
       </c>
       <c r="G2" s="22"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="19.5" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -1011,7 +1020,7 @@
       </c>
       <c r="G3" s="21"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14">
       <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
@@ -1029,7 +1038,7 @@
       <c r="M4" s="19"/>
       <c r="N4" s="19"/>
     </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="41.4">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1073,7 +1082,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="13" customFormat="1" ht="43.2">
       <c r="A6" s="18">
         <v>46251</v>
       </c>
@@ -1119,7 +1128,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="57.6">
       <c r="A7" s="18">
         <v>46252</v>
       </c>
@@ -1165,7 +1174,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14">
       <c r="A8" s="18">
         <v>46253</v>
       </c>
@@ -1209,7 +1218,7 @@
       </c>
       <c r="N8" s="12"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14">
       <c r="A9" s="18">
         <v>46254</v>
       </c>
@@ -1255,7 +1264,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="57.6">
       <c r="A10" s="18">
         <v>46255</v>
       </c>
@@ -1301,7 +1310,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="57.6">
       <c r="A11" s="18">
         <v>46256</v>
       </c>
@@ -1347,7 +1356,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="18">
         <v>46257</v>
       </c>
@@ -1393,7 +1402,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="43.2">
       <c r="A13" s="18">
         <v>46258</v>
       </c>
@@ -1439,7 +1448,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="72">
       <c r="A14" s="18">
         <v>46259</v>
       </c>
@@ -1485,7 +1494,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="72">
       <c r="A15" s="18">
         <v>46260</v>
       </c>
@@ -1531,7 +1540,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="72">
       <c r="A16" s="18">
         <v>46261</v>
       </c>
@@ -1577,7 +1586,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="86.4">
       <c r="A17" s="18">
         <v>46262</v>
       </c>
@@ -1623,7 +1632,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="72">
       <c r="A18" s="18">
         <v>46263</v>
       </c>
@@ -1669,7 +1678,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14">
       <c r="A19" s="18">
         <v>46264</v>
       </c>
@@ -1715,7 +1724,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="57.6">
       <c r="A20" s="18">
         <v>46265</v>
       </c>
@@ -1761,7 +1770,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="43.2">
       <c r="A21" s="8">
         <v>46266</v>
       </c>
@@ -1807,7 +1816,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="57.6">
       <c r="A22" s="8">
         <v>46267</v>
       </c>
@@ -1853,7 +1862,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="86.4">
       <c r="A23" s="8">
         <v>46268</v>
       </c>
@@ -1899,7 +1908,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="43.2">
       <c r="A24" s="8">
         <v>46269</v>
       </c>
@@ -1945,7 +1954,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="57.6">
       <c r="A25" s="8">
         <v>46270</v>
       </c>
@@ -1991,7 +2000,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14">
       <c r="A26" s="8">
         <v>46271</v>
       </c>
@@ -2037,7 +2046,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="72">
       <c r="A27" s="8">
         <v>46272</v>
       </c>
@@ -2083,7 +2092,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14">
       <c r="A28" s="8">
         <v>46273</v>
       </c>
@@ -2093,73 +2102,133 @@
       <c r="C28" s="9">
         <v>0</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
+      <c r="D28" s="9">
+        <v>120</v>
+      </c>
+      <c r="E28" s="9">
+        <v>30</v>
+      </c>
+      <c r="F28" s="9">
+        <v>150</v>
+      </c>
+      <c r="G28" s="9">
+        <v>3</v>
+      </c>
+      <c r="H28" s="9">
+        <v>60</v>
+      </c>
       <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v>1080</v>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
+        <v>720</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="12"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="72">
       <c r="A29" s="8">
         <v>46274</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+      <c r="B29" s="9">
+        <v>360</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>120</v>
+      </c>
+      <c r="E29" s="9">
+        <v>30</v>
+      </c>
+      <c r="F29" s="9">
+        <v>400</v>
+      </c>
+      <c r="G29" s="9">
+        <v>8</v>
+      </c>
+      <c r="H29" s="9">
+        <v>180</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="115.2">
       <c r="A30" s="8">
         <v>46275</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+      <c r="B30" s="9">
+        <v>420</v>
+      </c>
+      <c r="C30" s="9">
+        <v>60</v>
+      </c>
+      <c r="D30" s="9">
+        <v>120</v>
+      </c>
+      <c r="E30" s="9">
+        <v>60</v>
+      </c>
+      <c r="F30" s="9">
+        <v>150</v>
+      </c>
+      <c r="G30" s="9">
+        <v>3</v>
+      </c>
+      <c r="H30" s="9">
+        <v>180</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>990</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="8">
         <v>46276</v>
       </c>
@@ -2183,7 +2252,7 @@
       <c r="M31" s="11"/>
       <c r="N31" s="12"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14">
       <c r="A32" s="8">
         <v>46277</v>
       </c>
@@ -2207,7 +2276,7 @@
       <c r="M32" s="11"/>
       <c r="N32" s="12"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14">
       <c r="A33" s="8">
         <v>46278</v>
       </c>
@@ -2231,7 +2300,7 @@
       <c r="M33" s="11"/>
       <c r="N33" s="12"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14">
       <c r="A34" s="8">
         <v>46279</v>
       </c>
@@ -2255,7 +2324,7 @@
       <c r="M34" s="11"/>
       <c r="N34" s="12"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14">
       <c r="A35" s="8">
         <v>46280</v>
       </c>
@@ -2279,7 +2348,7 @@
       <c r="M35" s="11"/>
       <c r="N35" s="12"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14">
       <c r="A36" s="8">
         <v>46281</v>
       </c>
@@ -2303,7 +2372,7 @@
       <c r="M36" s="11"/>
       <c r="N36" s="12"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14">
       <c r="A37" s="8">
         <v>46282</v>
       </c>
@@ -2327,7 +2396,7 @@
       <c r="M37" s="11"/>
       <c r="N37" s="12"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14">
       <c r="A38" s="8">
         <v>46283</v>
       </c>
@@ -2351,7 +2420,7 @@
       <c r="M38" s="11"/>
       <c r="N38" s="12"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14">
       <c r="A39" s="8">
         <v>46284</v>
       </c>
@@ -2375,7 +2444,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="12"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14">
       <c r="A40" s="8">
         <v>46285</v>
       </c>
@@ -2399,7 +2468,7 @@
       <c r="M40" s="11"/>
       <c r="N40" s="12"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14">
       <c r="A41" s="8">
         <v>46286</v>
       </c>
@@ -2423,7 +2492,7 @@
       <c r="M41" s="11"/>
       <c r="N41" s="12"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14">
       <c r="A42" s="8">
         <v>46287</v>
       </c>
@@ -2447,7 +2516,7 @@
       <c r="M42" s="11"/>
       <c r="N42" s="12"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14">
       <c r="A43" s="8">
         <v>46288</v>
       </c>
@@ -2471,7 +2540,7 @@
       <c r="M43" s="11"/>
       <c r="N43" s="12"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14">
       <c r="A44" s="8">
         <v>46289</v>
       </c>
@@ -2495,7 +2564,7 @@
       <c r="M44" s="11"/>
       <c r="N44" s="12"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14">
       <c r="A45" s="8">
         <v>46290</v>
       </c>
@@ -2519,7 +2588,7 @@
       <c r="M45" s="11"/>
       <c r="N45" s="12"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14">
       <c r="A46" s="8">
         <v>46291</v>
       </c>
@@ -2543,7 +2612,7 @@
       <c r="M46" s="11"/>
       <c r="N46" s="12"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14">
       <c r="A47" s="8">
         <v>46292</v>
       </c>
@@ -2567,7 +2636,7 @@
       <c r="M47" s="11"/>
       <c r="N47" s="12"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14">
       <c r="A48" s="8">
         <v>46293</v>
       </c>
@@ -2591,7 +2660,7 @@
       <c r="M48" s="11"/>
       <c r="N48" s="12"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14">
       <c r="A49" s="8">
         <v>46294</v>
       </c>
@@ -2615,7 +2684,7 @@
       <c r="M49" s="11"/>
       <c r="N49" s="12"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14">
       <c r="A50" s="8">
         <v>46295</v>
       </c>
@@ -2639,7 +2708,7 @@
       <c r="M50" s="11"/>
       <c r="N50" s="12"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14">
       <c r="A51" s="8"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -2661,7 +2730,7 @@
       <c r="M51" s="11"/>
       <c r="N51" s="12"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14">
       <c r="A52" s="8"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -2683,7 +2752,7 @@
       <c r="M52" s="11"/>
       <c r="N52" s="12"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14">
       <c r="A53" s="8"/>
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
@@ -2705,7 +2774,7 @@
       <c r="M53" s="11"/>
       <c r="N53" s="12"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14">
       <c r="A54" s="8"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
@@ -2727,7 +2796,7 @@
       <c r="M54" s="11"/>
       <c r="N54" s="12"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14">
       <c r="A55" s="8"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -2749,7 +2818,7 @@
       <c r="M55" s="11"/>
       <c r="N55" s="12"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14">
       <c r="A56" s="8"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -2771,7 +2840,7 @@
       <c r="M56" s="11"/>
       <c r="N56" s="12"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14">
       <c r="A57" s="8"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -2793,7 +2862,7 @@
       <c r="M57" s="11"/>
       <c r="N57" s="12"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14">
       <c r="A58" s="8"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -2815,7 +2884,7 @@
       <c r="M58" s="11"/>
       <c r="N58" s="12"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14">
       <c r="A59" s="8"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
@@ -2837,7 +2906,7 @@
       <c r="M59" s="11"/>
       <c r="N59" s="12"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14">
       <c r="A60" s="8"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -2859,7 +2928,7 @@
       <c r="M60" s="11"/>
       <c r="N60" s="12"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14">
       <c r="A61" s="8"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
@@ -2881,7 +2950,7 @@
       <c r="M61" s="11"/>
       <c r="N61" s="12"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14">
       <c r="A62" s="8"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
@@ -2903,7 +2972,7 @@
       <c r="M62" s="11"/>
       <c r="N62" s="12"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -2925,7 +2994,7 @@
       <c r="M63" s="11"/>
       <c r="N63" s="12"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14">
       <c r="A64" s="8"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
@@ -2947,7 +3016,7 @@
       <c r="M64" s="11"/>
       <c r="N64" s="12"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14">
       <c r="A65" s="8"/>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
@@ -2969,7 +3038,7 @@
       <c r="M65" s="11"/>
       <c r="N65" s="12"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14">
       <c r="A66" s="8"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -2991,7 +3060,7 @@
       <c r="M66" s="11"/>
       <c r="N66" s="12"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14">
       <c r="A67" s="8"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -3013,7 +3082,7 @@
       <c r="M67" s="11"/>
       <c r="N67" s="12"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14">
       <c r="A68" s="8"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
@@ -3035,7 +3104,7 @@
       <c r="M68" s="11"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14">
       <c r="A69" s="8"/>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
@@ -3057,7 +3126,7 @@
       <c r="M69" s="11"/>
       <c r="N69" s="12"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14">
       <c r="A70" s="8"/>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
@@ -3079,7 +3148,7 @@
       <c r="M70" s="11"/>
       <c r="N70" s="12"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14">
       <c r="A71" s="8"/>
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
@@ -3101,7 +3170,7 @@
       <c r="M71" s="11"/>
       <c r="N71" s="12"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14">
       <c r="A72" s="8"/>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
@@ -3123,7 +3192,7 @@
       <c r="M72" s="11"/>
       <c r="N72" s="12"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14">
       <c r="A73" s="8"/>
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
@@ -3145,7 +3214,7 @@
       <c r="M73" s="11"/>
       <c r="N73" s="12"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14">
       <c r="A74" s="8"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
@@ -3167,7 +3236,7 @@
       <c r="M74" s="11"/>
       <c r="N74" s="12"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14">
       <c r="A75" s="8"/>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
@@ -3189,7 +3258,7 @@
       <c r="M75" s="11"/>
       <c r="N75" s="12"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14">
       <c r="A76" s="8"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
@@ -3211,7 +3280,7 @@
       <c r="M76" s="11"/>
       <c r="N76" s="12"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14">
       <c r="A77" s="8"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
@@ -3233,7 +3302,7 @@
       <c r="M77" s="11"/>
       <c r="N77" s="12"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14">
       <c r="A78" s="8"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
@@ -3255,7 +3324,7 @@
       <c r="M78" s="11"/>
       <c r="N78" s="12"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14">
       <c r="A79" s="8"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
@@ -3277,7 +3346,7 @@
       <c r="M79" s="11"/>
       <c r="N79" s="12"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14">
       <c r="A80" s="8"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
@@ -3299,7 +3368,7 @@
       <c r="M80" s="11"/>
       <c r="N80" s="12"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14">
       <c r="A81" s="8"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
@@ -3321,7 +3390,7 @@
       <c r="M81" s="11"/>
       <c r="N81" s="12"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14">
       <c r="A82" s="8"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
@@ -3343,7 +3412,7 @@
       <c r="M82" s="11"/>
       <c r="N82" s="12"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14">
       <c r="A83" s="8"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
@@ -3365,7 +3434,7 @@
       <c r="M83" s="11"/>
       <c r="N83" s="12"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14">
       <c r="A84" s="8"/>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
@@ -3387,7 +3456,7 @@
       <c r="M84" s="11"/>
       <c r="N84" s="12"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14">
       <c r="A85" s="8"/>
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
@@ -3409,7 +3478,7 @@
       <c r="M85" s="11"/>
       <c r="N85" s="12"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14">
       <c r="A86" s="8"/>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
@@ -3431,7 +3500,7 @@
       <c r="M86" s="11"/>
       <c r="N86" s="12"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14">
       <c r="A87" s="8"/>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
@@ -3453,7 +3522,7 @@
       <c r="M87" s="11"/>
       <c r="N87" s="12"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14">
       <c r="A88" s="8"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
@@ -3475,7 +3544,7 @@
       <c r="M88" s="11"/>
       <c r="N88" s="12"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14">
       <c r="A89" s="8"/>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
@@ -3497,7 +3566,7 @@
       <c r="M89" s="11"/>
       <c r="N89" s="12"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14">
       <c r="A90" s="8"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
@@ -3519,7 +3588,7 @@
       <c r="M90" s="11"/>
       <c r="N90" s="12"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14">
       <c r="A91" s="8"/>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
@@ -3541,7 +3610,7 @@
       <c r="M91" s="11"/>
       <c r="N91" s="12"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14">
       <c r="A92" s="8"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
@@ -3563,7 +3632,7 @@
       <c r="M92" s="11"/>
       <c r="N92" s="12"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14">
       <c r="A93" s="8"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
@@ -3585,7 +3654,7 @@
       <c r="M93" s="11"/>
       <c r="N93" s="12"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14">
       <c r="A94" s="8"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
@@ -3607,7 +3676,7 @@
       <c r="M94" s="11"/>
       <c r="N94" s="12"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14">
       <c r="A95" s="8"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
@@ -3629,7 +3698,7 @@
       <c r="M95" s="11"/>
       <c r="N95" s="12"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14">
       <c r="A96" s="8"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
@@ -3651,7 +3720,7 @@
       <c r="M96" s="11"/>
       <c r="N96" s="12"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14">
       <c r="A97" s="8"/>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
@@ -3673,7 +3742,7 @@
       <c r="M97" s="11"/>
       <c r="N97" s="12"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14">
       <c r="A98" s="8"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
@@ -3695,7 +3764,7 @@
       <c r="M98" s="11"/>
       <c r="N98" s="12"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14">
       <c r="A99" s="8"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
@@ -3717,7 +3786,7 @@
       <c r="M99" s="11"/>
       <c r="N99" s="12"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14">
       <c r="A100" s="8"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
@@ -3739,7 +3808,7 @@
       <c r="M100" s="11"/>
       <c r="N100" s="12"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14">
       <c r="A101" s="8"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
@@ -3761,7 +3830,7 @@
       <c r="M101" s="11"/>
       <c r="N101" s="12"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14">
       <c r="A102" s="8"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
@@ -3783,7 +3852,7 @@
       <c r="M102" s="11"/>
       <c r="N102" s="12"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14">
       <c r="A103" s="8"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
@@ -3805,7 +3874,7 @@
       <c r="M103" s="11"/>
       <c r="N103" s="12"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14">
       <c r="A104" s="8"/>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
@@ -3827,7 +3896,7 @@
       <c r="M104" s="11"/>
       <c r="N104" s="12"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14">
       <c r="A105" s="8"/>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
@@ -3849,7 +3918,7 @@
       <c r="M105" s="11"/>
       <c r="N105" s="12"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14">
       <c r="A106" s="8"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
@@ -3871,7 +3940,7 @@
       <c r="M106" s="11"/>
       <c r="N106" s="12"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14">
       <c r="A107" s="8"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
@@ -3893,7 +3962,7 @@
       <c r="M107" s="11"/>
       <c r="N107" s="12"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14">
       <c r="A108" s="8"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
@@ -3915,7 +3984,7 @@
       <c r="M108" s="11"/>
       <c r="N108" s="12"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14">
       <c r="A109" s="8"/>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
@@ -3937,7 +4006,7 @@
       <c r="M109" s="11"/>
       <c r="N109" s="12"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14">
       <c r="A110" s="8"/>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
@@ -3959,7 +4028,7 @@
       <c r="M110" s="11"/>
       <c r="N110" s="12"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14">
       <c r="A111" s="8"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
@@ -3981,7 +4050,7 @@
       <c r="M111" s="11"/>
       <c r="N111" s="12"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14">
       <c r="A112" s="8"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
@@ -4003,7 +4072,7 @@
       <c r="M112" s="11"/>
       <c r="N112" s="12"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14">
       <c r="A113" s="8"/>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
@@ -4025,7 +4094,7 @@
       <c r="M113" s="11"/>
       <c r="N113" s="12"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14">
       <c r="A114" s="8"/>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
@@ -4047,7 +4116,7 @@
       <c r="M114" s="11"/>
       <c r="N114" s="12"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14">
       <c r="A115" s="8"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
@@ -4069,7 +4138,7 @@
       <c r="M115" s="11"/>
       <c r="N115" s="12"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14">
       <c r="A116" s="8"/>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
@@ -4091,7 +4160,7 @@
       <c r="M116" s="11"/>
       <c r="N116" s="12"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14">
       <c r="A117" s="8"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
@@ -4113,7 +4182,7 @@
       <c r="M117" s="11"/>
       <c r="N117" s="12"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14">
       <c r="A118" s="8"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
@@ -4135,7 +4204,7 @@
       <c r="M118" s="11"/>
       <c r="N118" s="12"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14">
       <c r="A119" s="8"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
@@ -4157,7 +4226,7 @@
       <c r="M119" s="11"/>
       <c r="N119" s="12"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14">
       <c r="A120" s="8"/>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
@@ -4179,7 +4248,7 @@
       <c r="M120" s="11"/>
       <c r="N120" s="12"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14">
       <c r="A121" s="8"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
@@ -4201,7 +4270,7 @@
       <c r="M121" s="11"/>
       <c r="N121" s="12"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14">
       <c r="A122" s="8"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
@@ -4223,7 +4292,7 @@
       <c r="M122" s="11"/>
       <c r="N122" s="12"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14">
       <c r="A123" s="8"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
@@ -4245,7 +4314,7 @@
       <c r="M123" s="11"/>
       <c r="N123" s="12"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14">
       <c r="A124" s="8"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
@@ -4267,7 +4336,7 @@
       <c r="M124" s="11"/>
       <c r="N124" s="12"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14">
       <c r="A125" s="8"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
@@ -4289,7 +4358,7 @@
       <c r="M125" s="11"/>
       <c r="N125" s="12"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14">
       <c r="A126" s="8"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
@@ -4311,7 +4380,7 @@
       <c r="M126" s="11"/>
       <c r="N126" s="12"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14">
       <c r="A127" s="8"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
@@ -4333,7 +4402,7 @@
       <c r="M127" s="11"/>
       <c r="N127" s="12"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14">
       <c r="A128" s="8"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
@@ -4355,7 +4424,7 @@
       <c r="M128" s="11"/>
       <c r="N128" s="12"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14">
       <c r="A129" s="8"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -4377,7 +4446,7 @@
       <c r="M129" s="11"/>
       <c r="N129" s="12"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14">
       <c r="A130" s="8"/>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
@@ -4399,7 +4468,7 @@
       <c r="M130" s="11"/>
       <c r="N130" s="12"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14">
       <c r="A131" s="8"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
@@ -4421,7 +4490,7 @@
       <c r="M131" s="11"/>
       <c r="N131" s="12"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14">
       <c r="A132" s="8"/>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
@@ -4443,7 +4512,7 @@
       <c r="M132" s="11"/>
       <c r="N132" s="12"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14">
       <c r="A133" s="8"/>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
@@ -4465,7 +4534,7 @@
       <c r="M133" s="11"/>
       <c r="N133" s="12"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14">
       <c r="A134" s="8"/>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
@@ -4487,7 +4556,7 @@
       <c r="M134" s="11"/>
       <c r="N134" s="12"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14">
       <c r="A135" s="8"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
@@ -4509,7 +4578,7 @@
       <c r="M135" s="11"/>
       <c r="N135" s="12"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14">
       <c r="A136" s="8"/>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
@@ -4531,7 +4600,7 @@
       <c r="M136" s="11"/>
       <c r="N136" s="12"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14">
       <c r="A137" s="8"/>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
@@ -4553,7 +4622,7 @@
       <c r="M137" s="11"/>
       <c r="N137" s="12"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14">
       <c r="A138" s="8"/>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
@@ -4575,7 +4644,7 @@
       <c r="M138" s="11"/>
       <c r="N138" s="12"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14">
       <c r="A139" s="8"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
@@ -4597,7 +4666,7 @@
       <c r="M139" s="11"/>
       <c r="N139" s="12"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14">
       <c r="A140" s="8"/>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
@@ -4619,7 +4688,7 @@
       <c r="M140" s="11"/>
       <c r="N140" s="12"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14">
       <c r="A141" s="8"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
@@ -4641,7 +4710,7 @@
       <c r="M141" s="11"/>
       <c r="N141" s="12"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14">
       <c r="A142" s="8"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
@@ -4663,7 +4732,7 @@
       <c r="M142" s="11"/>
       <c r="N142" s="12"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14">
       <c r="A143" s="8"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
@@ -4685,7 +4754,7 @@
       <c r="M143" s="11"/>
       <c r="N143" s="12"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14">
       <c r="A144" s="8"/>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
@@ -4707,7 +4776,7 @@
       <c r="M144" s="11"/>
       <c r="N144" s="12"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14">
       <c r="A145" s="8"/>
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
@@ -4729,7 +4798,7 @@
       <c r="M145" s="11"/>
       <c r="N145" s="12"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14">
       <c r="A146" s="8"/>
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
@@ -4751,7 +4820,7 @@
       <c r="M146" s="11"/>
       <c r="N146" s="12"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14">
       <c r="A147" s="8"/>
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
@@ -4773,7 +4842,7 @@
       <c r="M147" s="11"/>
       <c r="N147" s="12"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14">
       <c r="A148" s="8"/>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
@@ -4795,7 +4864,7 @@
       <c r="M148" s="11"/>
       <c r="N148" s="12"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14">
       <c r="A149" s="8"/>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
@@ -4817,7 +4886,7 @@
       <c r="M149" s="11"/>
       <c r="N149" s="12"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14">
       <c r="A150" s="8"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
@@ -4839,7 +4908,7 @@
       <c r="M150" s="11"/>
       <c r="N150" s="12"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14">
       <c r="A151" s="8"/>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
@@ -4861,7 +4930,7 @@
       <c r="M151" s="11"/>
       <c r="N151" s="12"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14">
       <c r="A152" s="8"/>
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
@@ -4883,7 +4952,7 @@
       <c r="M152" s="11"/>
       <c r="N152" s="12"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14">
       <c r="A153" s="8"/>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
@@ -4905,7 +4974,7 @@
       <c r="M153" s="11"/>
       <c r="N153" s="12"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14">
       <c r="A154" s="8"/>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
@@ -4927,7 +4996,7 @@
       <c r="M154" s="11"/>
       <c r="N154" s="12"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14">
       <c r="A155" s="8"/>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
@@ -4949,7 +5018,7 @@
       <c r="M155" s="11"/>
       <c r="N155" s="12"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14">
       <c r="A156" s="8"/>
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
@@ -4971,7 +5040,7 @@
       <c r="M156" s="11"/>
       <c r="N156" s="12"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14">
       <c r="A157" s="8"/>
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
@@ -4993,7 +5062,7 @@
       <c r="M157" s="11"/>
       <c r="N157" s="12"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14">
       <c r="A158" s="8"/>
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
@@ -5015,7 +5084,7 @@
       <c r="M158" s="11"/>
       <c r="N158" s="12"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14">
       <c r="A159" s="8"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
@@ -5037,7 +5106,7 @@
       <c r="M159" s="11"/>
       <c r="N159" s="12"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14">
       <c r="A160" s="8"/>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
@@ -5059,7 +5128,7 @@
       <c r="M160" s="11"/>
       <c r="N160" s="12"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14">
       <c r="A161" s="8"/>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
@@ -5081,7 +5150,7 @@
       <c r="M161" s="11"/>
       <c r="N161" s="12"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14">
       <c r="A162" s="8"/>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
@@ -5103,7 +5172,7 @@
       <c r="M162" s="11"/>
       <c r="N162" s="12"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14">
       <c r="A163" s="8"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
@@ -5125,7 +5194,7 @@
       <c r="M163" s="11"/>
       <c r="N163" s="12"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14">
       <c r="A164" s="8"/>
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
@@ -5147,7 +5216,7 @@
       <c r="M164" s="11"/>
       <c r="N164" s="12"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:14">
       <c r="A165" s="8"/>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
@@ -5169,7 +5238,7 @@
       <c r="M165" s="11"/>
       <c r="N165" s="12"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:14">
       <c r="A166" s="8"/>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
@@ -5191,7 +5260,7 @@
       <c r="M166" s="11"/>
       <c r="N166" s="12"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14">
       <c r="A167" s="8"/>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
@@ -5213,7 +5282,7 @@
       <c r="M167" s="11"/>
       <c r="N167" s="12"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:14">
       <c r="A168" s="8"/>
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
@@ -5235,7 +5304,7 @@
       <c r="M168" s="11"/>
       <c r="N168" s="12"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14">
       <c r="A169" s="8"/>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
@@ -5257,7 +5326,7 @@
       <c r="M169" s="11"/>
       <c r="N169" s="12"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14">
       <c r="A170" s="8"/>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
@@ -5279,7 +5348,7 @@
       <c r="M170" s="11"/>
       <c r="N170" s="12"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14">
       <c r="A171" s="8"/>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
@@ -5301,7 +5370,7 @@
       <c r="M171" s="11"/>
       <c r="N171" s="12"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14">
       <c r="A172" s="8"/>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
@@ -5323,7 +5392,7 @@
       <c r="M172" s="11"/>
       <c r="N172" s="12"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14">
       <c r="A173" s="8"/>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
@@ -5345,7 +5414,7 @@
       <c r="M173" s="11"/>
       <c r="N173" s="12"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14">
       <c r="A174" s="8"/>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
@@ -5367,7 +5436,7 @@
       <c r="M174" s="11"/>
       <c r="N174" s="12"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14">
       <c r="A175" s="8"/>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
@@ -5389,7 +5458,7 @@
       <c r="M175" s="11"/>
       <c r="N175" s="12"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14">
       <c r="A176" s="8"/>
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
@@ -5411,7 +5480,7 @@
       <c r="M176" s="11"/>
       <c r="N176" s="12"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14">
       <c r="A177" s="8"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
@@ -5433,7 +5502,7 @@
       <c r="M177" s="11"/>
       <c r="N177" s="12"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14">
       <c r="A178" s="8"/>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
@@ -5455,7 +5524,7 @@
       <c r="M178" s="11"/>
       <c r="N178" s="12"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14">
       <c r="A179" s="8"/>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
@@ -5477,7 +5546,7 @@
       <c r="M179" s="11"/>
       <c r="N179" s="12"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14">
       <c r="A180" s="8"/>
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
@@ -5499,7 +5568,7 @@
       <c r="M180" s="11"/>
       <c r="N180" s="12"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14">
       <c r="A181" s="8"/>
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
@@ -5521,7 +5590,7 @@
       <c r="M181" s="11"/>
       <c r="N181" s="12"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14">
       <c r="A182" s="8"/>
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
@@ -5543,7 +5612,7 @@
       <c r="M182" s="11"/>
       <c r="N182" s="12"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14">
       <c r="A183" s="8"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
@@ -5565,7 +5634,7 @@
       <c r="M183" s="11"/>
       <c r="N183" s="12"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14">
       <c r="A184" s="8"/>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
@@ -5587,7 +5656,7 @@
       <c r="M184" s="11"/>
       <c r="N184" s="12"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14">
       <c r="A185" s="8"/>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
@@ -5609,7 +5678,7 @@
       <c r="M185" s="11"/>
       <c r="N185" s="12"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14">
       <c r="A186" s="8"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
@@ -5631,7 +5700,7 @@
       <c r="M186" s="11"/>
       <c r="N186" s="12"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14">
       <c r="A187" s="8"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
@@ -5653,7 +5722,7 @@
       <c r="M187" s="11"/>
       <c r="N187" s="12"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:14">
       <c r="A188" s="8"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
@@ -5675,7 +5744,7 @@
       <c r="M188" s="11"/>
       <c r="N188" s="12"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:14">
       <c r="A189" s="8"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
@@ -5697,7 +5766,7 @@
       <c r="M189" s="11"/>
       <c r="N189" s="12"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:14">
       <c r="A190" s="8"/>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
@@ -5719,7 +5788,7 @@
       <c r="M190" s="11"/>
       <c r="N190" s="12"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:14">
       <c r="A191" s="8"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
@@ -5741,7 +5810,7 @@
       <c r="M191" s="11"/>
       <c r="N191" s="12"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:14">
       <c r="A192" s="8"/>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
@@ -5763,7 +5832,7 @@
       <c r="M192" s="11"/>
       <c r="N192" s="12"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:14">
       <c r="A193" s="8"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
@@ -5785,7 +5854,7 @@
       <c r="M193" s="11"/>
       <c r="N193" s="12"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:14">
       <c r="A194" s="8"/>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
@@ -5807,7 +5876,7 @@
       <c r="M194" s="11"/>
       <c r="N194" s="12"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:14">
       <c r="A195" s="8"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
@@ -5829,7 +5898,7 @@
       <c r="M195" s="11"/>
       <c r="N195" s="12"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14">
       <c r="A196" s="8"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
@@ -5851,7 +5920,7 @@
       <c r="M196" s="11"/>
       <c r="N196" s="12"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14">
       <c r="A197" s="8"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
@@ -5873,7 +5942,7 @@
       <c r="M197" s="11"/>
       <c r="N197" s="12"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14">
       <c r="A198" s="8"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
@@ -5895,7 +5964,7 @@
       <c r="M198" s="11"/>
       <c r="N198" s="12"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:14">
       <c r="A199" s="8"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
@@ -5917,7 +5986,7 @@
       <c r="M199" s="11"/>
       <c r="N199" s="12"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:14">
       <c r="A200" s="8"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
@@ -5939,7 +6008,7 @@
       <c r="M200" s="11"/>
       <c r="N200" s="12"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14">
       <c r="A201" s="8"/>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
@@ -5961,7 +6030,7 @@
       <c r="M201" s="11"/>
       <c r="N201" s="12"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:14">
       <c r="A202" s="8"/>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
@@ -5983,7 +6052,7 @@
       <c r="M202" s="11"/>
       <c r="N202" s="12"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:14">
       <c r="A203" s="8"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
@@ -6005,7 +6074,7 @@
       <c r="M203" s="11"/>
       <c r="N203" s="12"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:14">
       <c r="A204" s="8"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
@@ -6027,7 +6096,7 @@
       <c r="M204" s="11"/>
       <c r="N204" s="12"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:14">
       <c r="A205" s="8"/>
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
@@ -6049,7 +6118,7 @@
       <c r="M205" s="11"/>
       <c r="N205" s="12"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:14">
       <c r="A206" s="8"/>
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
@@ -6071,7 +6140,7 @@
       <c r="M206" s="11"/>
       <c r="N206" s="12"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:14">
       <c r="A207" s="8"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
@@ -6093,7 +6162,7 @@
       <c r="M207" s="11"/>
       <c r="N207" s="12"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:14">
       <c r="A208" s="8"/>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
@@ -6115,7 +6184,7 @@
       <c r="M208" s="11"/>
       <c r="N208" s="12"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:14">
       <c r="A209" s="8"/>
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
@@ -6137,7 +6206,7 @@
       <c r="M209" s="11"/>
       <c r="N209" s="12"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:14">
       <c r="A210" s="8"/>
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
@@ -6159,7 +6228,7 @@
       <c r="M210" s="11"/>
       <c r="N210" s="12"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:14">
       <c r="A211" s="8"/>
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
@@ -6181,7 +6250,7 @@
       <c r="M211" s="11"/>
       <c r="N211" s="12"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:14">
       <c r="A212" s="8"/>
       <c r="B212" s="9"/>
       <c r="C212" s="9"/>
@@ -6203,7 +6272,7 @@
       <c r="M212" s="11"/>
       <c r="N212" s="12"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:14">
       <c r="A213" s="8"/>
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
@@ -6225,7 +6294,7 @@
       <c r="M213" s="11"/>
       <c r="N213" s="12"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:14">
       <c r="A214" s="8"/>
       <c r="B214" s="9"/>
       <c r="C214" s="9"/>
@@ -6247,7 +6316,7 @@
       <c r="M214" s="11"/>
       <c r="N214" s="12"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:14">
       <c r="A215" s="8"/>
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
@@ -6269,7 +6338,7 @@
       <c r="M215" s="11"/>
       <c r="N215" s="12"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:14">
       <c r="A216" s="8"/>
       <c r="B216" s="9"/>
       <c r="C216" s="9"/>
@@ -6291,7 +6360,7 @@
       <c r="M216" s="11"/>
       <c r="N216" s="12"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:14">
       <c r="A217" s="8"/>
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
@@ -6313,7 +6382,7 @@
       <c r="M217" s="11"/>
       <c r="N217" s="12"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:14">
       <c r="A218" s="8"/>
       <c r="B218" s="9"/>
       <c r="C218" s="9"/>
@@ -6335,7 +6404,7 @@
       <c r="M218" s="11"/>
       <c r="N218" s="12"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:14">
       <c r="A219" s="8"/>
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
@@ -6357,7 +6426,7 @@
       <c r="M219" s="11"/>
       <c r="N219" s="12"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:14">
       <c r="A220" s="8"/>
       <c r="B220" s="9"/>
       <c r="C220" s="9"/>
@@ -6379,7 +6448,7 @@
       <c r="M220" s="11"/>
       <c r="N220" s="12"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:14">
       <c r="A221" s="8"/>
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
@@ -6401,7 +6470,7 @@
       <c r="M221" s="11"/>
       <c r="N221" s="12"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:14">
       <c r="A222" s="8"/>
       <c r="B222" s="9"/>
       <c r="C222" s="9"/>
@@ -6423,7 +6492,7 @@
       <c r="M222" s="11"/>
       <c r="N222" s="12"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:14">
       <c r="A223" s="8"/>
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
@@ -6445,7 +6514,7 @@
       <c r="M223" s="11"/>
       <c r="N223" s="12"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:14">
       <c r="A224" s="8"/>
       <c r="B224" s="9"/>
       <c r="C224" s="9"/>
@@ -6467,7 +6536,7 @@
       <c r="M224" s="11"/>
       <c r="N224" s="12"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:14">
       <c r="A225" s="8"/>
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
@@ -6489,7 +6558,7 @@
       <c r="M225" s="11"/>
       <c r="N225" s="12"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:14">
       <c r="A226" s="8"/>
       <c r="B226" s="9"/>
       <c r="C226" s="9"/>
@@ -6511,7 +6580,7 @@
       <c r="M226" s="11"/>
       <c r="N226" s="12"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:14">
       <c r="A227" s="8"/>
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
@@ -6533,7 +6602,7 @@
       <c r="M227" s="11"/>
       <c r="N227" s="12"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:14">
       <c r="A228" s="8"/>
       <c r="B228" s="9"/>
       <c r="C228" s="9"/>
@@ -6555,7 +6624,7 @@
       <c r="M228" s="11"/>
       <c r="N228" s="12"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:14">
       <c r="A229" s="8"/>
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
@@ -6577,7 +6646,7 @@
       <c r="M229" s="11"/>
       <c r="N229" s="12"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:14">
       <c r="A230" s="8"/>
       <c r="B230" s="9"/>
       <c r="C230" s="9"/>
@@ -6599,7 +6668,7 @@
       <c r="M230" s="11"/>
       <c r="N230" s="12"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:14">
       <c r="A231" s="8"/>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
@@ -6621,7 +6690,7 @@
       <c r="M231" s="11"/>
       <c r="N231" s="12"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:14">
       <c r="A232" s="8"/>
       <c r="B232" s="9"/>
       <c r="C232" s="9"/>
@@ -6643,7 +6712,7 @@
       <c r="M232" s="11"/>
       <c r="N232" s="12"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:14">
       <c r="A233" s="8"/>
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
@@ -6665,7 +6734,7 @@
       <c r="M233" s="11"/>
       <c r="N233" s="12"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:14">
       <c r="A234" s="8"/>
       <c r="B234" s="9"/>
       <c r="C234" s="9"/>
@@ -6687,7 +6756,7 @@
       <c r="M234" s="11"/>
       <c r="N234" s="12"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:14">
       <c r="A235" s="8"/>
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
@@ -6709,7 +6778,7 @@
       <c r="M235" s="11"/>
       <c r="N235" s="12"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:14">
       <c r="A236" s="8"/>
       <c r="B236" s="9"/>
       <c r="C236" s="9"/>
@@ -6731,7 +6800,7 @@
       <c r="M236" s="11"/>
       <c r="N236" s="12"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:14">
       <c r="A237" s="8"/>
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
@@ -6753,7 +6822,7 @@
       <c r="M237" s="11"/>
       <c r="N237" s="12"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:14">
       <c r="A238" s="8"/>
       <c r="B238" s="9"/>
       <c r="C238" s="9"/>
@@ -6775,7 +6844,7 @@
       <c r="M238" s="11"/>
       <c r="N238" s="12"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:14">
       <c r="A239" s="8"/>
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
@@ -6797,7 +6866,7 @@
       <c r="M239" s="11"/>
       <c r="N239" s="12"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:14">
       <c r="A240" s="8"/>
       <c r="B240" s="9"/>
       <c r="C240" s="9"/>
@@ -6819,7 +6888,7 @@
       <c r="M240" s="11"/>
       <c r="N240" s="12"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:14">
       <c r="A241" s="8"/>
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
@@ -6841,7 +6910,7 @@
       <c r="M241" s="11"/>
       <c r="N241" s="12"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:14">
       <c r="A242" s="8"/>
       <c r="B242" s="9"/>
       <c r="C242" s="9"/>
@@ -6863,7 +6932,7 @@
       <c r="M242" s="11"/>
       <c r="N242" s="12"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:14">
       <c r="A243" s="8"/>
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
@@ -6885,7 +6954,7 @@
       <c r="M243" s="11"/>
       <c r="N243" s="12"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:14">
       <c r="A244" s="8"/>
       <c r="B244" s="9"/>
       <c r="C244" s="9"/>
@@ -6907,7 +6976,7 @@
       <c r="M244" s="11"/>
       <c r="N244" s="12"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:14">
       <c r="A245" s="8"/>
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
@@ -6929,7 +6998,7 @@
       <c r="M245" s="11"/>
       <c r="N245" s="12"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:14">
       <c r="A246" s="8"/>
       <c r="B246" s="9"/>
       <c r="C246" s="9"/>
@@ -6951,7 +7020,7 @@
       <c r="M246" s="11"/>
       <c r="N246" s="12"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:14">
       <c r="A247" s="8"/>
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
@@ -6973,7 +7042,7 @@
       <c r="M247" s="11"/>
       <c r="N247" s="12"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:14">
       <c r="A248" s="8"/>
       <c r="B248" s="9"/>
       <c r="C248" s="9"/>
@@ -6995,7 +7064,7 @@
       <c r="M248" s="11"/>
       <c r="N248" s="12"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:14">
       <c r="A249" s="8"/>
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
@@ -7017,7 +7086,7 @@
       <c r="M249" s="11"/>
       <c r="N249" s="12"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:14">
       <c r="A250" s="8"/>
       <c r="B250" s="9"/>
       <c r="C250" s="9"/>
@@ -7039,7 +7108,7 @@
       <c r="M250" s="11"/>
       <c r="N250" s="12"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:14">
       <c r="A251" s="8"/>
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
@@ -7061,7 +7130,7 @@
       <c r="M251" s="11"/>
       <c r="N251" s="12"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:14">
       <c r="A252" s="8"/>
       <c r="B252" s="9"/>
       <c r="C252" s="9"/>
@@ -7083,7 +7152,7 @@
       <c r="M252" s="11"/>
       <c r="N252" s="12"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:14">
       <c r="A253" s="8"/>
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
@@ -7105,7 +7174,7 @@
       <c r="M253" s="11"/>
       <c r="N253" s="12"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:14">
       <c r="A254" s="8"/>
       <c r="B254" s="9"/>
       <c r="C254" s="9"/>
@@ -7127,7 +7196,7 @@
       <c r="M254" s="11"/>
       <c r="N254" s="12"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:14">
       <c r="A255" s="8"/>
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
@@ -7149,7 +7218,7 @@
       <c r="M255" s="11"/>
       <c r="N255" s="12"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:14">
       <c r="A256" s="8"/>
       <c r="B256" s="9"/>
       <c r="C256" s="9"/>
@@ -7171,7 +7240,7 @@
       <c r="M256" s="11"/>
       <c r="N256" s="12"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:14">
       <c r="A257" s="8"/>
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
@@ -7193,7 +7262,7 @@
       <c r="M257" s="11"/>
       <c r="N257" s="12"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:14">
       <c r="A258" s="8"/>
       <c r="B258" s="9"/>
       <c r="C258" s="9"/>
@@ -7215,7 +7284,7 @@
       <c r="M258" s="11"/>
       <c r="N258" s="12"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:14">
       <c r="A259" s="8"/>
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
@@ -7237,7 +7306,7 @@
       <c r="M259" s="11"/>
       <c r="N259" s="12"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:14">
       <c r="A260" s="8"/>
       <c r="B260" s="9"/>
       <c r="C260" s="9"/>
@@ -7259,7 +7328,7 @@
       <c r="M260" s="11"/>
       <c r="N260" s="12"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:14">
       <c r="A261" s="8"/>
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
@@ -7281,7 +7350,7 @@
       <c r="M261" s="11"/>
       <c r="N261" s="12"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:14">
       <c r="A262" s="8"/>
       <c r="B262" s="9"/>
       <c r="C262" s="9"/>
@@ -7303,7 +7372,7 @@
       <c r="M262" s="11"/>
       <c r="N262" s="12"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:14">
       <c r="A263" s="8"/>
       <c r="B263" s="9"/>
       <c r="C263" s="9"/>
@@ -7325,7 +7394,7 @@
       <c r="M263" s="11"/>
       <c r="N263" s="12"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:14">
       <c r="A264" s="8"/>
       <c r="B264" s="9"/>
       <c r="C264" s="9"/>
@@ -7347,7 +7416,7 @@
       <c r="M264" s="11"/>
       <c r="N264" s="12"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:14">
       <c r="A265" s="8"/>
       <c r="B265" s="9"/>
       <c r="C265" s="9"/>
@@ -7369,7 +7438,7 @@
       <c r="M265" s="11"/>
       <c r="N265" s="12"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14">
       <c r="A266" s="8"/>
       <c r="B266" s="9"/>
       <c r="C266" s="9"/>
@@ -7391,7 +7460,7 @@
       <c r="M266" s="11"/>
       <c r="N266" s="12"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:14">
       <c r="A267" s="8"/>
       <c r="B267" s="9"/>
       <c r="C267" s="9"/>
@@ -7413,7 +7482,7 @@
       <c r="M267" s="11"/>
       <c r="N267" s="12"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:14">
       <c r="A268" s="8"/>
       <c r="B268" s="9"/>
       <c r="C268" s="9"/>
@@ -7435,7 +7504,7 @@
       <c r="M268" s="11"/>
       <c r="N268" s="12"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14">
       <c r="A269" s="8"/>
       <c r="B269" s="9"/>
       <c r="C269" s="9"/>
@@ -7457,7 +7526,7 @@
       <c r="M269" s="11"/>
       <c r="N269" s="12"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:14">
       <c r="A270" s="8"/>
       <c r="B270" s="9"/>
       <c r="C270" s="9"/>
@@ -7479,7 +7548,7 @@
       <c r="M270" s="11"/>
       <c r="N270" s="12"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:14">
       <c r="A271" s="8"/>
       <c r="B271" s="9"/>
       <c r="C271" s="9"/>
@@ -7501,7 +7570,7 @@
       <c r="M271" s="11"/>
       <c r="N271" s="12"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:14">
       <c r="A272" s="8"/>
       <c r="B272" s="9"/>
       <c r="C272" s="9"/>
@@ -7523,7 +7592,7 @@
       <c r="M272" s="11"/>
       <c r="N272" s="12"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:14">
       <c r="A273" s="8"/>
       <c r="B273" s="9"/>
       <c r="C273" s="9"/>
@@ -7545,7 +7614,7 @@
       <c r="M273" s="11"/>
       <c r="N273" s="12"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:14">
       <c r="A274" s="8"/>
       <c r="B274" s="9"/>
       <c r="C274" s="9"/>
@@ -7567,7 +7636,7 @@
       <c r="M274" s="11"/>
       <c r="N274" s="12"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14">
       <c r="A275" s="8"/>
       <c r="B275" s="9"/>
       <c r="C275" s="9"/>
@@ -7589,7 +7658,7 @@
       <c r="M275" s="11"/>
       <c r="N275" s="12"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14">
       <c r="A276" s="8"/>
       <c r="B276" s="9"/>
       <c r="C276" s="9"/>
@@ -7611,7 +7680,7 @@
       <c r="M276" s="11"/>
       <c r="N276" s="12"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14">
       <c r="A277" s="8"/>
       <c r="B277" s="9"/>
       <c r="C277" s="9"/>
@@ -7633,7 +7702,7 @@
       <c r="M277" s="11"/>
       <c r="N277" s="12"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14">
       <c r="A278" s="8"/>
       <c r="B278" s="9"/>
       <c r="C278" s="9"/>
@@ -7655,7 +7724,7 @@
       <c r="M278" s="11"/>
       <c r="N278" s="12"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14">
       <c r="A279" s="8"/>
       <c r="B279" s="9"/>
       <c r="C279" s="9"/>
@@ -7677,7 +7746,7 @@
       <c r="M279" s="11"/>
       <c r="N279" s="12"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14">
       <c r="A280" s="8"/>
       <c r="B280" s="9"/>
       <c r="C280" s="9"/>
@@ -7699,7 +7768,7 @@
       <c r="M280" s="11"/>
       <c r="N280" s="12"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14">
       <c r="A281" s="8"/>
       <c r="B281" s="9"/>
       <c r="C281" s="9"/>
@@ -7721,7 +7790,7 @@
       <c r="M281" s="11"/>
       <c r="N281" s="12"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14">
       <c r="A282" s="8"/>
       <c r="B282" s="9"/>
       <c r="C282" s="9"/>
@@ -7743,7 +7812,7 @@
       <c r="M282" s="11"/>
       <c r="N282" s="12"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14">
       <c r="A283" s="8"/>
       <c r="B283" s="9"/>
       <c r="C283" s="9"/>
@@ -7765,7 +7834,7 @@
       <c r="M283" s="11"/>
       <c r="N283" s="12"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14">
       <c r="A284" s="8"/>
       <c r="B284" s="9"/>
       <c r="C284" s="9"/>
@@ -7787,7 +7856,7 @@
       <c r="M284" s="11"/>
       <c r="N284" s="12"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14">
       <c r="A285" s="8"/>
       <c r="B285" s="9"/>
       <c r="C285" s="9"/>
@@ -7809,7 +7878,7 @@
       <c r="M285" s="11"/>
       <c r="N285" s="12"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14">
       <c r="A286" s="8"/>
       <c r="B286" s="9"/>
       <c r="C286" s="9"/>
@@ -7831,7 +7900,7 @@
       <c r="M286" s="11"/>
       <c r="N286" s="12"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14">
       <c r="A287" s="8"/>
       <c r="B287" s="9"/>
       <c r="C287" s="9"/>
@@ -7853,7 +7922,7 @@
       <c r="M287" s="11"/>
       <c r="N287" s="12"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14">
       <c r="A288" s="8"/>
       <c r="B288" s="9"/>
       <c r="C288" s="9"/>
@@ -7875,7 +7944,7 @@
       <c r="M288" s="11"/>
       <c r="N288" s="12"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:14">
       <c r="A289" s="8"/>
       <c r="B289" s="9"/>
       <c r="C289" s="9"/>
@@ -7897,7 +7966,7 @@
       <c r="M289" s="11"/>
       <c r="N289" s="12"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:14">
       <c r="A290" s="8"/>
       <c r="B290" s="9"/>
       <c r="C290" s="9"/>
@@ -7919,7 +7988,7 @@
       <c r="M290" s="11"/>
       <c r="N290" s="12"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:14">
       <c r="A291" s="8"/>
       <c r="B291" s="9"/>
       <c r="C291" s="9"/>
@@ -7941,7 +8010,7 @@
       <c r="M291" s="11"/>
       <c r="N291" s="12"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:14">
       <c r="A292" s="8"/>
       <c r="B292" s="9"/>
       <c r="C292" s="9"/>
@@ -7963,7 +8032,7 @@
       <c r="M292" s="11"/>
       <c r="N292" s="12"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:14">
       <c r="A293" s="8"/>
       <c r="B293" s="9"/>
       <c r="C293" s="9"/>
@@ -7985,7 +8054,7 @@
       <c r="M293" s="11"/>
       <c r="N293" s="12"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:14">
       <c r="A294" s="8"/>
       <c r="B294" s="9"/>
       <c r="C294" s="9"/>
@@ -8007,7 +8076,7 @@
       <c r="M294" s="11"/>
       <c r="N294" s="12"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:14">
       <c r="A295" s="8"/>
       <c r="B295" s="9"/>
       <c r="C295" s="9"/>
@@ -8029,7 +8098,7 @@
       <c r="M295" s="11"/>
       <c r="N295" s="12"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:14">
       <c r="A296" s="8"/>
       <c r="B296" s="9"/>
       <c r="C296" s="9"/>
@@ -8051,7 +8120,7 @@
       <c r="M296" s="11"/>
       <c r="N296" s="12"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:14">
       <c r="A297" s="8"/>
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
@@ -8073,7 +8142,7 @@
       <c r="M297" s="11"/>
       <c r="N297" s="12"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:14">
       <c r="A298" s="8"/>
       <c r="B298" s="9"/>
       <c r="C298" s="9"/>
@@ -8095,7 +8164,7 @@
       <c r="M298" s="11"/>
       <c r="N298" s="12"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:14">
       <c r="A299" s="8"/>
       <c r="B299" s="9"/>
       <c r="C299" s="9"/>
@@ -8117,7 +8186,7 @@
       <c r="M299" s="11"/>
       <c r="N299" s="12"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:14">
       <c r="A300" s="8"/>
       <c r="B300" s="9"/>
       <c r="C300" s="9"/>
@@ -8139,7 +8208,7 @@
       <c r="M300" s="11"/>
       <c r="N300" s="12"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:14">
       <c r="A301" s="8"/>
       <c r="B301" s="9"/>
       <c r="C301" s="9"/>
@@ -8161,7 +8230,7 @@
       <c r="M301" s="11"/>
       <c r="N301" s="12"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:14">
       <c r="A302" s="8"/>
       <c r="B302" s="9"/>
       <c r="C302" s="9"/>
@@ -8183,7 +8252,7 @@
       <c r="M302" s="11"/>
       <c r="N302" s="12"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:14">
       <c r="A303" s="8"/>
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
@@ -8205,7 +8274,7 @@
       <c r="M303" s="11"/>
       <c r="N303" s="12"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:14">
       <c r="A304" s="8"/>
       <c r="B304" s="9"/>
       <c r="C304" s="9"/>
@@ -8227,7 +8296,7 @@
       <c r="M304" s="11"/>
       <c r="N304" s="12"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:14">
       <c r="A305" s="8"/>
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
@@ -8249,7 +8318,7 @@
       <c r="M305" s="11"/>
       <c r="N305" s="12"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:14">
       <c r="A306" s="8"/>
       <c r="B306" s="9"/>
       <c r="C306" s="9"/>
@@ -8271,7 +8340,7 @@
       <c r="M306" s="11"/>
       <c r="N306" s="12"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:14">
       <c r="A307" s="8"/>
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
@@ -8293,7 +8362,7 @@
       <c r="M307" s="11"/>
       <c r="N307" s="12"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:14">
       <c r="A308" s="8"/>
       <c r="B308" s="9"/>
       <c r="C308" s="9"/>
@@ -8315,7 +8384,7 @@
       <c r="M308" s="11"/>
       <c r="N308" s="12"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:14">
       <c r="A309" s="8"/>
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
@@ -8337,7 +8406,7 @@
       <c r="M309" s="11"/>
       <c r="N309" s="12"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:14">
       <c r="A310" s="8"/>
       <c r="B310" s="9"/>
       <c r="C310" s="9"/>
@@ -8359,7 +8428,7 @@
       <c r="M310" s="11"/>
       <c r="N310" s="12"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:14">
       <c r="A311" s="8"/>
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
@@ -8381,7 +8450,7 @@
       <c r="M311" s="11"/>
       <c r="N311" s="12"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:14">
       <c r="A312" s="8"/>
       <c r="B312" s="9"/>
       <c r="C312" s="9"/>
@@ -8403,7 +8472,7 @@
       <c r="M312" s="11"/>
       <c r="N312" s="12"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:14">
       <c r="A313" s="8"/>
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
@@ -8425,7 +8494,7 @@
       <c r="M313" s="11"/>
       <c r="N313" s="12"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:14">
       <c r="A314" s="8"/>
       <c r="B314" s="9"/>
       <c r="C314" s="9"/>
@@ -8447,7 +8516,7 @@
       <c r="M314" s="11"/>
       <c r="N314" s="12"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:14">
       <c r="A315" s="8"/>
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
@@ -8469,7 +8538,7 @@
       <c r="M315" s="11"/>
       <c r="N315" s="12"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:14">
       <c r="A316" s="8"/>
       <c r="B316" s="9"/>
       <c r="C316" s="9"/>
@@ -8491,7 +8560,7 @@
       <c r="M316" s="11"/>
       <c r="N316" s="12"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:14">
       <c r="A317" s="8"/>
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
@@ -8513,7 +8582,7 @@
       <c r="M317" s="11"/>
       <c r="N317" s="12"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:14">
       <c r="A318" s="8"/>
       <c r="B318" s="9"/>
       <c r="C318" s="9"/>
@@ -8535,7 +8604,7 @@
       <c r="M318" s="11"/>
       <c r="N318" s="12"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:14">
       <c r="A319" s="8"/>
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
@@ -8557,7 +8626,7 @@
       <c r="M319" s="11"/>
       <c r="N319" s="12"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:14">
       <c r="A320" s="8"/>
       <c r="B320" s="9"/>
       <c r="C320" s="9"/>
@@ -8579,7 +8648,7 @@
       <c r="M320" s="11"/>
       <c r="N320" s="12"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:14">
       <c r="A321" s="8"/>
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
@@ -8601,7 +8670,7 @@
       <c r="M321" s="11"/>
       <c r="N321" s="12"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:14">
       <c r="A322" s="8"/>
       <c r="B322" s="9"/>
       <c r="C322" s="9"/>
@@ -8623,7 +8692,7 @@
       <c r="M322" s="11"/>
       <c r="N322" s="12"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:14">
       <c r="A323" s="8"/>
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
@@ -8645,7 +8714,7 @@
       <c r="M323" s="11"/>
       <c r="N323" s="12"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:14">
       <c r="A324" s="8"/>
       <c r="B324" s="9"/>
       <c r="C324" s="9"/>
@@ -8667,7 +8736,7 @@
       <c r="M324" s="11"/>
       <c r="N324" s="12"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:14">
       <c r="A325" s="8"/>
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
@@ -8689,7 +8758,7 @@
       <c r="M325" s="11"/>
       <c r="N325" s="12"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:14">
       <c r="A326" s="8"/>
       <c r="B326" s="9"/>
       <c r="C326" s="9"/>
@@ -8711,7 +8780,7 @@
       <c r="M326" s="11"/>
       <c r="N326" s="12"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:14">
       <c r="A327" s="8"/>
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
@@ -8733,7 +8802,7 @@
       <c r="M327" s="11"/>
       <c r="N327" s="12"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:14">
       <c r="A328" s="8"/>
       <c r="B328" s="9"/>
       <c r="C328" s="9"/>
@@ -8755,7 +8824,7 @@
       <c r="M328" s="11"/>
       <c r="N328" s="12"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:14">
       <c r="A329" s="8"/>
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
@@ -8777,7 +8846,7 @@
       <c r="M329" s="11"/>
       <c r="N329" s="12"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:14">
       <c r="A330" s="8"/>
       <c r="B330" s="9"/>
       <c r="C330" s="9"/>
@@ -8799,7 +8868,7 @@
       <c r="M330" s="11"/>
       <c r="N330" s="12"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:14">
       <c r="A331" s="8"/>
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
@@ -8821,7 +8890,7 @@
       <c r="M331" s="11"/>
       <c r="N331" s="12"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:14">
       <c r="A332" s="8"/>
       <c r="B332" s="9"/>
       <c r="C332" s="9"/>
@@ -8843,7 +8912,7 @@
       <c r="M332" s="11"/>
       <c r="N332" s="12"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:14">
       <c r="A333" s="8"/>
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
@@ -8865,7 +8934,7 @@
       <c r="M333" s="11"/>
       <c r="N333" s="12"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:14">
       <c r="A334" s="8"/>
       <c r="B334" s="9"/>
       <c r="C334" s="9"/>
@@ -8887,7 +8956,7 @@
       <c r="M334" s="11"/>
       <c r="N334" s="12"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:14">
       <c r="A335" s="8"/>
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
@@ -8909,7 +8978,7 @@
       <c r="M335" s="11"/>
       <c r="N335" s="12"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:14">
       <c r="A336" s="8"/>
       <c r="B336" s="9"/>
       <c r="C336" s="9"/>
@@ -8931,7 +9000,7 @@
       <c r="M336" s="11"/>
       <c r="N336" s="12"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:14">
       <c r="A337" s="8"/>
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
@@ -8953,7 +9022,7 @@
       <c r="M337" s="11"/>
       <c r="N337" s="12"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:14">
       <c r="A338" s="8"/>
       <c r="B338" s="9"/>
       <c r="C338" s="9"/>
@@ -8975,7 +9044,7 @@
       <c r="M338" s="11"/>
       <c r="N338" s="12"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:14">
       <c r="A339" s="8"/>
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
@@ -8997,7 +9066,7 @@
       <c r="M339" s="11"/>
       <c r="N339" s="12"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:14">
       <c r="A340" s="8"/>
       <c r="B340" s="9"/>
       <c r="C340" s="9"/>
@@ -9019,7 +9088,7 @@
       <c r="M340" s="11"/>
       <c r="N340" s="12"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:14">
       <c r="A341" s="8"/>
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
@@ -9041,7 +9110,7 @@
       <c r="M341" s="11"/>
       <c r="N341" s="12"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:14">
       <c r="A342" s="8"/>
       <c r="B342" s="9"/>
       <c r="C342" s="9"/>
@@ -9063,7 +9132,7 @@
       <c r="M342" s="11"/>
       <c r="N342" s="12"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:14">
       <c r="A343" s="8"/>
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
@@ -9085,7 +9154,7 @@
       <c r="M343" s="11"/>
       <c r="N343" s="12"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:14">
       <c r="A344" s="8"/>
       <c r="B344" s="9"/>
       <c r="C344" s="9"/>
@@ -9107,7 +9176,7 @@
       <c r="M344" s="11"/>
       <c r="N344" s="12"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:14">
       <c r="A345" s="8"/>
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
@@ -9129,7 +9198,7 @@
       <c r="M345" s="11"/>
       <c r="N345" s="12"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:14">
       <c r="A346" s="8"/>
       <c r="B346" s="9"/>
       <c r="C346" s="9"/>
@@ -9151,7 +9220,7 @@
       <c r="M346" s="11"/>
       <c r="N346" s="12"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:14">
       <c r="A347" s="8"/>
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
@@ -9173,7 +9242,7 @@
       <c r="M347" s="11"/>
       <c r="N347" s="12"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:14">
       <c r="A348" s="8"/>
       <c r="B348" s="9"/>
       <c r="C348" s="9"/>
@@ -9195,7 +9264,7 @@
       <c r="M348" s="11"/>
       <c r="N348" s="12"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:14">
       <c r="A349" s="8"/>
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
@@ -9217,7 +9286,7 @@
       <c r="M349" s="11"/>
       <c r="N349" s="12"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:14">
       <c r="A350" s="8"/>
       <c r="B350" s="9"/>
       <c r="C350" s="9"/>
@@ -9239,7 +9308,7 @@
       <c r="M350" s="11"/>
       <c r="N350" s="12"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:14">
       <c r="A351" s="8"/>
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
@@ -9261,7 +9330,7 @@
       <c r="M351" s="11"/>
       <c r="N351" s="12"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:14">
       <c r="A352" s="8"/>
       <c r="B352" s="9"/>
       <c r="C352" s="9"/>
@@ -9283,7 +9352,7 @@
       <c r="M352" s="11"/>
       <c r="N352" s="12"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:14">
       <c r="A353" s="8"/>
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
@@ -9305,7 +9374,7 @@
       <c r="M353" s="11"/>
       <c r="N353" s="12"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:14">
       <c r="A354" s="8"/>
       <c r="B354" s="9"/>
       <c r="C354" s="9"/>
@@ -9327,7 +9396,7 @@
       <c r="M354" s="11"/>
       <c r="N354" s="12"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:14">
       <c r="A355" s="8"/>
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
@@ -9349,7 +9418,7 @@
       <c r="M355" s="11"/>
       <c r="N355" s="12"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:14">
       <c r="A356" s="8"/>
       <c r="B356" s="9"/>
       <c r="C356" s="9"/>
@@ -9371,7 +9440,7 @@
       <c r="M356" s="11"/>
       <c r="N356" s="12"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:14">
       <c r="A357" s="8"/>
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
@@ -9393,7 +9462,7 @@
       <c r="M357" s="11"/>
       <c r="N357" s="12"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:14">
       <c r="A358" s="8"/>
       <c r="B358" s="9"/>
       <c r="C358" s="9"/>
@@ -9415,7 +9484,7 @@
       <c r="M358" s="11"/>
       <c r="N358" s="12"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:14">
       <c r="A359" s="8"/>
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
@@ -9437,7 +9506,7 @@
       <c r="M359" s="11"/>
       <c r="N359" s="12"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:14">
       <c r="A360" s="8"/>
       <c r="B360" s="9"/>
       <c r="C360" s="9"/>
@@ -9459,7 +9528,7 @@
       <c r="M360" s="11"/>
       <c r="N360" s="12"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:14">
       <c r="A361" s="8"/>
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
@@ -9481,7 +9550,7 @@
       <c r="M361" s="11"/>
       <c r="N361" s="12"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:14">
       <c r="A362" s="8"/>
       <c r="B362" s="9"/>
       <c r="C362" s="9"/>
@@ -9503,7 +9572,7 @@
       <c r="M362" s="11"/>
       <c r="N362" s="12"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:14">
       <c r="A363" s="8"/>
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
@@ -9525,7 +9594,7 @@
       <c r="M363" s="11"/>
       <c r="N363" s="12"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:14">
       <c r="A364" s="8"/>
       <c r="B364" s="9"/>
       <c r="C364" s="9"/>
@@ -9547,7 +9616,7 @@
       <c r="M364" s="11"/>
       <c r="N364" s="12"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:14">
       <c r="A365" s="8"/>
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
@@ -9569,7 +9638,7 @@
       <c r="M365" s="11"/>
       <c r="N365" s="12"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:14">
       <c r="A366" s="8"/>
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
@@ -9591,7 +9660,7 @@
       <c r="M366" s="11"/>
       <c r="N366" s="12"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:14">
       <c r="A367" s="8"/>
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
@@ -9613,7 +9682,7 @@
       <c r="M367" s="11"/>
       <c r="N367" s="12"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:14">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
       <c r="C368" s="9"/>
@@ -9635,7 +9704,7 @@
       <c r="M368" s="11"/>
       <c r="N368" s="12"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:14">
       <c r="A369" s="8"/>
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
@@ -9657,7 +9726,7 @@
       <c r="M369" s="11"/>
       <c r="N369" s="12"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:14">
       <c r="A370" s="8"/>
       <c r="B370" s="9"/>
       <c r="C370" s="9"/>
@@ -9679,7 +9748,7 @@
       <c r="M370" s="11"/>
       <c r="N370" s="12"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:14">
       <c r="A371" s="8"/>
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
@@ -9701,7 +9770,7 @@
       <c r="M371" s="11"/>
       <c r="N371" s="12"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:14">
       <c r="A372" s="8"/>
       <c r="B372" s="9"/>
       <c r="C372" s="9"/>
@@ -9723,7 +9792,7 @@
       <c r="M372" s="11"/>
       <c r="N372" s="12"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:14">
       <c r="A373" s="8"/>
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
@@ -9745,7 +9814,7 @@
       <c r="M373" s="11"/>
       <c r="N373" s="12"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:14">
       <c r="A374" s="8"/>
       <c r="B374" s="9"/>
       <c r="C374" s="9"/>
@@ -9767,7 +9836,7 @@
       <c r="M374" s="11"/>
       <c r="N374" s="12"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:14">
       <c r="A375" s="8"/>
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
@@ -9789,7 +9858,7 @@
       <c r="M375" s="11"/>
       <c r="N375" s="12"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:14">
       <c r="A376" s="8"/>
       <c r="B376" s="9"/>
       <c r="C376" s="9"/>
@@ -9811,7 +9880,7 @@
       <c r="M376" s="11"/>
       <c r="N376" s="12"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:14">
       <c r="A377" s="8"/>
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
@@ -9833,7 +9902,7 @@
       <c r="M377" s="11"/>
       <c r="N377" s="12"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:14">
       <c r="A378" s="8"/>
       <c r="B378" s="9"/>
       <c r="C378" s="9"/>
@@ -9855,7 +9924,7 @@
       <c r="M378" s="11"/>
       <c r="N378" s="12"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:14">
       <c r="A379" s="8"/>
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
@@ -9877,7 +9946,7 @@
       <c r="M379" s="11"/>
       <c r="N379" s="12"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:14">
       <c r="A380" s="8"/>
       <c r="B380" s="9"/>
       <c r="C380" s="9"/>
@@ -9899,7 +9968,7 @@
       <c r="M380" s="11"/>
       <c r="N380" s="12"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:14">
       <c r="A381" s="8"/>
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
@@ -9921,7 +9990,7 @@
       <c r="M381" s="11"/>
       <c r="N381" s="12"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:14">
       <c r="A382" s="8"/>
       <c r="B382" s="9"/>
       <c r="C382" s="9"/>
@@ -9943,7 +10012,7 @@
       <c r="M382" s="11"/>
       <c r="N382" s="12"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:14">
       <c r="A383" s="8"/>
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
@@ -9965,7 +10034,7 @@
       <c r="M383" s="11"/>
       <c r="N383" s="12"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:14">
       <c r="A384" s="8"/>
       <c r="B384" s="9"/>
       <c r="C384" s="9"/>
@@ -9987,7 +10056,7 @@
       <c r="M384" s="11"/>
       <c r="N384" s="12"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:14">
       <c r="A385" s="8"/>
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
@@ -10009,7 +10078,7 @@
       <c r="M385" s="11"/>
       <c r="N385" s="12"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:14">
       <c r="A386" s="8"/>
       <c r="B386" s="9"/>
       <c r="C386" s="9"/>
@@ -10031,7 +10100,7 @@
       <c r="M386" s="11"/>
       <c r="N386" s="12"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:14">
       <c r="A387" s="8"/>
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
@@ -10053,7 +10122,7 @@
       <c r="M387" s="11"/>
       <c r="N387" s="12"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:14">
       <c r="A388" s="8"/>
       <c r="B388" s="9"/>
       <c r="C388" s="9"/>
@@ -10075,7 +10144,7 @@
       <c r="M388" s="11"/>
       <c r="N388" s="12"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:14">
       <c r="A389" s="8"/>
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
@@ -10097,7 +10166,7 @@
       <c r="M389" s="11"/>
       <c r="N389" s="12"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:14">
       <c r="A390" s="8"/>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
@@ -10119,7 +10188,7 @@
       <c r="M390" s="11"/>
       <c r="N390" s="12"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:14">
       <c r="A391" s="8"/>
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
@@ -10141,7 +10210,7 @@
       <c r="M391" s="11"/>
       <c r="N391" s="12"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:14">
       <c r="A392" s="8"/>
       <c r="B392" s="9"/>
       <c r="C392" s="9"/>
@@ -10163,7 +10232,7 @@
       <c r="M392" s="11"/>
       <c r="N392" s="12"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:14">
       <c r="A393" s="8"/>
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
@@ -10185,7 +10254,7 @@
       <c r="M393" s="11"/>
       <c r="N393" s="12"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:14">
       <c r="A394" s="8"/>
       <c r="B394" s="9"/>
       <c r="C394" s="9"/>
@@ -10207,7 +10276,7 @@
       <c r="M394" s="11"/>
       <c r="N394" s="12"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:14">
       <c r="A395" s="8"/>
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
@@ -10229,7 +10298,7 @@
       <c r="M395" s="11"/>
       <c r="N395" s="12"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:14">
       <c r="A396" s="8"/>
       <c r="B396" s="9"/>
       <c r="C396" s="9"/>
@@ -10251,7 +10320,7 @@
       <c r="M396" s="11"/>
       <c r="N396" s="12"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:14">
       <c r="A397" s="8"/>
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
@@ -10273,7 +10342,7 @@
       <c r="M397" s="11"/>
       <c r="N397" s="12"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:14">
       <c r="A398" s="8"/>
       <c r="B398" s="9"/>
       <c r="C398" s="9"/>
@@ -10295,7 +10364,7 @@
       <c r="M398" s="11"/>
       <c r="N398" s="12"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:14">
       <c r="A399" s="8"/>
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
@@ -10317,7 +10386,7 @@
       <c r="M399" s="11"/>
       <c r="N399" s="12"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:14">
       <c r="A400" s="8"/>
       <c r="B400" s="9"/>
       <c r="C400" s="9"/>
@@ -10339,7 +10408,7 @@
       <c r="M400" s="11"/>
       <c r="N400" s="12"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:14">
       <c r="A401" s="8"/>
       <c r="B401" s="9"/>
       <c r="C401" s="9"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B036C2-0F34-4333-B599-BDD0E1A7E5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144F487E-D2F8-495A-A3D8-26F725EBD1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,12 @@
   <si>
     <t>I had DBMS viva,it was good.I discussed about the evaluation of english CA, but she has'nt genuine feedback. Also we had fresher's party, I enjoyed a lot,danced and ate every thing available and it helped me relieve.</t>
   </si>
+  <si>
+    <t xml:space="preserve">I had 3rd fresher league match,again we lost the match. </t>
+  </si>
+  <si>
+    <t>Felt dizzy for the whole day and low as well. Not a productive day.</t>
+  </si>
 </sst>
 </file>
 
@@ -301,7 +307,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,186 +768,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.8">
+    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.8">
+    <row r="2" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -953,7 +959,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
@@ -968,7 +974,7 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
@@ -986,7 +992,7 @@
       <c r="M1" s="20"/>
       <c r="N1" s="20"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1">
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -1003,7 +1009,7 @@
       </c>
       <c r="G2" s="22"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1">
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -1020,7 +1026,7 @@
       </c>
       <c r="G3" s="21"/>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
@@ -1038,7 +1044,7 @@
       <c r="M4" s="19"/>
       <c r="N4" s="19"/>
     </row>
-    <row r="5" spans="1:14" ht="41.4">
+    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1082,7 +1088,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="13" customFormat="1" ht="43.2">
+    <row r="6" spans="1:14" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>46251</v>
       </c>
@@ -1128,7 +1134,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="57.6">
+    <row r="7" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>46252</v>
       </c>
@@ -1174,7 +1180,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="18">
         <v>46253</v>
       </c>
@@ -1218,7 +1224,7 @@
       </c>
       <c r="N8" s="12"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>46254</v>
       </c>
@@ -1264,7 +1270,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="57.6">
+    <row r="10" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="18">
         <v>46255</v>
       </c>
@@ -1310,7 +1316,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="57.6">
+    <row r="11" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>46256</v>
       </c>
@@ -1356,7 +1362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="28.8">
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18">
         <v>46257</v>
       </c>
@@ -1402,7 +1408,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="43.2">
+    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>46258</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="72">
+    <row r="14" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="18">
         <v>46259</v>
       </c>
@@ -1494,7 +1500,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="72">
+    <row r="15" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>46260</v>
       </c>
@@ -1540,7 +1546,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="72">
+    <row r="16" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="18">
         <v>46261</v>
       </c>
@@ -1586,7 +1592,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="86.4">
+    <row r="17" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>46262</v>
       </c>
@@ -1632,7 +1638,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="72">
+    <row r="18" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="18">
         <v>46263</v>
       </c>
@@ -1678,7 +1684,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>46264</v>
       </c>
@@ -1724,7 +1730,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="57.6">
+    <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="18">
         <v>46265</v>
       </c>
@@ -1770,7 +1776,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="43.2">
+    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>46266</v>
       </c>
@@ -1816,7 +1822,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="57.6">
+    <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>46267</v>
       </c>
@@ -1862,7 +1868,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="86.4">
+    <row r="23" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>46268</v>
       </c>
@@ -1908,7 +1914,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="43.2">
+    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>46269</v>
       </c>
@@ -1954,7 +1960,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="57.6">
+    <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>46270</v>
       </c>
@@ -2000,7 +2006,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>46271</v>
       </c>
@@ -2046,7 +2052,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="72">
+    <row r="27" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>46272</v>
       </c>
@@ -2092,7 +2098,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>46273</v>
       </c>
@@ -2136,7 +2142,7 @@
       </c>
       <c r="N28" s="12"/>
     </row>
-    <row r="29" spans="1:14" ht="72">
+    <row r="29" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>46274</v>
       </c>
@@ -2182,7 +2188,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="115.2">
+    <row r="30" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>46275</v>
       </c>
@@ -2228,55 +2234,99 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>46276</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+      <c r="B31" s="9">
+        <v>180</v>
+      </c>
+      <c r="C31" s="9">
+        <v>50</v>
+      </c>
+      <c r="D31" s="9">
+        <v>60</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9">
+        <v>100</v>
+      </c>
+      <c r="G31" s="9">
+        <v>2</v>
+      </c>
+      <c r="H31" s="9">
+        <v>120</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>510</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
-    </row>
-    <row r="32" spans="1:14">
+        <v>930</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>46277</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+      <c r="B32" s="9">
+        <v>720</v>
+      </c>
+      <c r="C32" s="9">
+        <v>10</v>
+      </c>
+      <c r="D32" s="9">
+        <v>180</v>
+      </c>
+      <c r="E32" s="9">
+        <v>30</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>120</v>
+      </c>
+      <c r="I32" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
-    </row>
-    <row r="33" spans="1:14">
+        <v>380</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>46278</v>
       </c>
@@ -2300,7 +2350,7 @@
       <c r="M33" s="11"/>
       <c r="N33" s="12"/>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>46279</v>
       </c>
@@ -2324,7 +2374,7 @@
       <c r="M34" s="11"/>
       <c r="N34" s="12"/>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>46280</v>
       </c>
@@ -2348,7 +2398,7 @@
       <c r="M35" s="11"/>
       <c r="N35" s="12"/>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>46281</v>
       </c>
@@ -2372,7 +2422,7 @@
       <c r="M36" s="11"/>
       <c r="N36" s="12"/>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>46282</v>
       </c>
@@ -2396,7 +2446,7 @@
       <c r="M37" s="11"/>
       <c r="N37" s="12"/>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>46283</v>
       </c>
@@ -2420,7 +2470,7 @@
       <c r="M38" s="11"/>
       <c r="N38" s="12"/>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>46284</v>
       </c>
@@ -2444,7 +2494,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="12"/>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>46285</v>
       </c>
@@ -2468,7 +2518,7 @@
       <c r="M40" s="11"/>
       <c r="N40" s="12"/>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>46286</v>
       </c>
@@ -2492,7 +2542,7 @@
       <c r="M41" s="11"/>
       <c r="N41" s="12"/>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>46287</v>
       </c>
@@ -2516,7 +2566,7 @@
       <c r="M42" s="11"/>
       <c r="N42" s="12"/>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>46288</v>
       </c>
@@ -2540,7 +2590,7 @@
       <c r="M43" s="11"/>
       <c r="N43" s="12"/>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>46289</v>
       </c>
@@ -2564,7 +2614,7 @@
       <c r="M44" s="11"/>
       <c r="N44" s="12"/>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>46290</v>
       </c>
@@ -2588,7 +2638,7 @@
       <c r="M45" s="11"/>
       <c r="N45" s="12"/>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>46291</v>
       </c>
@@ -2612,7 +2662,7 @@
       <c r="M46" s="11"/>
       <c r="N46" s="12"/>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>46292</v>
       </c>
@@ -2636,7 +2686,7 @@
       <c r="M47" s="11"/>
       <c r="N47" s="12"/>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>46293</v>
       </c>
@@ -2660,7 +2710,7 @@
       <c r="M48" s="11"/>
       <c r="N48" s="12"/>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>46294</v>
       </c>
@@ -2684,7 +2734,7 @@
       <c r="M49" s="11"/>
       <c r="N49" s="12"/>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>46295</v>
       </c>
@@ -2708,7 +2758,7 @@
       <c r="M50" s="11"/>
       <c r="N50" s="12"/>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -2730,7 +2780,7 @@
       <c r="M51" s="11"/>
       <c r="N51" s="12"/>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -2752,7 +2802,7 @@
       <c r="M52" s="11"/>
       <c r="N52" s="12"/>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
@@ -2774,7 +2824,7 @@
       <c r="M53" s="11"/>
       <c r="N53" s="12"/>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
@@ -2796,7 +2846,7 @@
       <c r="M54" s="11"/>
       <c r="N54" s="12"/>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -2818,7 +2868,7 @@
       <c r="M55" s="11"/>
       <c r="N55" s="12"/>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -2840,7 +2890,7 @@
       <c r="M56" s="11"/>
       <c r="N56" s="12"/>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -2862,7 +2912,7 @@
       <c r="M57" s="11"/>
       <c r="N57" s="12"/>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -2884,7 +2934,7 @@
       <c r="M58" s="11"/>
       <c r="N58" s="12"/>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="8"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
@@ -2906,7 +2956,7 @@
       <c r="M59" s="11"/>
       <c r="N59" s="12"/>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -2928,7 +2978,7 @@
       <c r="M60" s="11"/>
       <c r="N60" s="12"/>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
@@ -2950,7 +3000,7 @@
       <c r="M61" s="11"/>
       <c r="N61" s="12"/>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
@@ -2972,7 +3022,7 @@
       <c r="M62" s="11"/>
       <c r="N62" s="12"/>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -2994,7 +3044,7 @@
       <c r="M63" s="11"/>
       <c r="N63" s="12"/>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
@@ -3016,7 +3066,7 @@
       <c r="M64" s="11"/>
       <c r="N64" s="12"/>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
@@ -3038,7 +3088,7 @@
       <c r="M65" s="11"/>
       <c r="N65" s="12"/>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -3060,7 +3110,7 @@
       <c r="M66" s="11"/>
       <c r="N66" s="12"/>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -3082,7 +3132,7 @@
       <c r="M67" s="11"/>
       <c r="N67" s="12"/>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
@@ -3104,7 +3154,7 @@
       <c r="M68" s="11"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
@@ -3126,7 +3176,7 @@
       <c r="M69" s="11"/>
       <c r="N69" s="12"/>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
@@ -3148,7 +3198,7 @@
       <c r="M70" s="11"/>
       <c r="N70" s="12"/>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
@@ -3170,7 +3220,7 @@
       <c r="M71" s="11"/>
       <c r="N71" s="12"/>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
@@ -3192,7 +3242,7 @@
       <c r="M72" s="11"/>
       <c r="N72" s="12"/>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
@@ -3214,7 +3264,7 @@
       <c r="M73" s="11"/>
       <c r="N73" s="12"/>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
@@ -3236,7 +3286,7 @@
       <c r="M74" s="11"/>
       <c r="N74" s="12"/>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
@@ -3258,7 +3308,7 @@
       <c r="M75" s="11"/>
       <c r="N75" s="12"/>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
@@ -3280,7 +3330,7 @@
       <c r="M76" s="11"/>
       <c r="N76" s="12"/>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
@@ -3302,7 +3352,7 @@
       <c r="M77" s="11"/>
       <c r="N77" s="12"/>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
@@ -3324,7 +3374,7 @@
       <c r="M78" s="11"/>
       <c r="N78" s="12"/>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
@@ -3346,7 +3396,7 @@
       <c r="M79" s="11"/>
       <c r="N79" s="12"/>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
@@ -3368,7 +3418,7 @@
       <c r="M80" s="11"/>
       <c r="N80" s="12"/>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
@@ -3390,7 +3440,7 @@
       <c r="M81" s="11"/>
       <c r="N81" s="12"/>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
@@ -3412,7 +3462,7 @@
       <c r="M82" s="11"/>
       <c r="N82" s="12"/>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="8"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
@@ -3434,7 +3484,7 @@
       <c r="M83" s="11"/>
       <c r="N83" s="12"/>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="8"/>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
@@ -3456,7 +3506,7 @@
       <c r="M84" s="11"/>
       <c r="N84" s="12"/>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="8"/>
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
@@ -3478,7 +3528,7 @@
       <c r="M85" s="11"/>
       <c r="N85" s="12"/>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="8"/>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
@@ -3500,7 +3550,7 @@
       <c r="M86" s="11"/>
       <c r="N86" s="12"/>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="8"/>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
@@ -3522,7 +3572,7 @@
       <c r="M87" s="11"/>
       <c r="N87" s="12"/>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="8"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
@@ -3544,7 +3594,7 @@
       <c r="M88" s="11"/>
       <c r="N88" s="12"/>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="8"/>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
@@ -3566,7 +3616,7 @@
       <c r="M89" s="11"/>
       <c r="N89" s="12"/>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="8"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
@@ -3588,7 +3638,7 @@
       <c r="M90" s="11"/>
       <c r="N90" s="12"/>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="8"/>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
@@ -3610,7 +3660,7 @@
       <c r="M91" s="11"/>
       <c r="N91" s="12"/>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="8"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
@@ -3632,7 +3682,7 @@
       <c r="M92" s="11"/>
       <c r="N92" s="12"/>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="8"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
@@ -3654,7 +3704,7 @@
       <c r="M93" s="11"/>
       <c r="N93" s="12"/>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="8"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
@@ -3676,7 +3726,7 @@
       <c r="M94" s="11"/>
       <c r="N94" s="12"/>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="8"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
@@ -3698,7 +3748,7 @@
       <c r="M95" s="11"/>
       <c r="N95" s="12"/>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="8"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
@@ -3720,7 +3770,7 @@
       <c r="M96" s="11"/>
       <c r="N96" s="12"/>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="8"/>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
@@ -3742,7 +3792,7 @@
       <c r="M97" s="11"/>
       <c r="N97" s="12"/>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="8"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
@@ -3764,7 +3814,7 @@
       <c r="M98" s="11"/>
       <c r="N98" s="12"/>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="8"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
@@ -3786,7 +3836,7 @@
       <c r="M99" s="11"/>
       <c r="N99" s="12"/>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="8"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
@@ -3808,7 +3858,7 @@
       <c r="M100" s="11"/>
       <c r="N100" s="12"/>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="8"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
@@ -3830,7 +3880,7 @@
       <c r="M101" s="11"/>
       <c r="N101" s="12"/>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="8"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
@@ -3852,7 +3902,7 @@
       <c r="M102" s="11"/>
       <c r="N102" s="12"/>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="8"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
@@ -3874,7 +3924,7 @@
       <c r="M103" s="11"/>
       <c r="N103" s="12"/>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="8"/>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
@@ -3896,7 +3946,7 @@
       <c r="M104" s="11"/>
       <c r="N104" s="12"/>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="8"/>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
@@ -3918,7 +3968,7 @@
       <c r="M105" s="11"/>
       <c r="N105" s="12"/>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="8"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
@@ -3940,7 +3990,7 @@
       <c r="M106" s="11"/>
       <c r="N106" s="12"/>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="8"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
@@ -3962,7 +4012,7 @@
       <c r="M107" s="11"/>
       <c r="N107" s="12"/>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="8"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
@@ -3984,7 +4034,7 @@
       <c r="M108" s="11"/>
       <c r="N108" s="12"/>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="8"/>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
@@ -4006,7 +4056,7 @@
       <c r="M109" s="11"/>
       <c r="N109" s="12"/>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="8"/>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
@@ -4028,7 +4078,7 @@
       <c r="M110" s="11"/>
       <c r="N110" s="12"/>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="8"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
@@ -4050,7 +4100,7 @@
       <c r="M111" s="11"/>
       <c r="N111" s="12"/>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="8"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
@@ -4072,7 +4122,7 @@
       <c r="M112" s="11"/>
       <c r="N112" s="12"/>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="8"/>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
@@ -4094,7 +4144,7 @@
       <c r="M113" s="11"/>
       <c r="N113" s="12"/>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="8"/>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
@@ -4116,7 +4166,7 @@
       <c r="M114" s="11"/>
       <c r="N114" s="12"/>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="8"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
@@ -4138,7 +4188,7 @@
       <c r="M115" s="11"/>
       <c r="N115" s="12"/>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="8"/>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
@@ -4160,7 +4210,7 @@
       <c r="M116" s="11"/>
       <c r="N116" s="12"/>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="8"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
@@ -4182,7 +4232,7 @@
       <c r="M117" s="11"/>
       <c r="N117" s="12"/>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="8"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
@@ -4204,7 +4254,7 @@
       <c r="M118" s="11"/>
       <c r="N118" s="12"/>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="8"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
@@ -4226,7 +4276,7 @@
       <c r="M119" s="11"/>
       <c r="N119" s="12"/>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="8"/>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
@@ -4248,7 +4298,7 @@
       <c r="M120" s="11"/>
       <c r="N120" s="12"/>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="8"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
@@ -4270,7 +4320,7 @@
       <c r="M121" s="11"/>
       <c r="N121" s="12"/>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="8"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
@@ -4292,7 +4342,7 @@
       <c r="M122" s="11"/>
       <c r="N122" s="12"/>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="8"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
@@ -4314,7 +4364,7 @@
       <c r="M123" s="11"/>
       <c r="N123" s="12"/>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="8"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
@@ -4336,7 +4386,7 @@
       <c r="M124" s="11"/>
       <c r="N124" s="12"/>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="8"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
@@ -4358,7 +4408,7 @@
       <c r="M125" s="11"/>
       <c r="N125" s="12"/>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="8"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
@@ -4380,7 +4430,7 @@
       <c r="M126" s="11"/>
       <c r="N126" s="12"/>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="8"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
@@ -4402,7 +4452,7 @@
       <c r="M127" s="11"/>
       <c r="N127" s="12"/>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="8"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
@@ -4424,7 +4474,7 @@
       <c r="M128" s="11"/>
       <c r="N128" s="12"/>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="8"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -4446,7 +4496,7 @@
       <c r="M129" s="11"/>
       <c r="N129" s="12"/>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="8"/>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
@@ -4468,7 +4518,7 @@
       <c r="M130" s="11"/>
       <c r="N130" s="12"/>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="8"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
@@ -4490,7 +4540,7 @@
       <c r="M131" s="11"/>
       <c r="N131" s="12"/>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="8"/>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
@@ -4512,7 +4562,7 @@
       <c r="M132" s="11"/>
       <c r="N132" s="12"/>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="8"/>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
@@ -4534,7 +4584,7 @@
       <c r="M133" s="11"/>
       <c r="N133" s="12"/>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="8"/>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
@@ -4556,7 +4606,7 @@
       <c r="M134" s="11"/>
       <c r="N134" s="12"/>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="8"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
@@ -4578,7 +4628,7 @@
       <c r="M135" s="11"/>
       <c r="N135" s="12"/>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="8"/>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
@@ -4600,7 +4650,7 @@
       <c r="M136" s="11"/>
       <c r="N136" s="12"/>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="8"/>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
@@ -4622,7 +4672,7 @@
       <c r="M137" s="11"/>
       <c r="N137" s="12"/>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="8"/>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
@@ -4644,7 +4694,7 @@
       <c r="M138" s="11"/>
       <c r="N138" s="12"/>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="8"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
@@ -4666,7 +4716,7 @@
       <c r="M139" s="11"/>
       <c r="N139" s="12"/>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="8"/>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
@@ -4688,7 +4738,7 @@
       <c r="M140" s="11"/>
       <c r="N140" s="12"/>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="8"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
@@ -4710,7 +4760,7 @@
       <c r="M141" s="11"/>
       <c r="N141" s="12"/>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="8"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
@@ -4732,7 +4782,7 @@
       <c r="M142" s="11"/>
       <c r="N142" s="12"/>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="8"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
@@ -4754,7 +4804,7 @@
       <c r="M143" s="11"/>
       <c r="N143" s="12"/>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="8"/>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
@@ -4776,7 +4826,7 @@
       <c r="M144" s="11"/>
       <c r="N144" s="12"/>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="8"/>
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
@@ -4798,7 +4848,7 @@
       <c r="M145" s="11"/>
       <c r="N145" s="12"/>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="8"/>
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
@@ -4820,7 +4870,7 @@
       <c r="M146" s="11"/>
       <c r="N146" s="12"/>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="8"/>
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
@@ -4842,7 +4892,7 @@
       <c r="M147" s="11"/>
       <c r="N147" s="12"/>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="8"/>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
@@ -4864,7 +4914,7 @@
       <c r="M148" s="11"/>
       <c r="N148" s="12"/>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="8"/>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
@@ -4886,7 +4936,7 @@
       <c r="M149" s="11"/>
       <c r="N149" s="12"/>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="8"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
@@ -4908,7 +4958,7 @@
       <c r="M150" s="11"/>
       <c r="N150" s="12"/>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="8"/>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
@@ -4930,7 +4980,7 @@
       <c r="M151" s="11"/>
       <c r="N151" s="12"/>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="8"/>
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
@@ -4952,7 +5002,7 @@
       <c r="M152" s="11"/>
       <c r="N152" s="12"/>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="8"/>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
@@ -4974,7 +5024,7 @@
       <c r="M153" s="11"/>
       <c r="N153" s="12"/>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="8"/>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
@@ -4996,7 +5046,7 @@
       <c r="M154" s="11"/>
       <c r="N154" s="12"/>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="8"/>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
@@ -5018,7 +5068,7 @@
       <c r="M155" s="11"/>
       <c r="N155" s="12"/>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="8"/>
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
@@ -5040,7 +5090,7 @@
       <c r="M156" s="11"/>
       <c r="N156" s="12"/>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="8"/>
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
@@ -5062,7 +5112,7 @@
       <c r="M157" s="11"/>
       <c r="N157" s="12"/>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="8"/>
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
@@ -5084,7 +5134,7 @@
       <c r="M158" s="11"/>
       <c r="N158" s="12"/>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="8"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
@@ -5106,7 +5156,7 @@
       <c r="M159" s="11"/>
       <c r="N159" s="12"/>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="8"/>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
@@ -5128,7 +5178,7 @@
       <c r="M160" s="11"/>
       <c r="N160" s="12"/>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="8"/>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
@@ -5150,7 +5200,7 @@
       <c r="M161" s="11"/>
       <c r="N161" s="12"/>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="8"/>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
@@ -5172,7 +5222,7 @@
       <c r="M162" s="11"/>
       <c r="N162" s="12"/>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="8"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
@@ -5194,7 +5244,7 @@
       <c r="M163" s="11"/>
       <c r="N163" s="12"/>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="8"/>
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
@@ -5216,7 +5266,7 @@
       <c r="M164" s="11"/>
       <c r="N164" s="12"/>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="8"/>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
@@ -5238,7 +5288,7 @@
       <c r="M165" s="11"/>
       <c r="N165" s="12"/>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="8"/>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
@@ -5260,7 +5310,7 @@
       <c r="M166" s="11"/>
       <c r="N166" s="12"/>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="8"/>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
@@ -5282,7 +5332,7 @@
       <c r="M167" s="11"/>
       <c r="N167" s="12"/>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="8"/>
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
@@ -5304,7 +5354,7 @@
       <c r="M168" s="11"/>
       <c r="N168" s="12"/>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="8"/>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
@@ -5326,7 +5376,7 @@
       <c r="M169" s="11"/>
       <c r="N169" s="12"/>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="8"/>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
@@ -5348,7 +5398,7 @@
       <c r="M170" s="11"/>
       <c r="N170" s="12"/>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="8"/>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
@@ -5370,7 +5420,7 @@
       <c r="M171" s="11"/>
       <c r="N171" s="12"/>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="8"/>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
@@ -5392,7 +5442,7 @@
       <c r="M172" s="11"/>
       <c r="N172" s="12"/>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="8"/>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
@@ -5414,7 +5464,7 @@
       <c r="M173" s="11"/>
       <c r="N173" s="12"/>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="8"/>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
@@ -5436,7 +5486,7 @@
       <c r="M174" s="11"/>
       <c r="N174" s="12"/>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="8"/>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
@@ -5458,7 +5508,7 @@
       <c r="M175" s="11"/>
       <c r="N175" s="12"/>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="8"/>
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
@@ -5480,7 +5530,7 @@
       <c r="M176" s="11"/>
       <c r="N176" s="12"/>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="8"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
@@ -5502,7 +5552,7 @@
       <c r="M177" s="11"/>
       <c r="N177" s="12"/>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="8"/>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
@@ -5524,7 +5574,7 @@
       <c r="M178" s="11"/>
       <c r="N178" s="12"/>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="8"/>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
@@ -5546,7 +5596,7 @@
       <c r="M179" s="11"/>
       <c r="N179" s="12"/>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="8"/>
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
@@ -5568,7 +5618,7 @@
       <c r="M180" s="11"/>
       <c r="N180" s="12"/>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="8"/>
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
@@ -5590,7 +5640,7 @@
       <c r="M181" s="11"/>
       <c r="N181" s="12"/>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="8"/>
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
@@ -5612,7 +5662,7 @@
       <c r="M182" s="11"/>
       <c r="N182" s="12"/>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="8"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
@@ -5634,7 +5684,7 @@
       <c r="M183" s="11"/>
       <c r="N183" s="12"/>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="8"/>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
@@ -5656,7 +5706,7 @@
       <c r="M184" s="11"/>
       <c r="N184" s="12"/>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="8"/>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
@@ -5678,7 +5728,7 @@
       <c r="M185" s="11"/>
       <c r="N185" s="12"/>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="8"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
@@ -5700,7 +5750,7 @@
       <c r="M186" s="11"/>
       <c r="N186" s="12"/>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="8"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
@@ -5722,7 +5772,7 @@
       <c r="M187" s="11"/>
       <c r="N187" s="12"/>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="8"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
@@ -5744,7 +5794,7 @@
       <c r="M188" s="11"/>
       <c r="N188" s="12"/>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="8"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
@@ -5766,7 +5816,7 @@
       <c r="M189" s="11"/>
       <c r="N189" s="12"/>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="8"/>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
@@ -5788,7 +5838,7 @@
       <c r="M190" s="11"/>
       <c r="N190" s="12"/>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="8"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
@@ -5810,7 +5860,7 @@
       <c r="M191" s="11"/>
       <c r="N191" s="12"/>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="8"/>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
@@ -5832,7 +5882,7 @@
       <c r="M192" s="11"/>
       <c r="N192" s="12"/>
     </row>
-    <row r="193" spans="1:14">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="8"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
@@ -5854,7 +5904,7 @@
       <c r="M193" s="11"/>
       <c r="N193" s="12"/>
     </row>
-    <row r="194" spans="1:14">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="8"/>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
@@ -5876,7 +5926,7 @@
       <c r="M194" s="11"/>
       <c r="N194" s="12"/>
     </row>
-    <row r="195" spans="1:14">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="8"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
@@ -5898,7 +5948,7 @@
       <c r="M195" s="11"/>
       <c r="N195" s="12"/>
     </row>
-    <row r="196" spans="1:14">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="8"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
@@ -5920,7 +5970,7 @@
       <c r="M196" s="11"/>
       <c r="N196" s="12"/>
     </row>
-    <row r="197" spans="1:14">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="8"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
@@ -5942,7 +5992,7 @@
       <c r="M197" s="11"/>
       <c r="N197" s="12"/>
     </row>
-    <row r="198" spans="1:14">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="8"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
@@ -5964,7 +6014,7 @@
       <c r="M198" s="11"/>
       <c r="N198" s="12"/>
     </row>
-    <row r="199" spans="1:14">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="8"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
@@ -5986,7 +6036,7 @@
       <c r="M199" s="11"/>
       <c r="N199" s="12"/>
     </row>
-    <row r="200" spans="1:14">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="8"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
@@ -6008,7 +6058,7 @@
       <c r="M200" s="11"/>
       <c r="N200" s="12"/>
     </row>
-    <row r="201" spans="1:14">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="8"/>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
@@ -6030,7 +6080,7 @@
       <c r="M201" s="11"/>
       <c r="N201" s="12"/>
     </row>
-    <row r="202" spans="1:14">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="8"/>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
@@ -6052,7 +6102,7 @@
       <c r="M202" s="11"/>
       <c r="N202" s="12"/>
     </row>
-    <row r="203" spans="1:14">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="8"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
@@ -6074,7 +6124,7 @@
       <c r="M203" s="11"/>
       <c r="N203" s="12"/>
     </row>
-    <row r="204" spans="1:14">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="8"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
@@ -6096,7 +6146,7 @@
       <c r="M204" s="11"/>
       <c r="N204" s="12"/>
     </row>
-    <row r="205" spans="1:14">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="8"/>
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
@@ -6118,7 +6168,7 @@
       <c r="M205" s="11"/>
       <c r="N205" s="12"/>
     </row>
-    <row r="206" spans="1:14">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="8"/>
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
@@ -6140,7 +6190,7 @@
       <c r="M206" s="11"/>
       <c r="N206" s="12"/>
     </row>
-    <row r="207" spans="1:14">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="8"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
@@ -6162,7 +6212,7 @@
       <c r="M207" s="11"/>
       <c r="N207" s="12"/>
     </row>
-    <row r="208" spans="1:14">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="8"/>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
@@ -6184,7 +6234,7 @@
       <c r="M208" s="11"/>
       <c r="N208" s="12"/>
     </row>
-    <row r="209" spans="1:14">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="8"/>
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
@@ -6206,7 +6256,7 @@
       <c r="M209" s="11"/>
       <c r="N209" s="12"/>
     </row>
-    <row r="210" spans="1:14">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="8"/>
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
@@ -6228,7 +6278,7 @@
       <c r="M210" s="11"/>
       <c r="N210" s="12"/>
     </row>
-    <row r="211" spans="1:14">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="8"/>
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
@@ -6250,7 +6300,7 @@
       <c r="M211" s="11"/>
       <c r="N211" s="12"/>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="8"/>
       <c r="B212" s="9"/>
       <c r="C212" s="9"/>
@@ -6272,7 +6322,7 @@
       <c r="M212" s="11"/>
       <c r="N212" s="12"/>
     </row>
-    <row r="213" spans="1:14">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="8"/>
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
@@ -6294,7 +6344,7 @@
       <c r="M213" s="11"/>
       <c r="N213" s="12"/>
     </row>
-    <row r="214" spans="1:14">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="8"/>
       <c r="B214" s="9"/>
       <c r="C214" s="9"/>
@@ -6316,7 +6366,7 @@
       <c r="M214" s="11"/>
       <c r="N214" s="12"/>
     </row>
-    <row r="215" spans="1:14">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="8"/>
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
@@ -6338,7 +6388,7 @@
       <c r="M215" s="11"/>
       <c r="N215" s="12"/>
     </row>
-    <row r="216" spans="1:14">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="8"/>
       <c r="B216" s="9"/>
       <c r="C216" s="9"/>
@@ -6360,7 +6410,7 @@
       <c r="M216" s="11"/>
       <c r="N216" s="12"/>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="8"/>
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
@@ -6382,7 +6432,7 @@
       <c r="M217" s="11"/>
       <c r="N217" s="12"/>
     </row>
-    <row r="218" spans="1:14">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="8"/>
       <c r="B218" s="9"/>
       <c r="C218" s="9"/>
@@ -6404,7 +6454,7 @@
       <c r="M218" s="11"/>
       <c r="N218" s="12"/>
     </row>
-    <row r="219" spans="1:14">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="8"/>
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
@@ -6426,7 +6476,7 @@
       <c r="M219" s="11"/>
       <c r="N219" s="12"/>
     </row>
-    <row r="220" spans="1:14">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="8"/>
       <c r="B220" s="9"/>
       <c r="C220" s="9"/>
@@ -6448,7 +6498,7 @@
       <c r="M220" s="11"/>
       <c r="N220" s="12"/>
     </row>
-    <row r="221" spans="1:14">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="8"/>
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
@@ -6470,7 +6520,7 @@
       <c r="M221" s="11"/>
       <c r="N221" s="12"/>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="8"/>
       <c r="B222" s="9"/>
       <c r="C222" s="9"/>
@@ -6492,7 +6542,7 @@
       <c r="M222" s="11"/>
       <c r="N222" s="12"/>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="8"/>
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
@@ -6514,7 +6564,7 @@
       <c r="M223" s="11"/>
       <c r="N223" s="12"/>
     </row>
-    <row r="224" spans="1:14">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="8"/>
       <c r="B224" s="9"/>
       <c r="C224" s="9"/>
@@ -6536,7 +6586,7 @@
       <c r="M224" s="11"/>
       <c r="N224" s="12"/>
     </row>
-    <row r="225" spans="1:14">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" s="8"/>
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
@@ -6558,7 +6608,7 @@
       <c r="M225" s="11"/>
       <c r="N225" s="12"/>
     </row>
-    <row r="226" spans="1:14">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" s="8"/>
       <c r="B226" s="9"/>
       <c r="C226" s="9"/>
@@ -6580,7 +6630,7 @@
       <c r="M226" s="11"/>
       <c r="N226" s="12"/>
     </row>
-    <row r="227" spans="1:14">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" s="8"/>
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
@@ -6602,7 +6652,7 @@
       <c r="M227" s="11"/>
       <c r="N227" s="12"/>
     </row>
-    <row r="228" spans="1:14">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" s="8"/>
       <c r="B228" s="9"/>
       <c r="C228" s="9"/>
@@ -6624,7 +6674,7 @@
       <c r="M228" s="11"/>
       <c r="N228" s="12"/>
     </row>
-    <row r="229" spans="1:14">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" s="8"/>
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
@@ -6646,7 +6696,7 @@
       <c r="M229" s="11"/>
       <c r="N229" s="12"/>
     </row>
-    <row r="230" spans="1:14">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" s="8"/>
       <c r="B230" s="9"/>
       <c r="C230" s="9"/>
@@ -6668,7 +6718,7 @@
       <c r="M230" s="11"/>
       <c r="N230" s="12"/>
     </row>
-    <row r="231" spans="1:14">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" s="8"/>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
@@ -6690,7 +6740,7 @@
       <c r="M231" s="11"/>
       <c r="N231" s="12"/>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" s="8"/>
       <c r="B232" s="9"/>
       <c r="C232" s="9"/>
@@ -6712,7 +6762,7 @@
       <c r="M232" s="11"/>
       <c r="N232" s="12"/>
     </row>
-    <row r="233" spans="1:14">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" s="8"/>
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
@@ -6734,7 +6784,7 @@
       <c r="M233" s="11"/>
       <c r="N233" s="12"/>
     </row>
-    <row r="234" spans="1:14">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="8"/>
       <c r="B234" s="9"/>
       <c r="C234" s="9"/>
@@ -6756,7 +6806,7 @@
       <c r="M234" s="11"/>
       <c r="N234" s="12"/>
     </row>
-    <row r="235" spans="1:14">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="8"/>
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
@@ -6778,7 +6828,7 @@
       <c r="M235" s="11"/>
       <c r="N235" s="12"/>
     </row>
-    <row r="236" spans="1:14">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="8"/>
       <c r="B236" s="9"/>
       <c r="C236" s="9"/>
@@ -6800,7 +6850,7 @@
       <c r="M236" s="11"/>
       <c r="N236" s="12"/>
     </row>
-    <row r="237" spans="1:14">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" s="8"/>
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
@@ -6822,7 +6872,7 @@
       <c r="M237" s="11"/>
       <c r="N237" s="12"/>
     </row>
-    <row r="238" spans="1:14">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" s="8"/>
       <c r="B238" s="9"/>
       <c r="C238" s="9"/>
@@ -6844,7 +6894,7 @@
       <c r="M238" s="11"/>
       <c r="N238" s="12"/>
     </row>
-    <row r="239" spans="1:14">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" s="8"/>
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
@@ -6866,7 +6916,7 @@
       <c r="M239" s="11"/>
       <c r="N239" s="12"/>
     </row>
-    <row r="240" spans="1:14">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" s="8"/>
       <c r="B240" s="9"/>
       <c r="C240" s="9"/>
@@ -6888,7 +6938,7 @@
       <c r="M240" s="11"/>
       <c r="N240" s="12"/>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" s="8"/>
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
@@ -6910,7 +6960,7 @@
       <c r="M241" s="11"/>
       <c r="N241" s="12"/>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" s="8"/>
       <c r="B242" s="9"/>
       <c r="C242" s="9"/>
@@ -6932,7 +6982,7 @@
       <c r="M242" s="11"/>
       <c r="N242" s="12"/>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" s="8"/>
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
@@ -6954,7 +7004,7 @@
       <c r="M243" s="11"/>
       <c r="N243" s="12"/>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" s="8"/>
       <c r="B244" s="9"/>
       <c r="C244" s="9"/>
@@ -6976,7 +7026,7 @@
       <c r="M244" s="11"/>
       <c r="N244" s="12"/>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" s="8"/>
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
@@ -6998,7 +7048,7 @@
       <c r="M245" s="11"/>
       <c r="N245" s="12"/>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" s="8"/>
       <c r="B246" s="9"/>
       <c r="C246" s="9"/>
@@ -7020,7 +7070,7 @@
       <c r="M246" s="11"/>
       <c r="N246" s="12"/>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" s="8"/>
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
@@ -7042,7 +7092,7 @@
       <c r="M247" s="11"/>
       <c r="N247" s="12"/>
     </row>
-    <row r="248" spans="1:14">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" s="8"/>
       <c r="B248" s="9"/>
       <c r="C248" s="9"/>
@@ -7064,7 +7114,7 @@
       <c r="M248" s="11"/>
       <c r="N248" s="12"/>
     </row>
-    <row r="249" spans="1:14">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" s="8"/>
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
@@ -7086,7 +7136,7 @@
       <c r="M249" s="11"/>
       <c r="N249" s="12"/>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" s="8"/>
       <c r="B250" s="9"/>
       <c r="C250" s="9"/>
@@ -7108,7 +7158,7 @@
       <c r="M250" s="11"/>
       <c r="N250" s="12"/>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" s="8"/>
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
@@ -7130,7 +7180,7 @@
       <c r="M251" s="11"/>
       <c r="N251" s="12"/>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" s="8"/>
       <c r="B252" s="9"/>
       <c r="C252" s="9"/>
@@ -7152,7 +7202,7 @@
       <c r="M252" s="11"/>
       <c r="N252" s="12"/>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" s="8"/>
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
@@ -7174,7 +7224,7 @@
       <c r="M253" s="11"/>
       <c r="N253" s="12"/>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" s="8"/>
       <c r="B254" s="9"/>
       <c r="C254" s="9"/>
@@ -7196,7 +7246,7 @@
       <c r="M254" s="11"/>
       <c r="N254" s="12"/>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" s="8"/>
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
@@ -7218,7 +7268,7 @@
       <c r="M255" s="11"/>
       <c r="N255" s="12"/>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" s="8"/>
       <c r="B256" s="9"/>
       <c r="C256" s="9"/>
@@ -7240,7 +7290,7 @@
       <c r="M256" s="11"/>
       <c r="N256" s="12"/>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" s="8"/>
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
@@ -7262,7 +7312,7 @@
       <c r="M257" s="11"/>
       <c r="N257" s="12"/>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" s="8"/>
       <c r="B258" s="9"/>
       <c r="C258" s="9"/>
@@ -7284,7 +7334,7 @@
       <c r="M258" s="11"/>
       <c r="N258" s="12"/>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" s="8"/>
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
@@ -7306,7 +7356,7 @@
       <c r="M259" s="11"/>
       <c r="N259" s="12"/>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" s="8"/>
       <c r="B260" s="9"/>
       <c r="C260" s="9"/>
@@ -7328,7 +7378,7 @@
       <c r="M260" s="11"/>
       <c r="N260" s="12"/>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" s="8"/>
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
@@ -7350,7 +7400,7 @@
       <c r="M261" s="11"/>
       <c r="N261" s="12"/>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" s="8"/>
       <c r="B262" s="9"/>
       <c r="C262" s="9"/>
@@ -7372,7 +7422,7 @@
       <c r="M262" s="11"/>
       <c r="N262" s="12"/>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" s="8"/>
       <c r="B263" s="9"/>
       <c r="C263" s="9"/>
@@ -7394,7 +7444,7 @@
       <c r="M263" s="11"/>
       <c r="N263" s="12"/>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" s="8"/>
       <c r="B264" s="9"/>
       <c r="C264" s="9"/>
@@ -7416,7 +7466,7 @@
       <c r="M264" s="11"/>
       <c r="N264" s="12"/>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" s="8"/>
       <c r="B265" s="9"/>
       <c r="C265" s="9"/>
@@ -7438,7 +7488,7 @@
       <c r="M265" s="11"/>
       <c r="N265" s="12"/>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" s="8"/>
       <c r="B266" s="9"/>
       <c r="C266" s="9"/>
@@ -7460,7 +7510,7 @@
       <c r="M266" s="11"/>
       <c r="N266" s="12"/>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" s="8"/>
       <c r="B267" s="9"/>
       <c r="C267" s="9"/>
@@ -7482,7 +7532,7 @@
       <c r="M267" s="11"/>
       <c r="N267" s="12"/>
     </row>
-    <row r="268" spans="1:14">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" s="8"/>
       <c r="B268" s="9"/>
       <c r="C268" s="9"/>
@@ -7504,7 +7554,7 @@
       <c r="M268" s="11"/>
       <c r="N268" s="12"/>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" s="8"/>
       <c r="B269" s="9"/>
       <c r="C269" s="9"/>
@@ -7526,7 +7576,7 @@
       <c r="M269" s="11"/>
       <c r="N269" s="12"/>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" s="8"/>
       <c r="B270" s="9"/>
       <c r="C270" s="9"/>
@@ -7548,7 +7598,7 @@
       <c r="M270" s="11"/>
       <c r="N270" s="12"/>
     </row>
-    <row r="271" spans="1:14">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" s="8"/>
       <c r="B271" s="9"/>
       <c r="C271" s="9"/>
@@ -7570,7 +7620,7 @@
       <c r="M271" s="11"/>
       <c r="N271" s="12"/>
     </row>
-    <row r="272" spans="1:14">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" s="8"/>
       <c r="B272" s="9"/>
       <c r="C272" s="9"/>
@@ -7592,7 +7642,7 @@
       <c r="M272" s="11"/>
       <c r="N272" s="12"/>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" s="8"/>
       <c r="B273" s="9"/>
       <c r="C273" s="9"/>
@@ -7614,7 +7664,7 @@
       <c r="M273" s="11"/>
       <c r="N273" s="12"/>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" s="8"/>
       <c r="B274" s="9"/>
       <c r="C274" s="9"/>
@@ -7636,7 +7686,7 @@
       <c r="M274" s="11"/>
       <c r="N274" s="12"/>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" s="8"/>
       <c r="B275" s="9"/>
       <c r="C275" s="9"/>
@@ -7658,7 +7708,7 @@
       <c r="M275" s="11"/>
       <c r="N275" s="12"/>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" s="8"/>
       <c r="B276" s="9"/>
       <c r="C276" s="9"/>
@@ -7680,7 +7730,7 @@
       <c r="M276" s="11"/>
       <c r="N276" s="12"/>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" s="8"/>
       <c r="B277" s="9"/>
       <c r="C277" s="9"/>
@@ -7702,7 +7752,7 @@
       <c r="M277" s="11"/>
       <c r="N277" s="12"/>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" s="8"/>
       <c r="B278" s="9"/>
       <c r="C278" s="9"/>
@@ -7724,7 +7774,7 @@
       <c r="M278" s="11"/>
       <c r="N278" s="12"/>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" s="8"/>
       <c r="B279" s="9"/>
       <c r="C279" s="9"/>
@@ -7746,7 +7796,7 @@
       <c r="M279" s="11"/>
       <c r="N279" s="12"/>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" s="8"/>
       <c r="B280" s="9"/>
       <c r="C280" s="9"/>
@@ -7768,7 +7818,7 @@
       <c r="M280" s="11"/>
       <c r="N280" s="12"/>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" s="8"/>
       <c r="B281" s="9"/>
       <c r="C281" s="9"/>
@@ -7790,7 +7840,7 @@
       <c r="M281" s="11"/>
       <c r="N281" s="12"/>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" s="8"/>
       <c r="B282" s="9"/>
       <c r="C282" s="9"/>
@@ -7812,7 +7862,7 @@
       <c r="M282" s="11"/>
       <c r="N282" s="12"/>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" s="8"/>
       <c r="B283" s="9"/>
       <c r="C283" s="9"/>
@@ -7834,7 +7884,7 @@
       <c r="M283" s="11"/>
       <c r="N283" s="12"/>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" s="8"/>
       <c r="B284" s="9"/>
       <c r="C284" s="9"/>
@@ -7856,7 +7906,7 @@
       <c r="M284" s="11"/>
       <c r="N284" s="12"/>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" s="8"/>
       <c r="B285" s="9"/>
       <c r="C285" s="9"/>
@@ -7878,7 +7928,7 @@
       <c r="M285" s="11"/>
       <c r="N285" s="12"/>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" s="8"/>
       <c r="B286" s="9"/>
       <c r="C286" s="9"/>
@@ -7900,7 +7950,7 @@
       <c r="M286" s="11"/>
       <c r="N286" s="12"/>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" s="8"/>
       <c r="B287" s="9"/>
       <c r="C287" s="9"/>
@@ -7922,7 +7972,7 @@
       <c r="M287" s="11"/>
       <c r="N287" s="12"/>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" s="8"/>
       <c r="B288" s="9"/>
       <c r="C288" s="9"/>
@@ -7944,7 +7994,7 @@
       <c r="M288" s="11"/>
       <c r="N288" s="12"/>
     </row>
-    <row r="289" spans="1:14">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="8"/>
       <c r="B289" s="9"/>
       <c r="C289" s="9"/>
@@ -7966,7 +8016,7 @@
       <c r="M289" s="11"/>
       <c r="N289" s="12"/>
     </row>
-    <row r="290" spans="1:14">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="8"/>
       <c r="B290" s="9"/>
       <c r="C290" s="9"/>
@@ -7988,7 +8038,7 @@
       <c r="M290" s="11"/>
       <c r="N290" s="12"/>
     </row>
-    <row r="291" spans="1:14">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="8"/>
       <c r="B291" s="9"/>
       <c r="C291" s="9"/>
@@ -8010,7 +8060,7 @@
       <c r="M291" s="11"/>
       <c r="N291" s="12"/>
     </row>
-    <row r="292" spans="1:14">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="8"/>
       <c r="B292" s="9"/>
       <c r="C292" s="9"/>
@@ -8032,7 +8082,7 @@
       <c r="M292" s="11"/>
       <c r="N292" s="12"/>
     </row>
-    <row r="293" spans="1:14">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="8"/>
       <c r="B293" s="9"/>
       <c r="C293" s="9"/>
@@ -8054,7 +8104,7 @@
       <c r="M293" s="11"/>
       <c r="N293" s="12"/>
     </row>
-    <row r="294" spans="1:14">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="8"/>
       <c r="B294" s="9"/>
       <c r="C294" s="9"/>
@@ -8076,7 +8126,7 @@
       <c r="M294" s="11"/>
       <c r="N294" s="12"/>
     </row>
-    <row r="295" spans="1:14">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="8"/>
       <c r="B295" s="9"/>
       <c r="C295" s="9"/>
@@ -8098,7 +8148,7 @@
       <c r="M295" s="11"/>
       <c r="N295" s="12"/>
     </row>
-    <row r="296" spans="1:14">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="8"/>
       <c r="B296" s="9"/>
       <c r="C296" s="9"/>
@@ -8120,7 +8170,7 @@
       <c r="M296" s="11"/>
       <c r="N296" s="12"/>
     </row>
-    <row r="297" spans="1:14">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="8"/>
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
@@ -8142,7 +8192,7 @@
       <c r="M297" s="11"/>
       <c r="N297" s="12"/>
     </row>
-    <row r="298" spans="1:14">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="8"/>
       <c r="B298" s="9"/>
       <c r="C298" s="9"/>
@@ -8164,7 +8214,7 @@
       <c r="M298" s="11"/>
       <c r="N298" s="12"/>
     </row>
-    <row r="299" spans="1:14">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="8"/>
       <c r="B299" s="9"/>
       <c r="C299" s="9"/>
@@ -8186,7 +8236,7 @@
       <c r="M299" s="11"/>
       <c r="N299" s="12"/>
     </row>
-    <row r="300" spans="1:14">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="8"/>
       <c r="B300" s="9"/>
       <c r="C300" s="9"/>
@@ -8208,7 +8258,7 @@
       <c r="M300" s="11"/>
       <c r="N300" s="12"/>
     </row>
-    <row r="301" spans="1:14">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" s="8"/>
       <c r="B301" s="9"/>
       <c r="C301" s="9"/>
@@ -8230,7 +8280,7 @@
       <c r="M301" s="11"/>
       <c r="N301" s="12"/>
     </row>
-    <row r="302" spans="1:14">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="8"/>
       <c r="B302" s="9"/>
       <c r="C302" s="9"/>
@@ -8252,7 +8302,7 @@
       <c r="M302" s="11"/>
       <c r="N302" s="12"/>
     </row>
-    <row r="303" spans="1:14">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="8"/>
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
@@ -8274,7 +8324,7 @@
       <c r="M303" s="11"/>
       <c r="N303" s="12"/>
     </row>
-    <row r="304" spans="1:14">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="8"/>
       <c r="B304" s="9"/>
       <c r="C304" s="9"/>
@@ -8296,7 +8346,7 @@
       <c r="M304" s="11"/>
       <c r="N304" s="12"/>
     </row>
-    <row r="305" spans="1:14">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="8"/>
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
@@ -8318,7 +8368,7 @@
       <c r="M305" s="11"/>
       <c r="N305" s="12"/>
     </row>
-    <row r="306" spans="1:14">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="8"/>
       <c r="B306" s="9"/>
       <c r="C306" s="9"/>
@@ -8340,7 +8390,7 @@
       <c r="M306" s="11"/>
       <c r="N306" s="12"/>
     </row>
-    <row r="307" spans="1:14">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="8"/>
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
@@ -8362,7 +8412,7 @@
       <c r="M307" s="11"/>
       <c r="N307" s="12"/>
     </row>
-    <row r="308" spans="1:14">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" s="8"/>
       <c r="B308" s="9"/>
       <c r="C308" s="9"/>
@@ -8384,7 +8434,7 @@
       <c r="M308" s="11"/>
       <c r="N308" s="12"/>
     </row>
-    <row r="309" spans="1:14">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" s="8"/>
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
@@ -8406,7 +8456,7 @@
       <c r="M309" s="11"/>
       <c r="N309" s="12"/>
     </row>
-    <row r="310" spans="1:14">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="8"/>
       <c r="B310" s="9"/>
       <c r="C310" s="9"/>
@@ -8428,7 +8478,7 @@
       <c r="M310" s="11"/>
       <c r="N310" s="12"/>
     </row>
-    <row r="311" spans="1:14">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" s="8"/>
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
@@ -8450,7 +8500,7 @@
       <c r="M311" s="11"/>
       <c r="N311" s="12"/>
     </row>
-    <row r="312" spans="1:14">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" s="8"/>
       <c r="B312" s="9"/>
       <c r="C312" s="9"/>
@@ -8472,7 +8522,7 @@
       <c r="M312" s="11"/>
       <c r="N312" s="12"/>
     </row>
-    <row r="313" spans="1:14">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" s="8"/>
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
@@ -8494,7 +8544,7 @@
       <c r="M313" s="11"/>
       <c r="N313" s="12"/>
     </row>
-    <row r="314" spans="1:14">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" s="8"/>
       <c r="B314" s="9"/>
       <c r="C314" s="9"/>
@@ -8516,7 +8566,7 @@
       <c r="M314" s="11"/>
       <c r="N314" s="12"/>
     </row>
-    <row r="315" spans="1:14">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="8"/>
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
@@ -8538,7 +8588,7 @@
       <c r="M315" s="11"/>
       <c r="N315" s="12"/>
     </row>
-    <row r="316" spans="1:14">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" s="8"/>
       <c r="B316" s="9"/>
       <c r="C316" s="9"/>
@@ -8560,7 +8610,7 @@
       <c r="M316" s="11"/>
       <c r="N316" s="12"/>
     </row>
-    <row r="317" spans="1:14">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" s="8"/>
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
@@ -8582,7 +8632,7 @@
       <c r="M317" s="11"/>
       <c r="N317" s="12"/>
     </row>
-    <row r="318" spans="1:14">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" s="8"/>
       <c r="B318" s="9"/>
       <c r="C318" s="9"/>
@@ -8604,7 +8654,7 @@
       <c r="M318" s="11"/>
       <c r="N318" s="12"/>
     </row>
-    <row r="319" spans="1:14">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" s="8"/>
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
@@ -8626,7 +8676,7 @@
       <c r="M319" s="11"/>
       <c r="N319" s="12"/>
     </row>
-    <row r="320" spans="1:14">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" s="8"/>
       <c r="B320" s="9"/>
       <c r="C320" s="9"/>
@@ -8648,7 +8698,7 @@
       <c r="M320" s="11"/>
       <c r="N320" s="12"/>
     </row>
-    <row r="321" spans="1:14">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A321" s="8"/>
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
@@ -8670,7 +8720,7 @@
       <c r="M321" s="11"/>
       <c r="N321" s="12"/>
     </row>
-    <row r="322" spans="1:14">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A322" s="8"/>
       <c r="B322" s="9"/>
       <c r="C322" s="9"/>
@@ -8692,7 +8742,7 @@
       <c r="M322" s="11"/>
       <c r="N322" s="12"/>
     </row>
-    <row r="323" spans="1:14">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A323" s="8"/>
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
@@ -8714,7 +8764,7 @@
       <c r="M323" s="11"/>
       <c r="N323" s="12"/>
     </row>
-    <row r="324" spans="1:14">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A324" s="8"/>
       <c r="B324" s="9"/>
       <c r="C324" s="9"/>
@@ -8736,7 +8786,7 @@
       <c r="M324" s="11"/>
       <c r="N324" s="12"/>
     </row>
-    <row r="325" spans="1:14">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" s="8"/>
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
@@ -8758,7 +8808,7 @@
       <c r="M325" s="11"/>
       <c r="N325" s="12"/>
     </row>
-    <row r="326" spans="1:14">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A326" s="8"/>
       <c r="B326" s="9"/>
       <c r="C326" s="9"/>
@@ -8780,7 +8830,7 @@
       <c r="M326" s="11"/>
       <c r="N326" s="12"/>
     </row>
-    <row r="327" spans="1:14">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A327" s="8"/>
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
@@ -8802,7 +8852,7 @@
       <c r="M327" s="11"/>
       <c r="N327" s="12"/>
     </row>
-    <row r="328" spans="1:14">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A328" s="8"/>
       <c r="B328" s="9"/>
       <c r="C328" s="9"/>
@@ -8824,7 +8874,7 @@
       <c r="M328" s="11"/>
       <c r="N328" s="12"/>
     </row>
-    <row r="329" spans="1:14">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A329" s="8"/>
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
@@ -8846,7 +8896,7 @@
       <c r="M329" s="11"/>
       <c r="N329" s="12"/>
     </row>
-    <row r="330" spans="1:14">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" s="8"/>
       <c r="B330" s="9"/>
       <c r="C330" s="9"/>
@@ -8868,7 +8918,7 @@
       <c r="M330" s="11"/>
       <c r="N330" s="12"/>
     </row>
-    <row r="331" spans="1:14">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A331" s="8"/>
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
@@ -8890,7 +8940,7 @@
       <c r="M331" s="11"/>
       <c r="N331" s="12"/>
     </row>
-    <row r="332" spans="1:14">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A332" s="8"/>
       <c r="B332" s="9"/>
       <c r="C332" s="9"/>
@@ -8912,7 +8962,7 @@
       <c r="M332" s="11"/>
       <c r="N332" s="12"/>
     </row>
-    <row r="333" spans="1:14">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A333" s="8"/>
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
@@ -8934,7 +8984,7 @@
       <c r="M333" s="11"/>
       <c r="N333" s="12"/>
     </row>
-    <row r="334" spans="1:14">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A334" s="8"/>
       <c r="B334" s="9"/>
       <c r="C334" s="9"/>
@@ -8956,7 +9006,7 @@
       <c r="M334" s="11"/>
       <c r="N334" s="12"/>
     </row>
-    <row r="335" spans="1:14">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A335" s="8"/>
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
@@ -8978,7 +9028,7 @@
       <c r="M335" s="11"/>
       <c r="N335" s="12"/>
     </row>
-    <row r="336" spans="1:14">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A336" s="8"/>
       <c r="B336" s="9"/>
       <c r="C336" s="9"/>
@@ -9000,7 +9050,7 @@
       <c r="M336" s="11"/>
       <c r="N336" s="12"/>
     </row>
-    <row r="337" spans="1:14">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A337" s="8"/>
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
@@ -9022,7 +9072,7 @@
       <c r="M337" s="11"/>
       <c r="N337" s="12"/>
     </row>
-    <row r="338" spans="1:14">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A338" s="8"/>
       <c r="B338" s="9"/>
       <c r="C338" s="9"/>
@@ -9044,7 +9094,7 @@
       <c r="M338" s="11"/>
       <c r="N338" s="12"/>
     </row>
-    <row r="339" spans="1:14">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A339" s="8"/>
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
@@ -9066,7 +9116,7 @@
       <c r="M339" s="11"/>
       <c r="N339" s="12"/>
     </row>
-    <row r="340" spans="1:14">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A340" s="8"/>
       <c r="B340" s="9"/>
       <c r="C340" s="9"/>
@@ -9088,7 +9138,7 @@
       <c r="M340" s="11"/>
       <c r="N340" s="12"/>
     </row>
-    <row r="341" spans="1:14">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A341" s="8"/>
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
@@ -9110,7 +9160,7 @@
       <c r="M341" s="11"/>
       <c r="N341" s="12"/>
     </row>
-    <row r="342" spans="1:14">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A342" s="8"/>
       <c r="B342" s="9"/>
       <c r="C342" s="9"/>
@@ -9132,7 +9182,7 @@
       <c r="M342" s="11"/>
       <c r="N342" s="12"/>
     </row>
-    <row r="343" spans="1:14">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A343" s="8"/>
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
@@ -9154,7 +9204,7 @@
       <c r="M343" s="11"/>
       <c r="N343" s="12"/>
     </row>
-    <row r="344" spans="1:14">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A344" s="8"/>
       <c r="B344" s="9"/>
       <c r="C344" s="9"/>
@@ -9176,7 +9226,7 @@
       <c r="M344" s="11"/>
       <c r="N344" s="12"/>
     </row>
-    <row r="345" spans="1:14">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A345" s="8"/>
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
@@ -9198,7 +9248,7 @@
       <c r="M345" s="11"/>
       <c r="N345" s="12"/>
     </row>
-    <row r="346" spans="1:14">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A346" s="8"/>
       <c r="B346" s="9"/>
       <c r="C346" s="9"/>
@@ -9220,7 +9270,7 @@
       <c r="M346" s="11"/>
       <c r="N346" s="12"/>
     </row>
-    <row r="347" spans="1:14">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A347" s="8"/>
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
@@ -9242,7 +9292,7 @@
       <c r="M347" s="11"/>
       <c r="N347" s="12"/>
     </row>
-    <row r="348" spans="1:14">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A348" s="8"/>
       <c r="B348" s="9"/>
       <c r="C348" s="9"/>
@@ -9264,7 +9314,7 @@
       <c r="M348" s="11"/>
       <c r="N348" s="12"/>
     </row>
-    <row r="349" spans="1:14">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A349" s="8"/>
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
@@ -9286,7 +9336,7 @@
       <c r="M349" s="11"/>
       <c r="N349" s="12"/>
     </row>
-    <row r="350" spans="1:14">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A350" s="8"/>
       <c r="B350" s="9"/>
       <c r="C350" s="9"/>
@@ -9308,7 +9358,7 @@
       <c r="M350" s="11"/>
       <c r="N350" s="12"/>
     </row>
-    <row r="351" spans="1:14">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A351" s="8"/>
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
@@ -9330,7 +9380,7 @@
       <c r="M351" s="11"/>
       <c r="N351" s="12"/>
     </row>
-    <row r="352" spans="1:14">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A352" s="8"/>
       <c r="B352" s="9"/>
       <c r="C352" s="9"/>
@@ -9352,7 +9402,7 @@
       <c r="M352" s="11"/>
       <c r="N352" s="12"/>
     </row>
-    <row r="353" spans="1:14">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A353" s="8"/>
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
@@ -9374,7 +9424,7 @@
       <c r="M353" s="11"/>
       <c r="N353" s="12"/>
     </row>
-    <row r="354" spans="1:14">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A354" s="8"/>
       <c r="B354" s="9"/>
       <c r="C354" s="9"/>
@@ -9396,7 +9446,7 @@
       <c r="M354" s="11"/>
       <c r="N354" s="12"/>
     </row>
-    <row r="355" spans="1:14">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A355" s="8"/>
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
@@ -9418,7 +9468,7 @@
       <c r="M355" s="11"/>
       <c r="N355" s="12"/>
     </row>
-    <row r="356" spans="1:14">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A356" s="8"/>
       <c r="B356" s="9"/>
       <c r="C356" s="9"/>
@@ -9440,7 +9490,7 @@
       <c r="M356" s="11"/>
       <c r="N356" s="12"/>
     </row>
-    <row r="357" spans="1:14">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A357" s="8"/>
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
@@ -9462,7 +9512,7 @@
       <c r="M357" s="11"/>
       <c r="N357" s="12"/>
     </row>
-    <row r="358" spans="1:14">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A358" s="8"/>
       <c r="B358" s="9"/>
       <c r="C358" s="9"/>
@@ -9484,7 +9534,7 @@
       <c r="M358" s="11"/>
       <c r="N358" s="12"/>
     </row>
-    <row r="359" spans="1:14">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A359" s="8"/>
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
@@ -9506,7 +9556,7 @@
       <c r="M359" s="11"/>
       <c r="N359" s="12"/>
     </row>
-    <row r="360" spans="1:14">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A360" s="8"/>
       <c r="B360" s="9"/>
       <c r="C360" s="9"/>
@@ -9528,7 +9578,7 @@
       <c r="M360" s="11"/>
       <c r="N360" s="12"/>
     </row>
-    <row r="361" spans="1:14">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A361" s="8"/>
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
@@ -9550,7 +9600,7 @@
       <c r="M361" s="11"/>
       <c r="N361" s="12"/>
     </row>
-    <row r="362" spans="1:14">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A362" s="8"/>
       <c r="B362" s="9"/>
       <c r="C362" s="9"/>
@@ -9572,7 +9622,7 @@
       <c r="M362" s="11"/>
       <c r="N362" s="12"/>
     </row>
-    <row r="363" spans="1:14">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A363" s="8"/>
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
@@ -9594,7 +9644,7 @@
       <c r="M363" s="11"/>
       <c r="N363" s="12"/>
     </row>
-    <row r="364" spans="1:14">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A364" s="8"/>
       <c r="B364" s="9"/>
       <c r="C364" s="9"/>
@@ -9616,7 +9666,7 @@
       <c r="M364" s="11"/>
       <c r="N364" s="12"/>
     </row>
-    <row r="365" spans="1:14">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A365" s="8"/>
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
@@ -9638,7 +9688,7 @@
       <c r="M365" s="11"/>
       <c r="N365" s="12"/>
     </row>
-    <row r="366" spans="1:14">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A366" s="8"/>
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
@@ -9660,7 +9710,7 @@
       <c r="M366" s="11"/>
       <c r="N366" s="12"/>
     </row>
-    <row r="367" spans="1:14">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A367" s="8"/>
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
@@ -9682,7 +9732,7 @@
       <c r="M367" s="11"/>
       <c r="N367" s="12"/>
     </row>
-    <row r="368" spans="1:14">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
       <c r="C368" s="9"/>
@@ -9704,7 +9754,7 @@
       <c r="M368" s="11"/>
       <c r="N368" s="12"/>
     </row>
-    <row r="369" spans="1:14">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A369" s="8"/>
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
@@ -9726,7 +9776,7 @@
       <c r="M369" s="11"/>
       <c r="N369" s="12"/>
     </row>
-    <row r="370" spans="1:14">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A370" s="8"/>
       <c r="B370" s="9"/>
       <c r="C370" s="9"/>
@@ -9748,7 +9798,7 @@
       <c r="M370" s="11"/>
       <c r="N370" s="12"/>
     </row>
-    <row r="371" spans="1:14">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A371" s="8"/>
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
@@ -9770,7 +9820,7 @@
       <c r="M371" s="11"/>
       <c r="N371" s="12"/>
     </row>
-    <row r="372" spans="1:14">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A372" s="8"/>
       <c r="B372" s="9"/>
       <c r="C372" s="9"/>
@@ -9792,7 +9842,7 @@
       <c r="M372" s="11"/>
       <c r="N372" s="12"/>
     </row>
-    <row r="373" spans="1:14">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A373" s="8"/>
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
@@ -9814,7 +9864,7 @@
       <c r="M373" s="11"/>
       <c r="N373" s="12"/>
     </row>
-    <row r="374" spans="1:14">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A374" s="8"/>
       <c r="B374" s="9"/>
       <c r="C374" s="9"/>
@@ -9836,7 +9886,7 @@
       <c r="M374" s="11"/>
       <c r="N374" s="12"/>
     </row>
-    <row r="375" spans="1:14">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A375" s="8"/>
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
@@ -9858,7 +9908,7 @@
       <c r="M375" s="11"/>
       <c r="N375" s="12"/>
     </row>
-    <row r="376" spans="1:14">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A376" s="8"/>
       <c r="B376" s="9"/>
       <c r="C376" s="9"/>
@@ -9880,7 +9930,7 @@
       <c r="M376" s="11"/>
       <c r="N376" s="12"/>
     </row>
-    <row r="377" spans="1:14">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A377" s="8"/>
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
@@ -9902,7 +9952,7 @@
       <c r="M377" s="11"/>
       <c r="N377" s="12"/>
     </row>
-    <row r="378" spans="1:14">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A378" s="8"/>
       <c r="B378" s="9"/>
       <c r="C378" s="9"/>
@@ -9924,7 +9974,7 @@
       <c r="M378" s="11"/>
       <c r="N378" s="12"/>
     </row>
-    <row r="379" spans="1:14">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A379" s="8"/>
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
@@ -9946,7 +9996,7 @@
       <c r="M379" s="11"/>
       <c r="N379" s="12"/>
     </row>
-    <row r="380" spans="1:14">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A380" s="8"/>
       <c r="B380" s="9"/>
       <c r="C380" s="9"/>
@@ -9968,7 +10018,7 @@
       <c r="M380" s="11"/>
       <c r="N380" s="12"/>
     </row>
-    <row r="381" spans="1:14">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A381" s="8"/>
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
@@ -9990,7 +10040,7 @@
       <c r="M381" s="11"/>
       <c r="N381" s="12"/>
     </row>
-    <row r="382" spans="1:14">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A382" s="8"/>
       <c r="B382" s="9"/>
       <c r="C382" s="9"/>
@@ -10012,7 +10062,7 @@
       <c r="M382" s="11"/>
       <c r="N382" s="12"/>
     </row>
-    <row r="383" spans="1:14">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A383" s="8"/>
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
@@ -10034,7 +10084,7 @@
       <c r="M383" s="11"/>
       <c r="N383" s="12"/>
     </row>
-    <row r="384" spans="1:14">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A384" s="8"/>
       <c r="B384" s="9"/>
       <c r="C384" s="9"/>
@@ -10056,7 +10106,7 @@
       <c r="M384" s="11"/>
       <c r="N384" s="12"/>
     </row>
-    <row r="385" spans="1:14">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A385" s="8"/>
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
@@ -10078,7 +10128,7 @@
       <c r="M385" s="11"/>
       <c r="N385" s="12"/>
     </row>
-    <row r="386" spans="1:14">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A386" s="8"/>
       <c r="B386" s="9"/>
       <c r="C386" s="9"/>
@@ -10100,7 +10150,7 @@
       <c r="M386" s="11"/>
       <c r="N386" s="12"/>
     </row>
-    <row r="387" spans="1:14">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A387" s="8"/>
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
@@ -10122,7 +10172,7 @@
       <c r="M387" s="11"/>
       <c r="N387" s="12"/>
     </row>
-    <row r="388" spans="1:14">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A388" s="8"/>
       <c r="B388" s="9"/>
       <c r="C388" s="9"/>
@@ -10144,7 +10194,7 @@
       <c r="M388" s="11"/>
       <c r="N388" s="12"/>
     </row>
-    <row r="389" spans="1:14">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A389" s="8"/>
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
@@ -10166,7 +10216,7 @@
       <c r="M389" s="11"/>
       <c r="N389" s="12"/>
     </row>
-    <row r="390" spans="1:14">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A390" s="8"/>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
@@ -10188,7 +10238,7 @@
       <c r="M390" s="11"/>
       <c r="N390" s="12"/>
     </row>
-    <row r="391" spans="1:14">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A391" s="8"/>
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
@@ -10210,7 +10260,7 @@
       <c r="M391" s="11"/>
       <c r="N391" s="12"/>
     </row>
-    <row r="392" spans="1:14">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A392" s="8"/>
       <c r="B392" s="9"/>
       <c r="C392" s="9"/>
@@ -10232,7 +10282,7 @@
       <c r="M392" s="11"/>
       <c r="N392" s="12"/>
     </row>
-    <row r="393" spans="1:14">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A393" s="8"/>
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
@@ -10254,7 +10304,7 @@
       <c r="M393" s="11"/>
       <c r="N393" s="12"/>
     </row>
-    <row r="394" spans="1:14">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A394" s="8"/>
       <c r="B394" s="9"/>
       <c r="C394" s="9"/>
@@ -10276,7 +10326,7 @@
       <c r="M394" s="11"/>
       <c r="N394" s="12"/>
     </row>
-    <row r="395" spans="1:14">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A395" s="8"/>
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
@@ -10298,7 +10348,7 @@
       <c r="M395" s="11"/>
       <c r="N395" s="12"/>
     </row>
-    <row r="396" spans="1:14">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A396" s="8"/>
       <c r="B396" s="9"/>
       <c r="C396" s="9"/>
@@ -10320,7 +10370,7 @@
       <c r="M396" s="11"/>
       <c r="N396" s="12"/>
     </row>
-    <row r="397" spans="1:14">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A397" s="8"/>
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
@@ -10342,7 +10392,7 @@
       <c r="M397" s="11"/>
       <c r="N397" s="12"/>
     </row>
-    <row r="398" spans="1:14">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A398" s="8"/>
       <c r="B398" s="9"/>
       <c r="C398" s="9"/>
@@ -10364,7 +10414,7 @@
       <c r="M398" s="11"/>
       <c r="N398" s="12"/>
     </row>
-    <row r="399" spans="1:14">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A399" s="8"/>
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
@@ -10386,7 +10436,7 @@
       <c r="M399" s="11"/>
       <c r="N399" s="12"/>
     </row>
-    <row r="400" spans="1:14">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A400" s="8"/>
       <c r="B400" s="9"/>
       <c r="C400" s="9"/>
@@ -10408,7 +10458,7 @@
       <c r="M400" s="11"/>
       <c r="N400" s="12"/>
     </row>
-    <row r="401" spans="1:14">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A401" s="8"/>
       <c r="B401" s="9"/>
       <c r="C401" s="9"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144F487E-D2F8-495A-A3D8-26F725EBD1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBB2A61-DAF2-41FD-89E0-703F94C8E2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,12 @@
   </si>
   <si>
     <t>Felt dizzy for the whole day and low as well. Not a productive day.</t>
+  </si>
+  <si>
+    <t>Preparing for CA exams.</t>
+  </si>
+  <si>
+    <t>Better Sunday.</t>
   </si>
 </sst>
 </file>
@@ -2330,49 +2336,93 @@
       <c r="A33" s="8">
         <v>46278</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+      <c r="B33" s="9">
+        <v>360</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9">
+        <v>180</v>
+      </c>
+      <c r="E33" s="9">
+        <v>60</v>
+      </c>
+      <c r="F33" s="9">
+        <v>0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>120</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>720</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
+        <v>720</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>46279</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+      <c r="B34" s="9">
+        <v>300</v>
+      </c>
+      <c r="C34" s="9">
+        <v>50</v>
+      </c>
+      <c r="D34" s="9">
+        <v>240</v>
+      </c>
+      <c r="E34" s="9">
+        <v>120</v>
+      </c>
+      <c r="F34" s="9">
+        <v>300</v>
+      </c>
+      <c r="G34" s="9">
+        <v>6</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+        <v>430</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8">

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBB2A61-DAF2-41FD-89E0-703F94C8E2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9F17AF-C44B-4DF2-9E13-37ABFE32FF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>Better Sunday.</t>
+  </si>
+  <si>
+    <t>Day went well. Had great time with friends.</t>
   </si>
 </sst>
 </file>
@@ -2424,29 +2427,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>46280</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+      <c r="B35" s="9">
+        <v>360</v>
+      </c>
+      <c r="C35" s="9">
+        <v>50</v>
+      </c>
+      <c r="D35" s="9">
+        <v>240</v>
+      </c>
+      <c r="E35" s="9">
+        <v>120</v>
+      </c>
+      <c r="F35" s="9">
+        <v>150</v>
+      </c>
+      <c r="G35" s="9">
+        <v>3</v>
+      </c>
+      <c r="H35" s="9">
+        <v>120</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8">

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9F17AF-C44B-4DF2-9E13-37ABFE32FF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D37D16F-63C3-43D3-AF64-A5BFA55D2C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -151,9 +151,6 @@
   </si>
   <si>
     <t>Fitness (min)</t>
-  </si>
-  <si>
-    <t>Study (min)</t>
   </si>
   <si>
     <t>Coding (min)</t>
@@ -307,6 +304,21 @@
   </si>
   <si>
     <t>Day went well. Had great time with friends.</t>
+  </si>
+  <si>
+    <t>Study_min</t>
+  </si>
+  <si>
+    <t>Day spent well with friends. Today had an exam, welll attempted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepared for CA for long eight hours. </t>
+  </si>
+  <si>
+    <t>Was a disciplined  and structured day.</t>
+  </si>
+  <si>
+    <t>NA.</t>
   </si>
 </sst>
 </file>
@@ -934,7 +946,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -1006,7 +1018,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
@@ -1023,7 +1035,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -1031,7 +1043,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3" s="21"/>
     </row>
@@ -1064,37 +1076,37 @@
         <v>37</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
@@ -1131,16 +1143,16 @@
         <v>560</v>
       </c>
       <c r="K6" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="M6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N6" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1177,16 +1189,16 @@
         <v>285</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L7" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1223,13 +1235,13 @@
         <v>240</v>
       </c>
       <c r="K8" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="M8" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>51</v>
       </c>
       <c r="N8" s="12"/>
     </row>
@@ -1267,16 +1279,16 @@
         <v>550</v>
       </c>
       <c r="K9" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N9" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1313,16 +1325,16 @@
         <v>440</v>
       </c>
       <c r="K10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="M10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M10" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N10" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1359,16 +1371,16 @@
         <v>430</v>
       </c>
       <c r="K11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="M11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N11" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1405,16 +1417,16 @@
         <v>760</v>
       </c>
       <c r="K12" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="L12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="11" t="s">
+      <c r="N12" s="12" t="s">
         <v>63</v>
-      </c>
-      <c r="N12" s="12" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1451,16 +1463,16 @@
         <v>400</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -1497,16 +1509,16 @@
         <v>670</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14" s="12" t="s">
         <v>66</v>
-      </c>
-      <c r="N14" s="12" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -1543,16 +1555,16 @@
         <v>490</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N15" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -1589,16 +1601,16 @@
         <v>760</v>
       </c>
       <c r="K16" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="M16" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N16" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
@@ -1635,16 +1647,16 @@
         <v>450</v>
       </c>
       <c r="K17" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="L17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="N17" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -1681,16 +1693,16 @@
         <v>990</v>
       </c>
       <c r="K18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N18" s="12" t="s">
         <v>71</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N18" s="12" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1727,16 +1739,16 @@
         <v>940</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1773,16 +1785,16 @@
         <v>600</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M20" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M20" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N20" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1819,16 +1831,16 @@
         <v>730</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1865,16 +1877,16 @@
         <v>420</v>
       </c>
       <c r="K22" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="M22" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N22" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
@@ -1911,16 +1923,16 @@
         <v>510</v>
       </c>
       <c r="K23" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="L23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="N23" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1957,16 +1969,16 @@
         <v>370</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M24" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N24" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2003,16 +2015,16 @@
         <v>780</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2049,16 +2061,16 @@
         <v>780</v>
       </c>
       <c r="K26" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L26" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="M26" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M26" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N26" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -2095,16 +2107,16 @@
         <v>520</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2141,13 +2153,13 @@
         <v>720</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N28" s="12"/>
     </row>
@@ -2185,16 +2197,16 @@
         <v>350</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L29" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N29" s="12" t="s">
         <v>82</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
@@ -2231,16 +2243,16 @@
         <v>450</v>
       </c>
       <c r="K30" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M30" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="L30" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="N30" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2277,16 +2289,16 @@
         <v>930</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2323,16 +2335,16 @@
         <v>380</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2369,16 +2381,16 @@
         <v>720</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2415,16 +2427,16 @@
         <v>430</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2461,113 +2473,201 @@
         <v>400</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>46281</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
+      <c r="B36" s="9">
+        <v>300</v>
+      </c>
+      <c r="C36" s="9">
+        <v>50</v>
+      </c>
+      <c r="D36" s="9">
+        <v>240</v>
+      </c>
+      <c r="E36" s="9">
+        <v>120</v>
+      </c>
+      <c r="F36" s="9">
+        <v>400</v>
+      </c>
+      <c r="G36" s="9">
+        <v>8</v>
+      </c>
+      <c r="H36" s="9">
+        <v>120</v>
+      </c>
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>46282</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
+      <c r="B37" s="9">
+        <v>360</v>
+      </c>
+      <c r="C37" s="9">
+        <v>50</v>
+      </c>
+      <c r="D37" s="9">
+        <v>400</v>
+      </c>
+      <c r="E37" s="9">
+        <v>120</v>
+      </c>
+      <c r="F37" s="9">
+        <v>250</v>
+      </c>
+      <c r="G37" s="9">
+        <v>5</v>
+      </c>
+      <c r="H37" s="9">
+        <v>60</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
+        <v>200</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>46283</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
+      <c r="B38" s="9">
+        <v>360</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0</v>
+      </c>
+      <c r="D38" s="9">
+        <v>300</v>
+      </c>
+      <c r="E38" s="9">
+        <v>60</v>
+      </c>
+      <c r="F38" s="9">
+        <v>250</v>
+      </c>
+      <c r="G38" s="9">
+        <v>5</v>
+      </c>
+      <c r="H38" s="9">
+        <v>120</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>46284</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
+      <c r="B39" s="9">
+        <v>300</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0</v>
+      </c>
+      <c r="D39" s="9">
+        <v>120</v>
+      </c>
+      <c r="E39" s="9">
+        <v>30</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>360</v>
+      </c>
+      <c r="I39" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
+        <v>810</v>
+      </c>
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
+        <v>630</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8">

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D37D16F-63C3-43D3-AF64-A5BFA55D2C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790AC34B-5418-40CE-A183-00AED9289422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2673,20 +2673,22 @@
       <c r="A40" s="8">
         <v>46285</v>
       </c>
-      <c r="B40" s="9"/>
+      <c r="B40" s="9">
+        <v>360</v>
+      </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790AC34B-5418-40CE-A183-00AED9289422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7FBAE5-7CC1-41FD-B6C2-27A8FFC5D2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,12 @@
   </si>
   <si>
     <t>NA.</t>
+  </si>
+  <si>
+    <t>Sun Day Fun Day</t>
+  </si>
+  <si>
+    <t>Had Maths CA.</t>
   </si>
 </sst>
 </file>
@@ -2676,48 +2682,90 @@
       <c r="B40" s="9">
         <v>360</v>
       </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
+      <c r="C40" s="9">
+        <v>0</v>
+      </c>
+      <c r="D40" s="9">
+        <v>120</v>
+      </c>
+      <c r="E40" s="9">
+        <v>60</v>
+      </c>
+      <c r="F40" s="9">
+        <v>0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>360</v>
+      </c>
       <c r="I40" s="10">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>900</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v>1080</v>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
+        <v>540</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>46286</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+      <c r="B41" s="9">
+        <v>480</v>
+      </c>
+      <c r="C41" s="9">
+        <v>0</v>
+      </c>
+      <c r="D41" s="9">
+        <v>300</v>
+      </c>
+      <c r="E41" s="9">
+        <v>30</v>
+      </c>
+      <c r="F41" s="9">
+        <v>100</v>
+      </c>
+      <c r="G41" s="9">
+        <v>2</v>
+      </c>
+      <c r="H41" s="9">
+        <v>120</v>
+      </c>
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
+        <v>410</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8">

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7FBAE5-7CC1-41FD-B6C2-27A8FFC5D2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B0500C-DC36-4D39-B83B-D05DC82CC56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>Had Maths CA.</t>
+  </si>
+  <si>
+    <t>Productive day.</t>
   </si>
 </sst>
 </file>
@@ -2771,25 +2774,47 @@
       <c r="A42" s="8">
         <v>46287</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
+      <c r="B42" s="9">
+        <v>480</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0</v>
+      </c>
+      <c r="D42" s="9">
+        <v>240</v>
+      </c>
+      <c r="E42" s="9">
+        <v>120</v>
+      </c>
+      <c r="F42" s="9">
+        <v>100</v>
+      </c>
+      <c r="G42" s="9">
+        <v>2</v>
+      </c>
+      <c r="H42" s="9">
+        <v>180</v>
+      </c>
+      <c r="I42" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J42" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
+        <v>320</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="8">

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B0500C-DC36-4D39-B83B-D05DC82CC56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0078995-457D-4570-A7DA-9E2F758F5113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2820,20 +2820,22 @@
       <c r="A43" s="8">
         <v>46288</v>
       </c>
-      <c r="B43" s="9"/>
+      <c r="B43" s="9">
+        <v>360</v>
+      </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
+      <c r="I43" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
@@ -2844,20 +2846,22 @@
       <c r="A44" s="8">
         <v>46289</v>
       </c>
-      <c r="B44" s="9"/>
+      <c r="B44" s="9">
+        <v>480</v>
+      </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
+      <c r="I44" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0078995-457D-4570-A7DA-9E2F758F5113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB963E83-7AB0-473F-BC12-085B684836D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,24 @@
   </si>
   <si>
     <t>Productive day.</t>
+  </si>
+  <si>
+    <t>Participated in my first hackathon</t>
+  </si>
+  <si>
+    <t>Travelling back to home due to protest. Lernt Protest is protest till violence is not involved,else it is vandilism.One should wear shoes of other before harming him/his property.</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Reached home, felt happy after meeting my family.</t>
+  </si>
+  <si>
+    <t>completed household works and activated dormant account.</t>
+  </si>
+  <si>
+    <t>Went market with mother for ration and vegetables.</t>
   </si>
 </sst>
 </file>
@@ -2823,219 +2841,403 @@
       <c r="B43" s="9">
         <v>360</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
+      <c r="C43" s="9">
+        <v>50</v>
+      </c>
+      <c r="D43" s="9">
+        <v>360</v>
+      </c>
+      <c r="E43" s="9">
+        <v>120</v>
+      </c>
+      <c r="F43" s="9">
+        <v>200</v>
+      </c>
+      <c r="G43" s="9">
+        <v>4</v>
+      </c>
+      <c r="H43" s="9">
+        <v>180</v>
+      </c>
       <c r="I43" s="10">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>1270</v>
       </c>
       <c r="J43" s="10">
         <f t="shared" si="1"/>
-        <v>1080</v>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
+        <v>170</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N43" s="12"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>46289</v>
       </c>
       <c r="B44" s="9">
         <v>480</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
+      <c r="C44" s="9">
+        <v>50</v>
+      </c>
+      <c r="D44" s="9">
+        <v>300</v>
+      </c>
+      <c r="E44" s="9">
+        <v>60</v>
+      </c>
+      <c r="F44" s="9">
+        <v>250</v>
+      </c>
+      <c r="G44" s="9">
+        <v>5</v>
+      </c>
+      <c r="H44" s="9">
+        <v>240</v>
+      </c>
       <c r="I44" s="10">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>1380</v>
       </c>
       <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v>960</v>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>46290</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
+      <c r="B45" s="9">
+        <v>360</v>
+      </c>
+      <c r="C45" s="9">
+        <v>50</v>
+      </c>
+      <c r="D45" s="9">
+        <v>360</v>
+      </c>
+      <c r="E45" s="9">
+        <v>60</v>
+      </c>
+      <c r="F45" s="9">
+        <v>0</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0</v>
+      </c>
+      <c r="H45" s="9">
+        <v>480</v>
+      </c>
+      <c r="I45" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
+        <v>130</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>62</v>
+      </c>
       <c r="N45" s="12"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>46291</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
+      <c r="B46" s="9">
+        <v>0</v>
+      </c>
+      <c r="C46" s="9">
+        <v>180</v>
+      </c>
+      <c r="D46" s="9">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>360</v>
+      </c>
+      <c r="I46" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
+        <v>540</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
+        <v>900</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>62</v>
+      </c>
       <c r="N46" s="12"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>46292</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
+      <c r="B47" s="9">
+        <v>180</v>
+      </c>
+      <c r="C47" s="9">
+        <v>120</v>
+      </c>
+      <c r="D47" s="9">
+        <v>120</v>
+      </c>
+      <c r="E47" s="9">
+        <v>60</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>360</v>
+      </c>
+      <c r="I47" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
+        <v>840</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>600</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
       <c r="N47" s="12"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>46293</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
+      <c r="B48" s="9">
+        <v>0</v>
+      </c>
+      <c r="C48" s="9">
+        <v>0</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>720</v>
+      </c>
+      <c r="I48" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+        <v>720</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+        <v>720</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>46294</v>
       </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
+      <c r="B49" s="9">
+        <v>360</v>
+      </c>
+      <c r="C49" s="9">
+        <v>0</v>
+      </c>
+      <c r="D49" s="9">
+        <v>0</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>360</v>
+      </c>
+      <c r="I49" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
+        <v>720</v>
+      </c>
+      <c r="J49" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="12"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+        <v>720</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>46295</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
+      <c r="B50" s="9">
+        <v>480</v>
+      </c>
+      <c r="C50" s="9">
+        <v>0</v>
+      </c>
+      <c r="D50" s="9">
+        <v>180</v>
+      </c>
+      <c r="E50" s="9">
+        <v>30</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>480</v>
+      </c>
+      <c r="I50" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J50" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="12"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10" t="str">
+        <v>270</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="9">
+        <v>360</v>
+      </c>
+      <c r="C51" s="9">
+        <v>0</v>
+      </c>
+      <c r="D51" s="9">
+        <v>180</v>
+      </c>
+      <c r="E51" s="9">
+        <v>120</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>360</v>
+      </c>
+      <c r="I51" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J51" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="12"/>
+        <v>420</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
+      <c r="A52" s="8">
+        <v>46297</v>
+      </c>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB963E83-7AB0-473F-BC12-085B684836D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F7B042-B2CD-432D-A40D-4B7DF7B81C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>Went market with mother for ration and vegetables.</t>
+  </si>
+  <si>
+    <t>Completed my first minor project and happy to tick all the to do list.</t>
   </si>
 </sst>
 </file>
@@ -3234,29 +3237,51 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>46297</v>
       </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10" t="str">
+      <c r="B52" s="9">
+        <v>360</v>
+      </c>
+      <c r="C52" s="9">
+        <v>0</v>
+      </c>
+      <c r="D52" s="9">
+        <v>240</v>
+      </c>
+      <c r="E52" s="9">
+        <v>120</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>720</v>
+      </c>
+      <c r="I52" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="10" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J52" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F7B042-B2CD-432D-A40D-4B7DF7B81C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47375E9C-0623-4AFF-BDCF-5153248E8527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3284,21 +3284,25 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
+      <c r="A53" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B53" s="9">
+        <v>360</v>
+      </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
-      <c r="I53" s="10" t="str">
+      <c r="I53" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J53" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K53" s="11"/>
       <c r="L53" s="11"/>
@@ -3306,21 +3310,25 @@
       <c r="N53" s="12"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
+      <c r="A54" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B54" s="9">
+        <v>240</v>
+      </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
-      <c r="I54" s="10" t="str">
+      <c r="I54" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="10" t="str">
+        <v>240</v>
+      </c>
+      <c r="J54" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47375E9C-0623-4AFF-BDCF-5153248E8527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC657335-D66C-49B4-A685-C229E955D36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3199,7 +3199,7 @@
         <v>360</v>
       </c>
       <c r="C51" s="9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D51" s="9">
         <v>180</v>
@@ -3218,11 +3218,11 @@
       </c>
       <c r="I51" s="10">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="J51" s="10">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>48</v>
@@ -3290,7 +3290,9 @@
       <c r="B53" s="9">
         <v>360</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="9">
+        <v>120</v>
+      </c>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
@@ -3298,11 +3300,11 @@
       <c r="H53" s="9"/>
       <c r="I53" s="10">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="J53" s="10">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>960</v>
       </c>
       <c r="K53" s="11"/>
       <c r="L53" s="11"/>
@@ -3316,7 +3318,9 @@
       <c r="B54" s="9">
         <v>240</v>
       </c>
-      <c r="C54" s="9"/>
+      <c r="C54" s="9">
+        <v>60</v>
+      </c>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
@@ -3324,11 +3328,11 @@
       <c r="H54" s="9"/>
       <c r="I54" s="10">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="J54" s="10">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1140</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="11"/>
@@ -3336,21 +3340,27 @@
       <c r="N54" s="12"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
+      <c r="A55" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B55" s="9">
+        <v>480</v>
+      </c>
+      <c r="C55" s="9">
+        <v>60</v>
+      </c>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
-      <c r="I55" s="10" t="str">
+      <c r="I55" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="10" t="str">
+        <v>540</v>
+      </c>
+      <c r="J55" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>900</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC657335-D66C-49B4-A685-C229E955D36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F60BCF-B696-494A-B532-56F5A4A178E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3368,21 +3368,25 @@
       <c r="N55" s="12"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
+      <c r="A56" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="9">
+        <v>560</v>
+      </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
-      <c r="I56" s="10" t="str">
+      <c r="I56" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="10" t="str">
+        <v>560</v>
+      </c>
+      <c r="J56" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>880</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="11"/>
@@ -3390,21 +3394,25 @@
       <c r="N56" s="12"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
+      <c r="A57" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="9">
+        <v>360</v>
+      </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
-      <c r="I57" s="10" t="str">
+      <c r="I57" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J57" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="11"/>
@@ -3412,21 +3420,25 @@
       <c r="N57" s="12"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
+      <c r="A58" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="9">
+        <v>120</v>
+      </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
-      <c r="I58" s="10" t="str">
+      <c r="I58" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="str">
+        <v>120</v>
+      </c>
+      <c r="J58" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1320</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="11"/>
@@ -3434,21 +3446,25 @@
       <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
+      <c r="A59" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="9">
+        <v>240</v>
+      </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
-      <c r="I59" s="10" t="str">
+      <c r="I59" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="str">
+        <v>240</v>
+      </c>
+      <c r="J59" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="11"/>
@@ -3456,7 +3472,9 @@
       <c r="N59" s="12"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
+      <c r="A60" s="8">
+        <v>46305</v>
+      </c>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F60BCF-B696-494A-B532-56F5A4A178E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DB2E0A-08F6-40DB-BB19-D7722ED3E5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3475,20 +3475,22 @@
       <c r="A60" s="8">
         <v>46305</v>
       </c>
-      <c r="B60" s="9"/>
+      <c r="B60" s="9">
+        <v>360</v>
+      </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
-      <c r="I60" s="10" t="str">
+      <c r="I60" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J60" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K60" s="11"/>
       <c r="L60" s="11"/>
@@ -3496,21 +3498,25 @@
       <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9"/>
+      <c r="A61" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="9">
+        <v>480</v>
+      </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
-      <c r="I61" s="10" t="str">
+      <c r="I61" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="J61" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="11"/>
@@ -3518,21 +3524,25 @@
       <c r="N61" s="12"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
+      <c r="A62" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="9">
+        <v>360</v>
+      </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
-      <c r="I62" s="10" t="str">
+      <c r="I62" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J62" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K62" s="11"/>
       <c r="L62" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DB2E0A-08F6-40DB-BB19-D7722ED3E5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725BA966-21A5-43FB-A599-F3F75322373C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3550,21 +3550,25 @@
       <c r="N62" s="12"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
+      <c r="A63" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="9">
+        <v>360</v>
+      </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
-      <c r="I63" s="10" t="str">
+      <c r="I63" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J63" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K63" s="11"/>
       <c r="L63" s="11"/>
@@ -3572,21 +3576,25 @@
       <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
+      <c r="A64" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="9">
+        <v>360</v>
+      </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
+      <c r="I64" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J64" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K64" s="11"/>
       <c r="L64" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725BA966-21A5-43FB-A599-F3F75322373C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E8355C-0552-4E88-9214-E804AC575035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3602,21 +3602,25 @@
       <c r="N64" s="12"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
+      <c r="A65" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="9">
+        <v>480</v>
+      </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
+      <c r="I65" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="J65" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K65" s="11"/>
       <c r="L65" s="11"/>
@@ -3624,21 +3628,25 @@
       <c r="N65" s="12"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
+      <c r="A66" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="9">
+        <v>360</v>
+      </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
+      <c r="I66" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J66" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K66" s="11"/>
       <c r="L66" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E8355C-0552-4E88-9214-E804AC575035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B771BB91-258D-4D8A-8B62-32E6FFE59E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -349,6 +349,21 @@
   </si>
   <si>
     <t>Completed my first minor project and happy to tick all the to do list.</t>
+  </si>
+  <si>
+    <t>Had a trip of nainital and kainchi dham. After then I was travelling back to college.</t>
+  </si>
+  <si>
+    <t>Had Upper Intermediate Communications MTE</t>
+  </si>
+  <si>
+    <t>Completed all the chapter and unit test of analytical skills assigned on hitsbulleye.</t>
+  </si>
+  <si>
+    <t>Had Analytics skill MTE</t>
+  </si>
+  <si>
+    <t>Had DBMS MTE</t>
   </si>
 </sst>
 </file>
@@ -3599,33 +3614,55 @@
       <c r="K64" s="11"/>
       <c r="L64" s="11"/>
       <c r="M64" s="11"/>
-      <c r="N64" s="12"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N64" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>46310</v>
       </c>
       <c r="B65" s="9">
         <v>480</v>
       </c>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
+      <c r="C65" s="9">
+        <v>60</v>
+      </c>
+      <c r="D65" s="9">
+        <v>480</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>360</v>
+      </c>
       <c r="I65" s="10">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>1380</v>
       </c>
       <c r="J65" s="10">
         <f t="shared" si="1"/>
-        <v>960</v>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N65" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
@@ -3634,85 +3671,159 @@
       <c r="B66" s="9">
         <v>360</v>
       </c>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
+      <c r="C66" s="9">
+        <v>60</v>
+      </c>
+      <c r="D66" s="9">
+        <v>120</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>360</v>
+      </c>
       <c r="I66" s="10">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>900</v>
       </c>
       <c r="J66" s="10">
         <f t="shared" si="1"/>
-        <v>1080</v>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
+        <v>540</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="9">
+        <v>360</v>
+      </c>
+      <c r="C67" s="9">
+        <v>60</v>
+      </c>
+      <c r="D67" s="9">
+        <v>60</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0</v>
+      </c>
+      <c r="H67" s="9">
+        <v>360</v>
+      </c>
+      <c r="I67" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
+        <v>840</v>
+      </c>
+      <c r="J67" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="12"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
+        <v>600</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="9">
+        <v>360</v>
+      </c>
+      <c r="C68" s="9">
+        <v>0</v>
+      </c>
+      <c r="D68" s="9">
+        <v>0</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>480</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
+        <v>840</v>
+      </c>
+      <c r="J68" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
+        <v>600</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
+      <c r="A69" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="9">
+        <v>240</v>
+      </c>
+      <c r="C69" s="9">
+        <v>60</v>
+      </c>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
+      <c r="I69" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
+        <v>300</v>
+      </c>
+      <c r="J69" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1140</v>
       </c>
       <c r="K69" s="11"/>
       <c r="L69" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B771BB91-258D-4D8A-8B62-32E6FFE59E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E29E48-BA9E-4516-A2AF-04FF463683B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3831,21 +3831,25 @@
       <c r="N69" s="12"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
+      <c r="A70" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="9">
+        <v>480</v>
+      </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
+      <c r="I70" s="10">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="J70" s="10">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K70" s="11"/>
       <c r="L70" s="11"/>
@@ -3853,21 +3857,25 @@
       <c r="N70" s="12"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
+      <c r="A71" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="9">
+        <v>360</v>
+      </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+      <c r="I71" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K71" s="11"/>
       <c r="L71" s="11"/>
@@ -3875,21 +3883,25 @@
       <c r="N71" s="12"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
+      <c r="A72" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="9">
+        <v>360</v>
+      </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+      <c r="I72" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K72" s="11"/>
       <c r="L72" s="11"/>
@@ -3897,21 +3909,25 @@
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
+      <c r="A73" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="9">
+        <v>480</v>
+      </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+      <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K73" s="11"/>
       <c r="L73" s="11"/>
@@ -3919,7 +3935,9 @@
       <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
+      <c r="A74" s="8">
+        <v>46319</v>
+      </c>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E29E48-BA9E-4516-A2AF-04FF463683B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B4601B-02F1-442C-907C-359AC178F0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3938,20 +3938,22 @@
       <c r="A74" s="8">
         <v>46319</v>
       </c>
-      <c r="B74" s="9"/>
+      <c r="B74" s="9">
+        <v>360</v>
+      </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+      <c r="I74" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K74" s="11"/>
       <c r="L74" s="11"/>
@@ -3959,21 +3961,25 @@
       <c r="N74" s="12"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
+      <c r="A75" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="9">
+        <v>360</v>
+      </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+      <c r="I75" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K75" s="11"/>
       <c r="L75" s="11"/>
@@ -3981,7 +3987,9 @@
       <c r="N75" s="12"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
+      <c r="A76" s="8">
+        <v>46321</v>
+      </c>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B4601B-02F1-442C-907C-359AC178F0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD50D37-9435-4B1A-AA75-D858B0FC4B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3990,20 +3990,22 @@
       <c r="A76" s="8">
         <v>46321</v>
       </c>
-      <c r="B76" s="9"/>
+      <c r="B76" s="9">
+        <v>480</v>
+      </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
+      <c r="I76" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K76" s="11"/>
       <c r="L76" s="11"/>
@@ -4011,21 +4013,25 @@
       <c r="N76" s="12"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
+      <c r="A77" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="9">
+        <v>360</v>
+      </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
+      <c r="I77" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K77" s="11"/>
       <c r="L77" s="11"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD50D37-9435-4B1A-AA75-D858B0FC4B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0C4767-2C88-4905-9A34-F3395FEDE65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4039,21 +4039,25 @@
       <c r="N77" s="12"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
+      <c r="A78" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="9">
+        <v>360</v>
+      </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+      <c r="I78" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K78" s="11"/>
       <c r="L78" s="11"/>
@@ -4061,7 +4065,9 @@
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
+      <c r="A79" s="8">
+        <v>46324</v>
+      </c>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
@@ -4083,7 +4089,9 @@
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
+      <c r="A80" s="8">
+        <v>46325</v>
+      </c>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
@@ -4105,7 +4113,9 @@
       <c r="N80" s="12"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
+      <c r="A81" s="8">
+        <v>46326</v>
+      </c>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
@@ -4127,7 +4137,9 @@
       <c r="N81" s="12"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="8"/>
+      <c r="A82" s="8">
+        <v>46327</v>
+      </c>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
@@ -4149,7 +4161,9 @@
       <c r="N82" s="12"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="8"/>
+      <c r="A83" s="8">
+        <v>46328</v>
+      </c>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
@@ -4171,7 +4185,9 @@
       <c r="N83" s="12"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="8"/>
+      <c r="A84" s="8">
+        <v>46329</v>
+      </c>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
@@ -4193,7 +4209,9 @@
       <c r="N84" s="12"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="8"/>
+      <c r="A85" s="8">
+        <v>46330</v>
+      </c>
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
@@ -4215,7 +4233,9 @@
       <c r="N85" s="12"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" s="8"/>
+      <c r="A86" s="8">
+        <v>46331</v>
+      </c>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
@@ -4237,7 +4257,9 @@
       <c r="N86" s="12"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" s="8"/>
+      <c r="A87" s="8">
+        <v>46332</v>
+      </c>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
@@ -4259,7 +4281,9 @@
       <c r="N87" s="12"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A88" s="8"/>
+      <c r="A88" s="8">
+        <v>46333</v>
+      </c>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -4281,7 +4305,9 @@
       <c r="N88" s="12"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A89" s="8"/>
+      <c r="A89" s="8">
+        <v>46334</v>
+      </c>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
@@ -4303,7 +4329,9 @@
       <c r="N89" s="12"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A90" s="8"/>
+      <c r="A90" s="8">
+        <v>46335</v>
+      </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
@@ -4325,7 +4353,9 @@
       <c r="N90" s="12"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A91" s="8"/>
+      <c r="A91" s="8">
+        <v>46336</v>
+      </c>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
@@ -4347,7 +4377,9 @@
       <c r="N91" s="12"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A92" s="8"/>
+      <c r="A92" s="8">
+        <v>46337</v>
+      </c>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
@@ -4369,7 +4401,9 @@
       <c r="N92" s="12"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A93" s="8"/>
+      <c r="A93" s="8">
+        <v>46338</v>
+      </c>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
@@ -4391,7 +4425,9 @@
       <c r="N93" s="12"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A94" s="8"/>
+      <c r="A94" s="8">
+        <v>46339</v>
+      </c>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
@@ -4413,7 +4449,9 @@
       <c r="N94" s="12"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A95" s="8"/>
+      <c r="A95" s="8">
+        <v>46340</v>
+      </c>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
@@ -4435,7 +4473,9 @@
       <c r="N95" s="12"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A96" s="8"/>
+      <c r="A96" s="8">
+        <v>46341</v>
+      </c>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
@@ -4457,7 +4497,9 @@
       <c r="N96" s="12"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A97" s="8"/>
+      <c r="A97" s="8">
+        <v>46342</v>
+      </c>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
@@ -4479,7 +4521,9 @@
       <c r="N97" s="12"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A98" s="8"/>
+      <c r="A98" s="8">
+        <v>46343</v>
+      </c>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
@@ -4501,7 +4545,9 @@
       <c r="N98" s="12"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A99" s="8"/>
+      <c r="A99" s="8">
+        <v>46344</v>
+      </c>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
@@ -4523,7 +4569,9 @@
       <c r="N99" s="12"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A100" s="8"/>
+      <c r="A100" s="8">
+        <v>46345</v>
+      </c>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
@@ -4545,7 +4593,9 @@
       <c r="N100" s="12"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A101" s="8"/>
+      <c r="A101" s="8">
+        <v>46346</v>
+      </c>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
@@ -4567,7 +4617,9 @@
       <c r="N101" s="12"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A102" s="8"/>
+      <c r="A102" s="8">
+        <v>46347</v>
+      </c>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -4589,7 +4641,9 @@
       <c r="N102" s="12"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A103" s="8"/>
+      <c r="A103" s="8">
+        <v>46348</v>
+      </c>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
@@ -4611,7 +4665,9 @@
       <c r="N103" s="12"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A104" s="8"/>
+      <c r="A104" s="8">
+        <v>46349</v>
+      </c>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
@@ -4633,7 +4689,9 @@
       <c r="N104" s="12"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A105" s="8"/>
+      <c r="A105" s="8">
+        <v>46350</v>
+      </c>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
@@ -4655,7 +4713,9 @@
       <c r="N105" s="12"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A106" s="8"/>
+      <c r="A106" s="8">
+        <v>46351</v>
+      </c>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
@@ -4677,7 +4737,9 @@
       <c r="N106" s="12"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A107" s="8"/>
+      <c r="A107" s="8">
+        <v>46352</v>
+      </c>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
@@ -4699,7 +4761,9 @@
       <c r="N107" s="12"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A108" s="8"/>
+      <c r="A108" s="8">
+        <v>46353</v>
+      </c>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
@@ -4721,7 +4785,9 @@
       <c r="N108" s="12"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A109" s="8"/>
+      <c r="A109" s="8">
+        <v>46354</v>
+      </c>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
@@ -4743,7 +4809,9 @@
       <c r="N109" s="12"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A110" s="8"/>
+      <c r="A110" s="8">
+        <v>46355</v>
+      </c>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
@@ -4765,7 +4833,9 @@
       <c r="N110" s="12"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A111" s="8"/>
+      <c r="A111" s="8">
+        <v>46356</v>
+      </c>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
@@ -4787,7 +4857,9 @@
       <c r="N111" s="12"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A112" s="8"/>
+      <c r="A112" s="8">
+        <v>46357</v>
+      </c>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
@@ -4809,7 +4881,9 @@
       <c r="N112" s="12"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" s="8"/>
+      <c r="A113" s="8">
+        <v>46358</v>
+      </c>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
@@ -4831,7 +4905,9 @@
       <c r="N113" s="12"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A114" s="8"/>
+      <c r="A114" s="8">
+        <v>46359</v>
+      </c>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
@@ -4853,7 +4929,9 @@
       <c r="N114" s="12"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A115" s="8"/>
+      <c r="A115" s="8">
+        <v>46360</v>
+      </c>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
@@ -4875,7 +4953,9 @@
       <c r="N115" s="12"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A116" s="8"/>
+      <c r="A116" s="8">
+        <v>46361</v>
+      </c>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
@@ -4897,7 +4977,9 @@
       <c r="N116" s="12"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A117" s="8"/>
+      <c r="A117" s="8">
+        <v>46362</v>
+      </c>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
@@ -4919,7 +5001,9 @@
       <c r="N117" s="12"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A118" s="8"/>
+      <c r="A118" s="8">
+        <v>46363</v>
+      </c>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
@@ -4941,7 +5025,9 @@
       <c r="N118" s="12"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A119" s="8"/>
+      <c r="A119" s="8">
+        <v>46364</v>
+      </c>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
@@ -4963,7 +5049,9 @@
       <c r="N119" s="12"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A120" s="8"/>
+      <c r="A120" s="8">
+        <v>46365</v>
+      </c>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
@@ -4985,7 +5073,9 @@
       <c r="N120" s="12"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A121" s="8"/>
+      <c r="A121" s="8">
+        <v>46366</v>
+      </c>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
@@ -5007,7 +5097,9 @@
       <c r="N121" s="12"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A122" s="8"/>
+      <c r="A122" s="8">
+        <v>46367</v>
+      </c>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
@@ -5029,7 +5121,9 @@
       <c r="N122" s="12"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A123" s="8"/>
+      <c r="A123" s="8">
+        <v>46368</v>
+      </c>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
@@ -5051,7 +5145,9 @@
       <c r="N123" s="12"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A124" s="8"/>
+      <c r="A124" s="8">
+        <v>46369</v>
+      </c>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
@@ -5073,7 +5169,9 @@
       <c r="N124" s="12"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A125" s="8"/>
+      <c r="A125" s="8">
+        <v>46370</v>
+      </c>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
@@ -5095,7 +5193,9 @@
       <c r="N125" s="12"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A126" s="8"/>
+      <c r="A126" s="8">
+        <v>46371</v>
+      </c>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
@@ -5117,7 +5217,9 @@
       <c r="N126" s="12"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A127" s="8"/>
+      <c r="A127" s="8">
+        <v>46372</v>
+      </c>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
@@ -5139,7 +5241,9 @@
       <c r="N127" s="12"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A128" s="8"/>
+      <c r="A128" s="8">
+        <v>46373</v>
+      </c>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
@@ -5161,7 +5265,9 @@
       <c r="N128" s="12"/>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A129" s="8"/>
+      <c r="A129" s="8">
+        <v>46374</v>
+      </c>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
@@ -5183,7 +5289,9 @@
       <c r="N129" s="12"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A130" s="8"/>
+      <c r="A130" s="8">
+        <v>46375</v>
+      </c>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
@@ -5205,7 +5313,9 @@
       <c r="N130" s="12"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A131" s="8"/>
+      <c r="A131" s="8">
+        <v>46376</v>
+      </c>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
@@ -5227,7 +5337,9 @@
       <c r="N131" s="12"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A132" s="8"/>
+      <c r="A132" s="8">
+        <v>46377</v>
+      </c>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
@@ -5249,7 +5361,9 @@
       <c r="N132" s="12"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="8"/>
+      <c r="A133" s="8">
+        <v>46378</v>
+      </c>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
@@ -5271,7 +5385,9 @@
       <c r="N133" s="12"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A134" s="8"/>
+      <c r="A134" s="8">
+        <v>46379</v>
+      </c>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
@@ -5293,7 +5409,9 @@
       <c r="N134" s="12"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A135" s="8"/>
+      <c r="A135" s="8">
+        <v>46380</v>
+      </c>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
@@ -5315,7 +5433,9 @@
       <c r="N135" s="12"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A136" s="8"/>
+      <c r="A136" s="8">
+        <v>46381</v>
+      </c>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
@@ -5337,7 +5457,9 @@
       <c r="N136" s="12"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A137" s="8"/>
+      <c r="A137" s="8">
+        <v>46382</v>
+      </c>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
@@ -5359,7 +5481,9 @@
       <c r="N137" s="12"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A138" s="8"/>
+      <c r="A138" s="8">
+        <v>46383</v>
+      </c>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
@@ -5381,7 +5505,9 @@
       <c r="N138" s="12"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" s="8"/>
+      <c r="A139" s="8">
+        <v>46384</v>
+      </c>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
@@ -5403,7 +5529,9 @@
       <c r="N139" s="12"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A140" s="8"/>
+      <c r="A140" s="8">
+        <v>46385</v>
+      </c>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
@@ -5425,7 +5553,9 @@
       <c r="N140" s="12"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A141" s="8"/>
+      <c r="A141" s="8">
+        <v>46386</v>
+      </c>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
@@ -5447,7 +5577,9 @@
       <c r="N141" s="12"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A142" s="8"/>
+      <c r="A142" s="8">
+        <v>46387</v>
+      </c>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
@@ -5469,7 +5601,9 @@
       <c r="N142" s="12"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A143" s="8"/>
+      <c r="A143" s="8">
+        <v>46388</v>
+      </c>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
@@ -5491,7 +5625,9 @@
       <c r="N143" s="12"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A144" s="8"/>
+      <c r="A144" s="8">
+        <v>46389</v>
+      </c>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
@@ -5513,7 +5649,9 @@
       <c r="N144" s="12"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A145" s="8"/>
+      <c r="A145" s="8">
+        <v>46390</v>
+      </c>
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
@@ -5535,7 +5673,9 @@
       <c r="N145" s="12"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A146" s="8"/>
+      <c r="A146" s="8">
+        <v>46391</v>
+      </c>
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
@@ -5557,7 +5697,9 @@
       <c r="N146" s="12"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A147" s="8"/>
+      <c r="A147" s="8">
+        <v>46392</v>
+      </c>
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
@@ -5579,7 +5721,9 @@
       <c r="N147" s="12"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A148" s="8"/>
+      <c r="A148" s="8">
+        <v>46393</v>
+      </c>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
@@ -5601,7 +5745,9 @@
       <c r="N148" s="12"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A149" s="8"/>
+      <c r="A149" s="8">
+        <v>46394</v>
+      </c>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
@@ -5623,7 +5769,9 @@
       <c r="N149" s="12"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A150" s="8"/>
+      <c r="A150" s="8">
+        <v>46395</v>
+      </c>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
@@ -5645,7 +5793,9 @@
       <c r="N150" s="12"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A151" s="8"/>
+      <c r="A151" s="8">
+        <v>46396</v>
+      </c>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
@@ -5667,7 +5817,9 @@
       <c r="N151" s="12"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A152" s="8"/>
+      <c r="A152" s="8">
+        <v>46397</v>
+      </c>
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
@@ -5689,7 +5841,9 @@
       <c r="N152" s="12"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A153" s="8"/>
+      <c r="A153" s="8">
+        <v>46398</v>
+      </c>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
@@ -5711,7 +5865,9 @@
       <c r="N153" s="12"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A154" s="8"/>
+      <c r="A154" s="8">
+        <v>46399</v>
+      </c>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
@@ -5733,7 +5889,9 @@
       <c r="N154" s="12"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A155" s="8"/>
+      <c r="A155" s="8">
+        <v>46400</v>
+      </c>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
@@ -5755,7 +5913,9 @@
       <c r="N155" s="12"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A156" s="8"/>
+      <c r="A156" s="8">
+        <v>46401</v>
+      </c>
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
@@ -5777,7 +5937,9 @@
       <c r="N156" s="12"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A157" s="8"/>
+      <c r="A157" s="8">
+        <v>46402</v>
+      </c>
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
@@ -5799,7 +5961,9 @@
       <c r="N157" s="12"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A158" s="8"/>
+      <c r="A158" s="8">
+        <v>46403</v>
+      </c>
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
@@ -5821,7 +5985,9 @@
       <c r="N158" s="12"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A159" s="8"/>
+      <c r="A159" s="8">
+        <v>46404</v>
+      </c>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
@@ -5843,7 +6009,9 @@
       <c r="N159" s="12"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A160" s="8"/>
+      <c r="A160" s="8">
+        <v>46405</v>
+      </c>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
@@ -5865,7 +6033,9 @@
       <c r="N160" s="12"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A161" s="8"/>
+      <c r="A161" s="8">
+        <v>46406</v>
+      </c>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
@@ -5887,7 +6057,9 @@
       <c r="N161" s="12"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A162" s="8"/>
+      <c r="A162" s="8">
+        <v>46407</v>
+      </c>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
@@ -5909,7 +6081,9 @@
       <c r="N162" s="12"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A163" s="8"/>
+      <c r="A163" s="8">
+        <v>46408</v>
+      </c>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
@@ -5931,7 +6105,9 @@
       <c r="N163" s="12"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A164" s="8"/>
+      <c r="A164" s="8">
+        <v>46409</v>
+      </c>
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
@@ -5953,7 +6129,9 @@
       <c r="N164" s="12"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A165" s="8"/>
+      <c r="A165" s="8">
+        <v>46410</v>
+      </c>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
@@ -5975,7 +6153,9 @@
       <c r="N165" s="12"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A166" s="8"/>
+      <c r="A166" s="8">
+        <v>46411</v>
+      </c>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
@@ -5997,7 +6177,9 @@
       <c r="N166" s="12"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A167" s="8"/>
+      <c r="A167" s="8">
+        <v>46412</v>
+      </c>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
@@ -6019,7 +6201,9 @@
       <c r="N167" s="12"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A168" s="8"/>
+      <c r="A168" s="8">
+        <v>46413</v>
+      </c>
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
@@ -6041,7 +6225,9 @@
       <c r="N168" s="12"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A169" s="8"/>
+      <c r="A169" s="8">
+        <v>46414</v>
+      </c>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
@@ -6063,7 +6249,9 @@
       <c r="N169" s="12"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A170" s="8"/>
+      <c r="A170" s="8">
+        <v>46415</v>
+      </c>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
@@ -6085,7 +6273,9 @@
       <c r="N170" s="12"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A171" s="8"/>
+      <c r="A171" s="8">
+        <v>46416</v>
+      </c>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
@@ -6107,7 +6297,9 @@
       <c r="N171" s="12"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A172" s="8"/>
+      <c r="A172" s="8">
+        <v>46417</v>
+      </c>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
@@ -6129,7 +6321,9 @@
       <c r="N172" s="12"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A173" s="8"/>
+      <c r="A173" s="8">
+        <v>46418</v>
+      </c>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
@@ -6151,7 +6345,9 @@
       <c r="N173" s="12"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A174" s="8"/>
+      <c r="A174" s="8">
+        <v>46419</v>
+      </c>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
@@ -6173,7 +6369,9 @@
       <c r="N174" s="12"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A175" s="8"/>
+      <c r="A175" s="8">
+        <v>46420</v>
+      </c>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
@@ -6195,7 +6393,9 @@
       <c r="N175" s="12"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A176" s="8"/>
+      <c r="A176" s="8">
+        <v>46421</v>
+      </c>
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
@@ -6217,7 +6417,9 @@
       <c r="N176" s="12"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A177" s="8"/>
+      <c r="A177" s="8">
+        <v>46422</v>
+      </c>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
@@ -6239,7 +6441,9 @@
       <c r="N177" s="12"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A178" s="8"/>
+      <c r="A178" s="8">
+        <v>46423</v>
+      </c>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
@@ -6261,7 +6465,9 @@
       <c r="N178" s="12"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A179" s="8"/>
+      <c r="A179" s="8">
+        <v>46424</v>
+      </c>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
@@ -6283,7 +6489,9 @@
       <c r="N179" s="12"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A180" s="8"/>
+      <c r="A180" s="8">
+        <v>46425</v>
+      </c>
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
@@ -6305,7 +6513,9 @@
       <c r="N180" s="12"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A181" s="8"/>
+      <c r="A181" s="8">
+        <v>46426</v>
+      </c>
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
@@ -6327,7 +6537,9 @@
       <c r="N181" s="12"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A182" s="8"/>
+      <c r="A182" s="8">
+        <v>46427</v>
+      </c>
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
@@ -6349,7 +6561,9 @@
       <c r="N182" s="12"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A183" s="8"/>
+      <c r="A183" s="8">
+        <v>46428</v>
+      </c>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
@@ -6371,7 +6585,9 @@
       <c r="N183" s="12"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A184" s="8"/>
+      <c r="A184" s="8">
+        <v>46429</v>
+      </c>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
@@ -6393,7 +6609,9 @@
       <c r="N184" s="12"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A185" s="8"/>
+      <c r="A185" s="8">
+        <v>46430</v>
+      </c>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
@@ -6415,7 +6633,9 @@
       <c r="N185" s="12"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A186" s="8"/>
+      <c r="A186" s="8">
+        <v>46431</v>
+      </c>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
@@ -6437,7 +6657,9 @@
       <c r="N186" s="12"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A187" s="8"/>
+      <c r="A187" s="8">
+        <v>46432</v>
+      </c>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
@@ -6459,7 +6681,9 @@
       <c r="N187" s="12"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A188" s="8"/>
+      <c r="A188" s="8">
+        <v>46433</v>
+      </c>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
@@ -6481,7 +6705,9 @@
       <c r="N188" s="12"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A189" s="8"/>
+      <c r="A189" s="8">
+        <v>46434</v>
+      </c>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
@@ -6503,7 +6729,9 @@
       <c r="N189" s="12"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A190" s="8"/>
+      <c r="A190" s="8">
+        <v>46435</v>
+      </c>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
@@ -6525,7 +6753,9 @@
       <c r="N190" s="12"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A191" s="8"/>
+      <c r="A191" s="8">
+        <v>46436</v>
+      </c>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
@@ -6547,7 +6777,9 @@
       <c r="N191" s="12"/>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A192" s="8"/>
+      <c r="A192" s="8">
+        <v>46437</v>
+      </c>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
@@ -6569,7 +6801,9 @@
       <c r="N192" s="12"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A193" s="8"/>
+      <c r="A193" s="8">
+        <v>46438</v>
+      </c>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
@@ -6591,7 +6825,9 @@
       <c r="N193" s="12"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A194" s="8"/>
+      <c r="A194" s="8">
+        <v>46439</v>
+      </c>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
@@ -6613,7 +6849,9 @@
       <c r="N194" s="12"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A195" s="8"/>
+      <c r="A195" s="8">
+        <v>46440</v>
+      </c>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
@@ -6635,7 +6873,9 @@
       <c r="N195" s="12"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A196" s="8"/>
+      <c r="A196" s="8">
+        <v>46441</v>
+      </c>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
@@ -6657,7 +6897,9 @@
       <c r="N196" s="12"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A197" s="8"/>
+      <c r="A197" s="8">
+        <v>46442</v>
+      </c>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
@@ -6679,7 +6921,9 @@
       <c r="N197" s="12"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A198" s="8"/>
+      <c r="A198" s="8">
+        <v>46443</v>
+      </c>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
@@ -6701,7 +6945,9 @@
       <c r="N198" s="12"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A199" s="8"/>
+      <c r="A199" s="8">
+        <v>46444</v>
+      </c>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
@@ -6723,7 +6969,9 @@
       <c r="N199" s="12"/>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A200" s="8"/>
+      <c r="A200" s="8">
+        <v>46445</v>
+      </c>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
@@ -6745,7 +6993,9 @@
       <c r="N200" s="12"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A201" s="8"/>
+      <c r="A201" s="8">
+        <v>46446</v>
+      </c>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
       <c r="D201" s="9"/>
@@ -6767,7 +7017,9 @@
       <c r="N201" s="12"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A202" s="8"/>
+      <c r="A202" s="8">
+        <v>46447</v>
+      </c>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
       <c r="D202" s="9"/>
@@ -6789,7 +7041,9 @@
       <c r="N202" s="12"/>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A203" s="8"/>
+      <c r="A203" s="8">
+        <v>46448</v>
+      </c>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
       <c r="D203" s="9"/>
@@ -6811,7 +7065,9 @@
       <c r="N203" s="12"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A204" s="8"/>
+      <c r="A204" s="8">
+        <v>46449</v>
+      </c>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
       <c r="D204" s="9"/>
@@ -6833,7 +7089,9 @@
       <c r="N204" s="12"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A205" s="8"/>
+      <c r="A205" s="8">
+        <v>46450</v>
+      </c>
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
       <c r="D205" s="9"/>
@@ -6855,7 +7113,9 @@
       <c r="N205" s="12"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A206" s="8"/>
+      <c r="A206" s="8">
+        <v>46451</v>
+      </c>
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
       <c r="D206" s="9"/>
@@ -6877,7 +7137,9 @@
       <c r="N206" s="12"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A207" s="8"/>
+      <c r="A207" s="8">
+        <v>46452</v>
+      </c>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
       <c r="D207" s="9"/>
@@ -6899,7 +7161,9 @@
       <c r="N207" s="12"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A208" s="8"/>
+      <c r="A208" s="8">
+        <v>46453</v>
+      </c>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
       <c r="D208" s="9"/>
@@ -6921,7 +7185,9 @@
       <c r="N208" s="12"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A209" s="8"/>
+      <c r="A209" s="8">
+        <v>46454</v>
+      </c>
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
       <c r="D209" s="9"/>
@@ -6943,7 +7209,9 @@
       <c r="N209" s="12"/>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A210" s="8"/>
+      <c r="A210" s="8">
+        <v>46455</v>
+      </c>
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
       <c r="D210" s="9"/>
@@ -6965,7 +7233,9 @@
       <c r="N210" s="12"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A211" s="8"/>
+      <c r="A211" s="8">
+        <v>46456</v>
+      </c>
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
       <c r="D211" s="9"/>
@@ -6987,7 +7257,9 @@
       <c r="N211" s="12"/>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A212" s="8"/>
+      <c r="A212" s="8">
+        <v>46457</v>
+      </c>
       <c r="B212" s="9"/>
       <c r="C212" s="9"/>
       <c r="D212" s="9"/>
@@ -7009,7 +7281,9 @@
       <c r="N212" s="12"/>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A213" s="8"/>
+      <c r="A213" s="8">
+        <v>46458</v>
+      </c>
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
       <c r="D213" s="9"/>
@@ -7031,7 +7305,9 @@
       <c r="N213" s="12"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A214" s="8"/>
+      <c r="A214" s="8">
+        <v>46459</v>
+      </c>
       <c r="B214" s="9"/>
       <c r="C214" s="9"/>
       <c r="D214" s="9"/>
@@ -7053,7 +7329,9 @@
       <c r="N214" s="12"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A215" s="8"/>
+      <c r="A215" s="8">
+        <v>46460</v>
+      </c>
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
       <c r="D215" s="9"/>
@@ -7075,7 +7353,9 @@
       <c r="N215" s="12"/>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A216" s="8"/>
+      <c r="A216" s="8">
+        <v>46461</v>
+      </c>
       <c r="B216" s="9"/>
       <c r="C216" s="9"/>
       <c r="D216" s="9"/>
@@ -7097,7 +7377,9 @@
       <c r="N216" s="12"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A217" s="8"/>
+      <c r="A217" s="8">
+        <v>46462</v>
+      </c>
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
       <c r="D217" s="9"/>
@@ -7119,7 +7401,9 @@
       <c r="N217" s="12"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A218" s="8"/>
+      <c r="A218" s="8">
+        <v>46463</v>
+      </c>
       <c r="B218" s="9"/>
       <c r="C218" s="9"/>
       <c r="D218" s="9"/>
@@ -7141,7 +7425,9 @@
       <c r="N218" s="12"/>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A219" s="8"/>
+      <c r="A219" s="8">
+        <v>46464</v>
+      </c>
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
       <c r="D219" s="9"/>
@@ -7163,7 +7449,9 @@
       <c r="N219" s="12"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A220" s="8"/>
+      <c r="A220" s="8">
+        <v>46465</v>
+      </c>
       <c r="B220" s="9"/>
       <c r="C220" s="9"/>
       <c r="D220" s="9"/>
@@ -7185,7 +7473,9 @@
       <c r="N220" s="12"/>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A221" s="8"/>
+      <c r="A221" s="8">
+        <v>46466</v>
+      </c>
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
       <c r="D221" s="9"/>
@@ -7207,7 +7497,9 @@
       <c r="N221" s="12"/>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A222" s="8"/>
+      <c r="A222" s="8">
+        <v>46467</v>
+      </c>
       <c r="B222" s="9"/>
       <c r="C222" s="9"/>
       <c r="D222" s="9"/>
@@ -7229,7 +7521,9 @@
       <c r="N222" s="12"/>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A223" s="8"/>
+      <c r="A223" s="8">
+        <v>46468</v>
+      </c>
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
       <c r="D223" s="9"/>
@@ -7251,7 +7545,9 @@
       <c r="N223" s="12"/>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A224" s="8"/>
+      <c r="A224" s="8">
+        <v>46469</v>
+      </c>
       <c r="B224" s="9"/>
       <c r="C224" s="9"/>
       <c r="D224" s="9"/>
@@ -7273,7 +7569,9 @@
       <c r="N224" s="12"/>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A225" s="8"/>
+      <c r="A225" s="8">
+        <v>46470</v>
+      </c>
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
       <c r="D225" s="9"/>
@@ -7295,7 +7593,9 @@
       <c r="N225" s="12"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A226" s="8"/>
+      <c r="A226" s="8">
+        <v>46471</v>
+      </c>
       <c r="B226" s="9"/>
       <c r="C226" s="9"/>
       <c r="D226" s="9"/>
@@ -7317,7 +7617,9 @@
       <c r="N226" s="12"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A227" s="8"/>
+      <c r="A227" s="8">
+        <v>46472</v>
+      </c>
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
       <c r="D227" s="9"/>
@@ -7339,7 +7641,9 @@
       <c r="N227" s="12"/>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A228" s="8"/>
+      <c r="A228" s="8">
+        <v>46473</v>
+      </c>
       <c r="B228" s="9"/>
       <c r="C228" s="9"/>
       <c r="D228" s="9"/>
@@ -7361,7 +7665,9 @@
       <c r="N228" s="12"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A229" s="8"/>
+      <c r="A229" s="8">
+        <v>46474</v>
+      </c>
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
       <c r="D229" s="9"/>
@@ -7383,7 +7689,9 @@
       <c r="N229" s="12"/>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A230" s="8"/>
+      <c r="A230" s="8">
+        <v>46475</v>
+      </c>
       <c r="B230" s="9"/>
       <c r="C230" s="9"/>
       <c r="D230" s="9"/>
@@ -7405,7 +7713,9 @@
       <c r="N230" s="12"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A231" s="8"/>
+      <c r="A231" s="8">
+        <v>46476</v>
+      </c>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
       <c r="D231" s="9"/>
@@ -7427,7 +7737,9 @@
       <c r="N231" s="12"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A232" s="8"/>
+      <c r="A232" s="8">
+        <v>46477</v>
+      </c>
       <c r="B232" s="9"/>
       <c r="C232" s="9"/>
       <c r="D232" s="9"/>
@@ -7449,7 +7761,9 @@
       <c r="N232" s="12"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A233" s="8"/>
+      <c r="A233" s="8">
+        <v>46478</v>
+      </c>
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
       <c r="D233" s="9"/>
@@ -7471,7 +7785,9 @@
       <c r="N233" s="12"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A234" s="8"/>
+      <c r="A234" s="8">
+        <v>46479</v>
+      </c>
       <c r="B234" s="9"/>
       <c r="C234" s="9"/>
       <c r="D234" s="9"/>
@@ -7493,7 +7809,9 @@
       <c r="N234" s="12"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A235" s="8"/>
+      <c r="A235" s="8">
+        <v>46480</v>
+      </c>
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
       <c r="D235" s="9"/>
@@ -7515,7 +7833,9 @@
       <c r="N235" s="12"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A236" s="8"/>
+      <c r="A236" s="8">
+        <v>46481</v>
+      </c>
       <c r="B236" s="9"/>
       <c r="C236" s="9"/>
       <c r="D236" s="9"/>
@@ -7537,7 +7857,9 @@
       <c r="N236" s="12"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A237" s="8"/>
+      <c r="A237" s="8">
+        <v>46482</v>
+      </c>
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
       <c r="D237" s="9"/>
@@ -7559,7 +7881,9 @@
       <c r="N237" s="12"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A238" s="8"/>
+      <c r="A238" s="8">
+        <v>46483</v>
+      </c>
       <c r="B238" s="9"/>
       <c r="C238" s="9"/>
       <c r="D238" s="9"/>
@@ -7581,7 +7905,9 @@
       <c r="N238" s="12"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A239" s="8"/>
+      <c r="A239" s="8">
+        <v>46484</v>
+      </c>
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
       <c r="D239" s="9"/>
@@ -7603,7 +7929,9 @@
       <c r="N239" s="12"/>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A240" s="8"/>
+      <c r="A240" s="8">
+        <v>46485</v>
+      </c>
       <c r="B240" s="9"/>
       <c r="C240" s="9"/>
       <c r="D240" s="9"/>
@@ -7625,7 +7953,9 @@
       <c r="N240" s="12"/>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A241" s="8"/>
+      <c r="A241" s="8">
+        <v>46486</v>
+      </c>
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
       <c r="D241" s="9"/>
@@ -7647,7 +7977,9 @@
       <c r="N241" s="12"/>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A242" s="8"/>
+      <c r="A242" s="8">
+        <v>46487</v>
+      </c>
       <c r="B242" s="9"/>
       <c r="C242" s="9"/>
       <c r="D242" s="9"/>
@@ -7669,7 +8001,9 @@
       <c r="N242" s="12"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A243" s="8"/>
+      <c r="A243" s="8">
+        <v>46488</v>
+      </c>
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
       <c r="D243" s="9"/>
@@ -7691,7 +8025,9 @@
       <c r="N243" s="12"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A244" s="8"/>
+      <c r="A244" s="8">
+        <v>46489</v>
+      </c>
       <c r="B244" s="9"/>
       <c r="C244" s="9"/>
       <c r="D244" s="9"/>
@@ -7713,7 +8049,9 @@
       <c r="N244" s="12"/>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A245" s="8"/>
+      <c r="A245" s="8">
+        <v>46490</v>
+      </c>
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
       <c r="D245" s="9"/>
@@ -7735,7 +8073,9 @@
       <c r="N245" s="12"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A246" s="8"/>
+      <c r="A246" s="8">
+        <v>46491</v>
+      </c>
       <c r="B246" s="9"/>
       <c r="C246" s="9"/>
       <c r="D246" s="9"/>
@@ -7757,7 +8097,9 @@
       <c r="N246" s="12"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A247" s="8"/>
+      <c r="A247" s="8">
+        <v>46492</v>
+      </c>
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
       <c r="D247" s="9"/>
@@ -7779,7 +8121,9 @@
       <c r="N247" s="12"/>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A248" s="8"/>
+      <c r="A248" s="8">
+        <v>46493</v>
+      </c>
       <c r="B248" s="9"/>
       <c r="C248" s="9"/>
       <c r="D248" s="9"/>
@@ -7801,7 +8145,9 @@
       <c r="N248" s="12"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A249" s="8"/>
+      <c r="A249" s="8">
+        <v>46494</v>
+      </c>
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
       <c r="D249" s="9"/>
@@ -7823,7 +8169,9 @@
       <c r="N249" s="12"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A250" s="8"/>
+      <c r="A250" s="8">
+        <v>46495</v>
+      </c>
       <c r="B250" s="9"/>
       <c r="C250" s="9"/>
       <c r="D250" s="9"/>
@@ -7845,7 +8193,9 @@
       <c r="N250" s="12"/>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A251" s="8"/>
+      <c r="A251" s="8">
+        <v>46496</v>
+      </c>
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
       <c r="D251" s="9"/>
@@ -7867,7 +8217,9 @@
       <c r="N251" s="12"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A252" s="8"/>
+      <c r="A252" s="8">
+        <v>46497</v>
+      </c>
       <c r="B252" s="9"/>
       <c r="C252" s="9"/>
       <c r="D252" s="9"/>
@@ -7889,7 +8241,9 @@
       <c r="N252" s="12"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A253" s="8"/>
+      <c r="A253" s="8">
+        <v>46498</v>
+      </c>
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
       <c r="D253" s="9"/>
@@ -7911,7 +8265,9 @@
       <c r="N253" s="12"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A254" s="8"/>
+      <c r="A254" s="8">
+        <v>46499</v>
+      </c>
       <c r="B254" s="9"/>
       <c r="C254" s="9"/>
       <c r="D254" s="9"/>
@@ -7933,7 +8289,9 @@
       <c r="N254" s="12"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A255" s="8"/>
+      <c r="A255" s="8">
+        <v>46500</v>
+      </c>
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
       <c r="D255" s="9"/>
@@ -7955,7 +8313,9 @@
       <c r="N255" s="12"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A256" s="8"/>
+      <c r="A256" s="8">
+        <v>46501</v>
+      </c>
       <c r="B256" s="9"/>
       <c r="C256" s="9"/>
       <c r="D256" s="9"/>
@@ -7977,7 +8337,9 @@
       <c r="N256" s="12"/>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A257" s="8"/>
+      <c r="A257" s="8">
+        <v>46502</v>
+      </c>
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
       <c r="D257" s="9"/>
@@ -7999,7 +8361,9 @@
       <c r="N257" s="12"/>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A258" s="8"/>
+      <c r="A258" s="8">
+        <v>46503</v>
+      </c>
       <c r="B258" s="9"/>
       <c r="C258" s="9"/>
       <c r="D258" s="9"/>
@@ -8021,7 +8385,9 @@
       <c r="N258" s="12"/>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A259" s="8"/>
+      <c r="A259" s="8">
+        <v>46504</v>
+      </c>
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
       <c r="D259" s="9"/>
@@ -8043,7 +8409,9 @@
       <c r="N259" s="12"/>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A260" s="8"/>
+      <c r="A260" s="8">
+        <v>46505</v>
+      </c>
       <c r="B260" s="9"/>
       <c r="C260" s="9"/>
       <c r="D260" s="9"/>
@@ -8065,7 +8433,9 @@
       <c r="N260" s="12"/>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A261" s="8"/>
+      <c r="A261" s="8">
+        <v>46506</v>
+      </c>
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
       <c r="D261" s="9"/>
@@ -8087,7 +8457,9 @@
       <c r="N261" s="12"/>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A262" s="8"/>
+      <c r="A262" s="8">
+        <v>46507</v>
+      </c>
       <c r="B262" s="9"/>
       <c r="C262" s="9"/>
       <c r="D262" s="9"/>
@@ -8109,7 +8481,9 @@
       <c r="N262" s="12"/>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A263" s="8"/>
+      <c r="A263" s="8">
+        <v>46508</v>
+      </c>
       <c r="B263" s="9"/>
       <c r="C263" s="9"/>
       <c r="D263" s="9"/>
@@ -8131,7 +8505,9 @@
       <c r="N263" s="12"/>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A264" s="8"/>
+      <c r="A264" s="8">
+        <v>46509</v>
+      </c>
       <c r="B264" s="9"/>
       <c r="C264" s="9"/>
       <c r="D264" s="9"/>
@@ -8153,7 +8529,9 @@
       <c r="N264" s="12"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A265" s="8"/>
+      <c r="A265" s="8">
+        <v>46510</v>
+      </c>
       <c r="B265" s="9"/>
       <c r="C265" s="9"/>
       <c r="D265" s="9"/>
@@ -8175,7 +8553,9 @@
       <c r="N265" s="12"/>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A266" s="8"/>
+      <c r="A266" s="8">
+        <v>46511</v>
+      </c>
       <c r="B266" s="9"/>
       <c r="C266" s="9"/>
       <c r="D266" s="9"/>
@@ -8197,7 +8577,9 @@
       <c r="N266" s="12"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A267" s="8"/>
+      <c r="A267" s="8">
+        <v>46512</v>
+      </c>
       <c r="B267" s="9"/>
       <c r="C267" s="9"/>
       <c r="D267" s="9"/>
@@ -8219,7 +8601,9 @@
       <c r="N267" s="12"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A268" s="8"/>
+      <c r="A268" s="8">
+        <v>46513</v>
+      </c>
       <c r="B268" s="9"/>
       <c r="C268" s="9"/>
       <c r="D268" s="9"/>
@@ -8241,7 +8625,9 @@
       <c r="N268" s="12"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A269" s="8"/>
+      <c r="A269" s="8">
+        <v>46514</v>
+      </c>
       <c r="B269" s="9"/>
       <c r="C269" s="9"/>
       <c r="D269" s="9"/>
@@ -8263,7 +8649,9 @@
       <c r="N269" s="12"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A270" s="8"/>
+      <c r="A270" s="8">
+        <v>46515</v>
+      </c>
       <c r="B270" s="9"/>
       <c r="C270" s="9"/>
       <c r="D270" s="9"/>
@@ -8285,7 +8673,9 @@
       <c r="N270" s="12"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A271" s="8"/>
+      <c r="A271" s="8">
+        <v>46516</v>
+      </c>
       <c r="B271" s="9"/>
       <c r="C271" s="9"/>
       <c r="D271" s="9"/>
@@ -8307,7 +8697,9 @@
       <c r="N271" s="12"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A272" s="8"/>
+      <c r="A272" s="8">
+        <v>46517</v>
+      </c>
       <c r="B272" s="9"/>
       <c r="C272" s="9"/>
       <c r="D272" s="9"/>
@@ -8329,7 +8721,9 @@
       <c r="N272" s="12"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A273" s="8"/>
+      <c r="A273" s="8">
+        <v>46518</v>
+      </c>
       <c r="B273" s="9"/>
       <c r="C273" s="9"/>
       <c r="D273" s="9"/>
@@ -8351,7 +8745,9 @@
       <c r="N273" s="12"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A274" s="8"/>
+      <c r="A274" s="8">
+        <v>46519</v>
+      </c>
       <c r="B274" s="9"/>
       <c r="C274" s="9"/>
       <c r="D274" s="9"/>
@@ -8373,7 +8769,9 @@
       <c r="N274" s="12"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A275" s="8"/>
+      <c r="A275" s="8">
+        <v>46520</v>
+      </c>
       <c r="B275" s="9"/>
       <c r="C275" s="9"/>
       <c r="D275" s="9"/>
@@ -8395,7 +8793,9 @@
       <c r="N275" s="12"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A276" s="8"/>
+      <c r="A276" s="8">
+        <v>46521</v>
+      </c>
       <c r="B276" s="9"/>
       <c r="C276" s="9"/>
       <c r="D276" s="9"/>
@@ -8417,7 +8817,9 @@
       <c r="N276" s="12"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A277" s="8"/>
+      <c r="A277" s="8">
+        <v>46522</v>
+      </c>
       <c r="B277" s="9"/>
       <c r="C277" s="9"/>
       <c r="D277" s="9"/>
@@ -8439,7 +8841,9 @@
       <c r="N277" s="12"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A278" s="8"/>
+      <c r="A278" s="8">
+        <v>46523</v>
+      </c>
       <c r="B278" s="9"/>
       <c r="C278" s="9"/>
       <c r="D278" s="9"/>
@@ -8461,7 +8865,9 @@
       <c r="N278" s="12"/>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A279" s="8"/>
+      <c r="A279" s="8">
+        <v>46524</v>
+      </c>
       <c r="B279" s="9"/>
       <c r="C279" s="9"/>
       <c r="D279" s="9"/>
@@ -8483,7 +8889,9 @@
       <c r="N279" s="12"/>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A280" s="8"/>
+      <c r="A280" s="8">
+        <v>46525</v>
+      </c>
       <c r="B280" s="9"/>
       <c r="C280" s="9"/>
       <c r="D280" s="9"/>
@@ -8505,7 +8913,9 @@
       <c r="N280" s="12"/>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A281" s="8"/>
+      <c r="A281" s="8">
+        <v>46526</v>
+      </c>
       <c r="B281" s="9"/>
       <c r="C281" s="9"/>
       <c r="D281" s="9"/>
@@ -8527,7 +8937,9 @@
       <c r="N281" s="12"/>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A282" s="8"/>
+      <c r="A282" s="8">
+        <v>46527</v>
+      </c>
       <c r="B282" s="9"/>
       <c r="C282" s="9"/>
       <c r="D282" s="9"/>
@@ -8549,7 +8961,9 @@
       <c r="N282" s="12"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A283" s="8"/>
+      <c r="A283" s="8">
+        <v>46528</v>
+      </c>
       <c r="B283" s="9"/>
       <c r="C283" s="9"/>
       <c r="D283" s="9"/>
@@ -8571,7 +8985,9 @@
       <c r="N283" s="12"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A284" s="8"/>
+      <c r="A284" s="8">
+        <v>46529</v>
+      </c>
       <c r="B284" s="9"/>
       <c r="C284" s="9"/>
       <c r="D284" s="9"/>
@@ -8593,7 +9009,9 @@
       <c r="N284" s="12"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A285" s="8"/>
+      <c r="A285" s="8">
+        <v>46530</v>
+      </c>
       <c r="B285" s="9"/>
       <c r="C285" s="9"/>
       <c r="D285" s="9"/>
@@ -8615,7 +9033,9 @@
       <c r="N285" s="12"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A286" s="8"/>
+      <c r="A286" s="8">
+        <v>46531</v>
+      </c>
       <c r="B286" s="9"/>
       <c r="C286" s="9"/>
       <c r="D286" s="9"/>
@@ -8637,7 +9057,9 @@
       <c r="N286" s="12"/>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A287" s="8"/>
+      <c r="A287" s="8">
+        <v>46532</v>
+      </c>
       <c r="B287" s="9"/>
       <c r="C287" s="9"/>
       <c r="D287" s="9"/>
@@ -8659,7 +9081,9 @@
       <c r="N287" s="12"/>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A288" s="8"/>
+      <c r="A288" s="8">
+        <v>46533</v>
+      </c>
       <c r="B288" s="9"/>
       <c r="C288" s="9"/>
       <c r="D288" s="9"/>
@@ -8681,7 +9105,9 @@
       <c r="N288" s="12"/>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A289" s="8"/>
+      <c r="A289" s="8">
+        <v>46534</v>
+      </c>
       <c r="B289" s="9"/>
       <c r="C289" s="9"/>
       <c r="D289" s="9"/>
@@ -8703,7 +9129,9 @@
       <c r="N289" s="12"/>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A290" s="8"/>
+      <c r="A290" s="8">
+        <v>46535</v>
+      </c>
       <c r="B290" s="9"/>
       <c r="C290" s="9"/>
       <c r="D290" s="9"/>
@@ -8725,7 +9153,9 @@
       <c r="N290" s="12"/>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A291" s="8"/>
+      <c r="A291" s="8">
+        <v>46536</v>
+      </c>
       <c r="B291" s="9"/>
       <c r="C291" s="9"/>
       <c r="D291" s="9"/>
@@ -8747,7 +9177,9 @@
       <c r="N291" s="12"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A292" s="8"/>
+      <c r="A292" s="8">
+        <v>46537</v>
+      </c>
       <c r="B292" s="9"/>
       <c r="C292" s="9"/>
       <c r="D292" s="9"/>
@@ -8769,7 +9201,9 @@
       <c r="N292" s="12"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A293" s="8"/>
+      <c r="A293" s="8">
+        <v>46538</v>
+      </c>
       <c r="B293" s="9"/>
       <c r="C293" s="9"/>
       <c r="D293" s="9"/>
@@ -8791,7 +9225,9 @@
       <c r="N293" s="12"/>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A294" s="8"/>
+      <c r="A294" s="8">
+        <v>46539</v>
+      </c>
       <c r="B294" s="9"/>
       <c r="C294" s="9"/>
       <c r="D294" s="9"/>
@@ -8813,7 +9249,9 @@
       <c r="N294" s="12"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A295" s="8"/>
+      <c r="A295" s="8">
+        <v>46540</v>
+      </c>
       <c r="B295" s="9"/>
       <c r="C295" s="9"/>
       <c r="D295" s="9"/>
@@ -8835,7 +9273,9 @@
       <c r="N295" s="12"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A296" s="8"/>
+      <c r="A296" s="8">
+        <v>46541</v>
+      </c>
       <c r="B296" s="9"/>
       <c r="C296" s="9"/>
       <c r="D296" s="9"/>
@@ -8857,7 +9297,9 @@
       <c r="N296" s="12"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A297" s="8"/>
+      <c r="A297" s="8">
+        <v>46542</v>
+      </c>
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
       <c r="D297" s="9"/>
@@ -8879,7 +9321,9 @@
       <c r="N297" s="12"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A298" s="8"/>
+      <c r="A298" s="8">
+        <v>46543</v>
+      </c>
       <c r="B298" s="9"/>
       <c r="C298" s="9"/>
       <c r="D298" s="9"/>
@@ -8901,7 +9345,9 @@
       <c r="N298" s="12"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A299" s="8"/>
+      <c r="A299" s="8">
+        <v>46544</v>
+      </c>
       <c r="B299" s="9"/>
       <c r="C299" s="9"/>
       <c r="D299" s="9"/>
@@ -8923,7 +9369,9 @@
       <c r="N299" s="12"/>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A300" s="8"/>
+      <c r="A300" s="8">
+        <v>46545</v>
+      </c>
       <c r="B300" s="9"/>
       <c r="C300" s="9"/>
       <c r="D300" s="9"/>
@@ -8945,7 +9393,9 @@
       <c r="N300" s="12"/>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A301" s="8"/>
+      <c r="A301" s="8">
+        <v>46546</v>
+      </c>
       <c r="B301" s="9"/>
       <c r="C301" s="9"/>
       <c r="D301" s="9"/>
@@ -8967,7 +9417,9 @@
       <c r="N301" s="12"/>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A302" s="8"/>
+      <c r="A302" s="8">
+        <v>46547</v>
+      </c>
       <c r="B302" s="9"/>
       <c r="C302" s="9"/>
       <c r="D302" s="9"/>
@@ -8989,7 +9441,9 @@
       <c r="N302" s="12"/>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A303" s="8"/>
+      <c r="A303" s="8">
+        <v>46548</v>
+      </c>
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
       <c r="D303" s="9"/>
@@ -9011,7 +9465,9 @@
       <c r="N303" s="12"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A304" s="8"/>
+      <c r="A304" s="8">
+        <v>46549</v>
+      </c>
       <c r="B304" s="9"/>
       <c r="C304" s="9"/>
       <c r="D304" s="9"/>
@@ -9033,7 +9489,9 @@
       <c r="N304" s="12"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A305" s="8"/>
+      <c r="A305" s="8">
+        <v>46550</v>
+      </c>
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
       <c r="D305" s="9"/>
@@ -9055,7 +9513,9 @@
       <c r="N305" s="12"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A306" s="8"/>
+      <c r="A306" s="8">
+        <v>46551</v>
+      </c>
       <c r="B306" s="9"/>
       <c r="C306" s="9"/>
       <c r="D306" s="9"/>
@@ -9077,7 +9537,9 @@
       <c r="N306" s="12"/>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A307" s="8"/>
+      <c r="A307" s="8">
+        <v>46552</v>
+      </c>
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
       <c r="D307" s="9"/>
@@ -9099,7 +9561,9 @@
       <c r="N307" s="12"/>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A308" s="8"/>
+      <c r="A308" s="8">
+        <v>46553</v>
+      </c>
       <c r="B308" s="9"/>
       <c r="C308" s="9"/>
       <c r="D308" s="9"/>
@@ -9121,7 +9585,9 @@
       <c r="N308" s="12"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A309" s="8"/>
+      <c r="A309" s="8">
+        <v>46554</v>
+      </c>
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
       <c r="D309" s="9"/>
@@ -9143,7 +9609,9 @@
       <c r="N309" s="12"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A310" s="8"/>
+      <c r="A310" s="8">
+        <v>46555</v>
+      </c>
       <c r="B310" s="9"/>
       <c r="C310" s="9"/>
       <c r="D310" s="9"/>
@@ -9165,7 +9633,9 @@
       <c r="N310" s="12"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A311" s="8"/>
+      <c r="A311" s="8">
+        <v>46556</v>
+      </c>
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
       <c r="D311" s="9"/>
@@ -9187,7 +9657,9 @@
       <c r="N311" s="12"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A312" s="8"/>
+      <c r="A312" s="8">
+        <v>46557</v>
+      </c>
       <c r="B312" s="9"/>
       <c r="C312" s="9"/>
       <c r="D312" s="9"/>
@@ -9209,7 +9681,9 @@
       <c r="N312" s="12"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A313" s="8"/>
+      <c r="A313" s="8">
+        <v>46558</v>
+      </c>
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
       <c r="D313" s="9"/>
@@ -9231,7 +9705,9 @@
       <c r="N313" s="12"/>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A314" s="8"/>
+      <c r="A314" s="8">
+        <v>46559</v>
+      </c>
       <c r="B314" s="9"/>
       <c r="C314" s="9"/>
       <c r="D314" s="9"/>
@@ -9253,7 +9729,9 @@
       <c r="N314" s="12"/>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A315" s="8"/>
+      <c r="A315" s="8">
+        <v>46560</v>
+      </c>
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
       <c r="D315" s="9"/>
@@ -9275,7 +9753,9 @@
       <c r="N315" s="12"/>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A316" s="8"/>
+      <c r="A316" s="8">
+        <v>46561</v>
+      </c>
       <c r="B316" s="9"/>
       <c r="C316" s="9"/>
       <c r="D316" s="9"/>
@@ -9297,7 +9777,9 @@
       <c r="N316" s="12"/>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A317" s="8"/>
+      <c r="A317" s="8">
+        <v>46562</v>
+      </c>
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
       <c r="D317" s="9"/>
@@ -9319,7 +9801,9 @@
       <c r="N317" s="12"/>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A318" s="8"/>
+      <c r="A318" s="8">
+        <v>46563</v>
+      </c>
       <c r="B318" s="9"/>
       <c r="C318" s="9"/>
       <c r="D318" s="9"/>
@@ -9341,7 +9825,9 @@
       <c r="N318" s="12"/>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A319" s="8"/>
+      <c r="A319" s="8">
+        <v>46564</v>
+      </c>
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
       <c r="D319" s="9"/>
@@ -9363,7 +9849,9 @@
       <c r="N319" s="12"/>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A320" s="8"/>
+      <c r="A320" s="8">
+        <v>46565</v>
+      </c>
       <c r="B320" s="9"/>
       <c r="C320" s="9"/>
       <c r="D320" s="9"/>
@@ -9385,7 +9873,9 @@
       <c r="N320" s="12"/>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A321" s="8"/>
+      <c r="A321" s="8">
+        <v>46566</v>
+      </c>
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
       <c r="D321" s="9"/>
@@ -9407,7 +9897,9 @@
       <c r="N321" s="12"/>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A322" s="8"/>
+      <c r="A322" s="8">
+        <v>46567</v>
+      </c>
       <c r="B322" s="9"/>
       <c r="C322" s="9"/>
       <c r="D322" s="9"/>
@@ -9429,7 +9921,9 @@
       <c r="N322" s="12"/>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A323" s="8"/>
+      <c r="A323" s="8">
+        <v>46568</v>
+      </c>
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
       <c r="D323" s="9"/>
@@ -9451,7 +9945,9 @@
       <c r="N323" s="12"/>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A324" s="8"/>
+      <c r="A324" s="8">
+        <v>46569</v>
+      </c>
       <c r="B324" s="9"/>
       <c r="C324" s="9"/>
       <c r="D324" s="9"/>
@@ -9473,7 +9969,9 @@
       <c r="N324" s="12"/>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A325" s="8"/>
+      <c r="A325" s="8">
+        <v>46570</v>
+      </c>
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
       <c r="D325" s="9"/>
@@ -9495,7 +9993,9 @@
       <c r="N325" s="12"/>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A326" s="8"/>
+      <c r="A326" s="8">
+        <v>46571</v>
+      </c>
       <c r="B326" s="9"/>
       <c r="C326" s="9"/>
       <c r="D326" s="9"/>
@@ -9517,7 +10017,9 @@
       <c r="N326" s="12"/>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A327" s="8"/>
+      <c r="A327" s="8">
+        <v>46572</v>
+      </c>
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
       <c r="D327" s="9"/>
@@ -9539,7 +10041,9 @@
       <c r="N327" s="12"/>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A328" s="8"/>
+      <c r="A328" s="8">
+        <v>46573</v>
+      </c>
       <c r="B328" s="9"/>
       <c r="C328" s="9"/>
       <c r="D328" s="9"/>
@@ -9561,7 +10065,9 @@
       <c r="N328" s="12"/>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A329" s="8"/>
+      <c r="A329" s="8">
+        <v>46574</v>
+      </c>
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
       <c r="D329" s="9"/>
@@ -9583,7 +10089,9 @@
       <c r="N329" s="12"/>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A330" s="8"/>
+      <c r="A330" s="8">
+        <v>46575</v>
+      </c>
       <c r="B330" s="9"/>
       <c r="C330" s="9"/>
       <c r="D330" s="9"/>
@@ -9605,7 +10113,9 @@
       <c r="N330" s="12"/>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A331" s="8"/>
+      <c r="A331" s="8">
+        <v>46576</v>
+      </c>
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
       <c r="D331" s="9"/>
@@ -9627,7 +10137,9 @@
       <c r="N331" s="12"/>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A332" s="8"/>
+      <c r="A332" s="8">
+        <v>46577</v>
+      </c>
       <c r="B332" s="9"/>
       <c r="C332" s="9"/>
       <c r="D332" s="9"/>
@@ -9649,7 +10161,9 @@
       <c r="N332" s="12"/>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A333" s="8"/>
+      <c r="A333" s="8">
+        <v>46578</v>
+      </c>
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
       <c r="D333" s="9"/>
@@ -9671,7 +10185,9 @@
       <c r="N333" s="12"/>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A334" s="8"/>
+      <c r="A334" s="8">
+        <v>46579</v>
+      </c>
       <c r="B334" s="9"/>
       <c r="C334" s="9"/>
       <c r="D334" s="9"/>
@@ -9693,7 +10209,9 @@
       <c r="N334" s="12"/>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A335" s="8"/>
+      <c r="A335" s="8">
+        <v>46580</v>
+      </c>
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
       <c r="D335" s="9"/>
@@ -9715,7 +10233,9 @@
       <c r="N335" s="12"/>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A336" s="8"/>
+      <c r="A336" s="8">
+        <v>46581</v>
+      </c>
       <c r="B336" s="9"/>
       <c r="C336" s="9"/>
       <c r="D336" s="9"/>
@@ -9737,7 +10257,9 @@
       <c r="N336" s="12"/>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A337" s="8"/>
+      <c r="A337" s="8">
+        <v>46582</v>
+      </c>
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
       <c r="D337" s="9"/>
@@ -9759,7 +10281,9 @@
       <c r="N337" s="12"/>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A338" s="8"/>
+      <c r="A338" s="8">
+        <v>46583</v>
+      </c>
       <c r="B338" s="9"/>
       <c r="C338" s="9"/>
       <c r="D338" s="9"/>
@@ -9781,7 +10305,9 @@
       <c r="N338" s="12"/>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A339" s="8"/>
+      <c r="A339" s="8">
+        <v>46584</v>
+      </c>
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
       <c r="D339" s="9"/>
@@ -9803,7 +10329,9 @@
       <c r="N339" s="12"/>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A340" s="8"/>
+      <c r="A340" s="8">
+        <v>46585</v>
+      </c>
       <c r="B340" s="9"/>
       <c r="C340" s="9"/>
       <c r="D340" s="9"/>
@@ -9825,7 +10353,9 @@
       <c r="N340" s="12"/>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A341" s="8"/>
+      <c r="A341" s="8">
+        <v>46586</v>
+      </c>
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
       <c r="D341" s="9"/>
@@ -9847,7 +10377,9 @@
       <c r="N341" s="12"/>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A342" s="8"/>
+      <c r="A342" s="8">
+        <v>46587</v>
+      </c>
       <c r="B342" s="9"/>
       <c r="C342" s="9"/>
       <c r="D342" s="9"/>
@@ -9869,7 +10401,9 @@
       <c r="N342" s="12"/>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A343" s="8"/>
+      <c r="A343" s="8">
+        <v>46588</v>
+      </c>
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
       <c r="D343" s="9"/>
@@ -9891,7 +10425,9 @@
       <c r="N343" s="12"/>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A344" s="8"/>
+      <c r="A344" s="8">
+        <v>46589</v>
+      </c>
       <c r="B344" s="9"/>
       <c r="C344" s="9"/>
       <c r="D344" s="9"/>
@@ -9913,7 +10449,9 @@
       <c r="N344" s="12"/>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A345" s="8"/>
+      <c r="A345" s="8">
+        <v>46590</v>
+      </c>
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
       <c r="D345" s="9"/>
@@ -9935,7 +10473,9 @@
       <c r="N345" s="12"/>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A346" s="8"/>
+      <c r="A346" s="8">
+        <v>46591</v>
+      </c>
       <c r="B346" s="9"/>
       <c r="C346" s="9"/>
       <c r="D346" s="9"/>
@@ -9957,7 +10497,9 @@
       <c r="N346" s="12"/>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A347" s="8"/>
+      <c r="A347" s="8">
+        <v>46592</v>
+      </c>
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
       <c r="D347" s="9"/>
@@ -9979,7 +10521,9 @@
       <c r="N347" s="12"/>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A348" s="8"/>
+      <c r="A348" s="8">
+        <v>46593</v>
+      </c>
       <c r="B348" s="9"/>
       <c r="C348" s="9"/>
       <c r="D348" s="9"/>
@@ -10001,7 +10545,9 @@
       <c r="N348" s="12"/>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A349" s="8"/>
+      <c r="A349" s="8">
+        <v>46594</v>
+      </c>
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
       <c r="D349" s="9"/>
@@ -10023,7 +10569,9 @@
       <c r="N349" s="12"/>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A350" s="8"/>
+      <c r="A350" s="8">
+        <v>46595</v>
+      </c>
       <c r="B350" s="9"/>
       <c r="C350" s="9"/>
       <c r="D350" s="9"/>
@@ -10045,7 +10593,9 @@
       <c r="N350" s="12"/>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A351" s="8"/>
+      <c r="A351" s="8">
+        <v>46596</v>
+      </c>
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
       <c r="D351" s="9"/>
@@ -10067,7 +10617,9 @@
       <c r="N351" s="12"/>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A352" s="8"/>
+      <c r="A352" s="8">
+        <v>46597</v>
+      </c>
       <c r="B352" s="9"/>
       <c r="C352" s="9"/>
       <c r="D352" s="9"/>
@@ -10089,7 +10641,9 @@
       <c r="N352" s="12"/>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A353" s="8"/>
+      <c r="A353" s="8">
+        <v>46598</v>
+      </c>
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
       <c r="D353" s="9"/>
@@ -10111,7 +10665,9 @@
       <c r="N353" s="12"/>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A354" s="8"/>
+      <c r="A354" s="8">
+        <v>46599</v>
+      </c>
       <c r="B354" s="9"/>
       <c r="C354" s="9"/>
       <c r="D354" s="9"/>
@@ -10133,7 +10689,9 @@
       <c r="N354" s="12"/>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A355" s="8"/>
+      <c r="A355" s="8">
+        <v>46600</v>
+      </c>
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
       <c r="D355" s="9"/>
@@ -10155,7 +10713,9 @@
       <c r="N355" s="12"/>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A356" s="8"/>
+      <c r="A356" s="8">
+        <v>46601</v>
+      </c>
       <c r="B356" s="9"/>
       <c r="C356" s="9"/>
       <c r="D356" s="9"/>
@@ -10177,7 +10737,9 @@
       <c r="N356" s="12"/>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A357" s="8"/>
+      <c r="A357" s="8">
+        <v>46602</v>
+      </c>
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
       <c r="D357" s="9"/>
@@ -10199,7 +10761,9 @@
       <c r="N357" s="12"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A358" s="8"/>
+      <c r="A358" s="8">
+        <v>46603</v>
+      </c>
       <c r="B358" s="9"/>
       <c r="C358" s="9"/>
       <c r="D358" s="9"/>
@@ -10221,7 +10785,9 @@
       <c r="N358" s="12"/>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A359" s="8"/>
+      <c r="A359" s="8">
+        <v>46604</v>
+      </c>
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
       <c r="D359" s="9"/>
@@ -10243,7 +10809,9 @@
       <c r="N359" s="12"/>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A360" s="8"/>
+      <c r="A360" s="8">
+        <v>46605</v>
+      </c>
       <c r="B360" s="9"/>
       <c r="C360" s="9"/>
       <c r="D360" s="9"/>
@@ -10265,7 +10833,9 @@
       <c r="N360" s="12"/>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A361" s="8"/>
+      <c r="A361" s="8">
+        <v>46606</v>
+      </c>
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
       <c r="D361" s="9"/>
@@ -10287,7 +10857,9 @@
       <c r="N361" s="12"/>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A362" s="8"/>
+      <c r="A362" s="8">
+        <v>46607</v>
+      </c>
       <c r="B362" s="9"/>
       <c r="C362" s="9"/>
       <c r="D362" s="9"/>
@@ -10309,7 +10881,9 @@
       <c r="N362" s="12"/>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A363" s="8"/>
+      <c r="A363" s="8">
+        <v>46608</v>
+      </c>
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
       <c r="D363" s="9"/>
@@ -10331,7 +10905,9 @@
       <c r="N363" s="12"/>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A364" s="8"/>
+      <c r="A364" s="8">
+        <v>46609</v>
+      </c>
       <c r="B364" s="9"/>
       <c r="C364" s="9"/>
       <c r="D364" s="9"/>
@@ -10353,7 +10929,9 @@
       <c r="N364" s="12"/>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A365" s="8"/>
+      <c r="A365" s="8">
+        <v>46610</v>
+      </c>
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
       <c r="D365" s="9"/>
@@ -10375,7 +10953,9 @@
       <c r="N365" s="12"/>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A366" s="8"/>
+      <c r="A366" s="8">
+        <v>46611</v>
+      </c>
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
       <c r="D366" s="9"/>
@@ -10397,7 +10977,9 @@
       <c r="N366" s="12"/>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A367" s="8"/>
+      <c r="A367" s="8">
+        <v>46612</v>
+      </c>
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
       <c r="D367" s="9"/>
@@ -10419,7 +11001,9 @@
       <c r="N367" s="12"/>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A368" s="8"/>
+      <c r="A368" s="8">
+        <v>46613</v>
+      </c>
       <c r="B368" s="9"/>
       <c r="C368" s="9"/>
       <c r="D368" s="9"/>
@@ -10441,7 +11025,9 @@
       <c r="N368" s="12"/>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A369" s="8"/>
+      <c r="A369" s="8">
+        <v>46614</v>
+      </c>
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
       <c r="D369" s="9"/>
@@ -10463,7 +11049,9 @@
       <c r="N369" s="12"/>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A370" s="8"/>
+      <c r="A370" s="8">
+        <v>46615</v>
+      </c>
       <c r="B370" s="9"/>
       <c r="C370" s="9"/>
       <c r="D370" s="9"/>
@@ -10485,7 +11073,9 @@
       <c r="N370" s="12"/>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A371" s="8"/>
+      <c r="A371" s="8">
+        <v>46616</v>
+      </c>
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
       <c r="D371" s="9"/>
@@ -10507,7 +11097,9 @@
       <c r="N371" s="12"/>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A372" s="8"/>
+      <c r="A372" s="8">
+        <v>46617</v>
+      </c>
       <c r="B372" s="9"/>
       <c r="C372" s="9"/>
       <c r="D372" s="9"/>
@@ -10529,7 +11121,9 @@
       <c r="N372" s="12"/>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A373" s="8"/>
+      <c r="A373" s="8">
+        <v>46618</v>
+      </c>
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
       <c r="D373" s="9"/>
@@ -10551,7 +11145,9 @@
       <c r="N373" s="12"/>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A374" s="8"/>
+      <c r="A374" s="8">
+        <v>46619</v>
+      </c>
       <c r="B374" s="9"/>
       <c r="C374" s="9"/>
       <c r="D374" s="9"/>
@@ -10573,7 +11169,9 @@
       <c r="N374" s="12"/>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A375" s="8"/>
+      <c r="A375" s="8">
+        <v>46620</v>
+      </c>
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
       <c r="D375" s="9"/>
@@ -10595,7 +11193,9 @@
       <c r="N375" s="12"/>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A376" s="8"/>
+      <c r="A376" s="8">
+        <v>46621</v>
+      </c>
       <c r="B376" s="9"/>
       <c r="C376" s="9"/>
       <c r="D376" s="9"/>
@@ -10617,7 +11217,9 @@
       <c r="N376" s="12"/>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A377" s="8"/>
+      <c r="A377" s="8">
+        <v>46622</v>
+      </c>
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
       <c r="D377" s="9"/>
@@ -10639,7 +11241,9 @@
       <c r="N377" s="12"/>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A378" s="8"/>
+      <c r="A378" s="8">
+        <v>46623</v>
+      </c>
       <c r="B378" s="9"/>
       <c r="C378" s="9"/>
       <c r="D378" s="9"/>
@@ -10661,7 +11265,9 @@
       <c r="N378" s="12"/>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A379" s="8"/>
+      <c r="A379" s="8">
+        <v>46624</v>
+      </c>
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
       <c r="D379" s="9"/>
@@ -10683,7 +11289,9 @@
       <c r="N379" s="12"/>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A380" s="8"/>
+      <c r="A380" s="8">
+        <v>46625</v>
+      </c>
       <c r="B380" s="9"/>
       <c r="C380" s="9"/>
       <c r="D380" s="9"/>
@@ -10705,7 +11313,9 @@
       <c r="N380" s="12"/>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A381" s="8"/>
+      <c r="A381" s="8">
+        <v>46626</v>
+      </c>
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
       <c r="D381" s="9"/>
@@ -10727,7 +11337,9 @@
       <c r="N381" s="12"/>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A382" s="8"/>
+      <c r="A382" s="8">
+        <v>46627</v>
+      </c>
       <c r="B382" s="9"/>
       <c r="C382" s="9"/>
       <c r="D382" s="9"/>
@@ -10749,7 +11361,9 @@
       <c r="N382" s="12"/>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A383" s="8"/>
+      <c r="A383" s="8">
+        <v>46628</v>
+      </c>
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
       <c r="D383" s="9"/>
@@ -10771,7 +11385,9 @@
       <c r="N383" s="12"/>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A384" s="8"/>
+      <c r="A384" s="8">
+        <v>46629</v>
+      </c>
       <c r="B384" s="9"/>
       <c r="C384" s="9"/>
       <c r="D384" s="9"/>
@@ -10793,7 +11409,9 @@
       <c r="N384" s="12"/>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A385" s="8"/>
+      <c r="A385" s="8">
+        <v>46630</v>
+      </c>
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
       <c r="D385" s="9"/>
@@ -10815,7 +11433,9 @@
       <c r="N385" s="12"/>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A386" s="8"/>
+      <c r="A386" s="8">
+        <v>46631</v>
+      </c>
       <c r="B386" s="9"/>
       <c r="C386" s="9"/>
       <c r="D386" s="9"/>
@@ -10837,7 +11457,9 @@
       <c r="N386" s="12"/>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A387" s="8"/>
+      <c r="A387" s="8">
+        <v>46632</v>
+      </c>
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
       <c r="D387" s="9"/>
@@ -10859,7 +11481,9 @@
       <c r="N387" s="12"/>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A388" s="8"/>
+      <c r="A388" s="8">
+        <v>46633</v>
+      </c>
       <c r="B388" s="9"/>
       <c r="C388" s="9"/>
       <c r="D388" s="9"/>
@@ -10881,7 +11505,9 @@
       <c r="N388" s="12"/>
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A389" s="8"/>
+      <c r="A389" s="8">
+        <v>46634</v>
+      </c>
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
       <c r="D389" s="9"/>
@@ -10903,7 +11529,9 @@
       <c r="N389" s="12"/>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A390" s="8"/>
+      <c r="A390" s="8">
+        <v>46635</v>
+      </c>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
       <c r="D390" s="9"/>
@@ -10925,7 +11553,9 @@
       <c r="N390" s="12"/>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A391" s="8"/>
+      <c r="A391" s="8">
+        <v>46636</v>
+      </c>
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
       <c r="D391" s="9"/>
@@ -10947,7 +11577,9 @@
       <c r="N391" s="12"/>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A392" s="8"/>
+      <c r="A392" s="8">
+        <v>46637</v>
+      </c>
       <c r="B392" s="9"/>
       <c r="C392" s="9"/>
       <c r="D392" s="9"/>
@@ -10969,7 +11601,9 @@
       <c r="N392" s="12"/>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A393" s="8"/>
+      <c r="A393" s="8">
+        <v>46638</v>
+      </c>
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
       <c r="D393" s="9"/>
@@ -10991,7 +11625,9 @@
       <c r="N393" s="12"/>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A394" s="8"/>
+      <c r="A394" s="8">
+        <v>46639</v>
+      </c>
       <c r="B394" s="9"/>
       <c r="C394" s="9"/>
       <c r="D394" s="9"/>
@@ -11013,7 +11649,9 @@
       <c r="N394" s="12"/>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A395" s="8"/>
+      <c r="A395" s="8">
+        <v>46640</v>
+      </c>
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
       <c r="D395" s="9"/>
@@ -11035,7 +11673,9 @@
       <c r="N395" s="12"/>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A396" s="8"/>
+      <c r="A396" s="8">
+        <v>46641</v>
+      </c>
       <c r="B396" s="9"/>
       <c r="C396" s="9"/>
       <c r="D396" s="9"/>
@@ -11057,7 +11697,9 @@
       <c r="N396" s="12"/>
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A397" s="8"/>
+      <c r="A397" s="8">
+        <v>46642</v>
+      </c>
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
       <c r="D397" s="9"/>
@@ -11079,7 +11721,9 @@
       <c r="N397" s="12"/>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A398" s="8"/>
+      <c r="A398" s="8">
+        <v>46643</v>
+      </c>
       <c r="B398" s="9"/>
       <c r="C398" s="9"/>
       <c r="D398" s="9"/>
@@ -11101,7 +11745,9 @@
       <c r="N398" s="12"/>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A399" s="8"/>
+      <c r="A399" s="8">
+        <v>46644</v>
+      </c>
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
       <c r="D399" s="9"/>
@@ -11123,7 +11769,9 @@
       <c r="N399" s="12"/>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A400" s="8"/>
+      <c r="A400" s="8">
+        <v>46645</v>
+      </c>
       <c r="B400" s="9"/>
       <c r="C400" s="9"/>
       <c r="D400" s="9"/>
@@ -11145,7 +11793,9 @@
       <c r="N400" s="12"/>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="8"/>
+      <c r="A401" s="8">
+        <v>46646</v>
+      </c>
       <c r="B401" s="9"/>
       <c r="C401" s="9"/>
       <c r="D401" s="9"/>

--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\GIT\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0C4767-2C88-4905-9A34-F3395FEDE65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809255B0-520A-4601-85F2-487B165AF428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4068,20 +4068,22 @@
       <c r="A79" s="8">
         <v>46324</v>
       </c>
-      <c r="B79" s="9"/>
+      <c r="B79" s="9">
+        <v>480</v>
+      </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+      <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K79" s="11"/>
       <c r="L79" s="11"/>
@@ -4092,20 +4094,22 @@
       <c r="A80" s="8">
         <v>46325</v>
       </c>
-      <c r="B80" s="9"/>
+      <c r="B80" s="9">
+        <v>360</v>
+      </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
+      <c r="I80" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
+        <v>360</v>
+      </c>
+      <c r="J80" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K80" s="11"/>
       <c r="L80" s="11"/>
